--- a/comments_1.xlsx
+++ b/comments_1.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,12 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A83589-130D-CC44-B813-8827A85A9383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{B5AD1834-6A30-0143-9235-A1E0209502BE}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{B5AD1834-6A30-0143-9235-A1E0209502BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -3680,7 +3680,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3690,9 +3690,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -3700,9 +3697,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4195,7 +4189,7 @@
       <c r="B14">
         <v>13</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" t="s">
         <v>102</v>
       </c>
     </row>
@@ -7357,10 +7351,10 @@
       </c>
     </row>
     <row r="302" spans="1:3">
-      <c r="A302" s="4">
+      <c r="A302" s="3">
         <v>4</v>
       </c>
-      <c r="B302" s="4">
+      <c r="B302" s="3">
         <v>1</v>
       </c>
       <c r="C302" t="s">
@@ -7368,10 +7362,10 @@
       </c>
     </row>
     <row r="303" spans="1:3">
-      <c r="A303" s="4">
+      <c r="A303" s="3">
         <v>4</v>
       </c>
-      <c r="B303" s="4">
+      <c r="B303" s="3">
         <v>2</v>
       </c>
       <c r="C303" t="s">
@@ -7379,10 +7373,10 @@
       </c>
     </row>
     <row r="304" spans="1:3">
-      <c r="A304" s="4">
+      <c r="A304" s="3">
         <v>4</v>
       </c>
-      <c r="B304" s="4">
+      <c r="B304" s="3">
         <v>3</v>
       </c>
       <c r="C304" t="s">
@@ -7390,10 +7384,10 @@
       </c>
     </row>
     <row r="305" spans="1:3">
-      <c r="A305" s="4">
+      <c r="A305" s="3">
         <v>4</v>
       </c>
-      <c r="B305" s="4">
+      <c r="B305" s="3">
         <v>4</v>
       </c>
       <c r="C305" t="s">
@@ -7401,10 +7395,10 @@
       </c>
     </row>
     <row r="306" spans="1:3">
-      <c r="A306" s="4">
+      <c r="A306" s="3">
         <v>4</v>
       </c>
-      <c r="B306" s="4">
+      <c r="B306" s="3">
         <v>5</v>
       </c>
       <c r="C306" t="s">
@@ -7412,10 +7406,10 @@
       </c>
     </row>
     <row r="307" spans="1:3">
-      <c r="A307" s="4">
+      <c r="A307" s="3">
         <v>4</v>
       </c>
-      <c r="B307" s="4">
+      <c r="B307" s="3">
         <v>6</v>
       </c>
       <c r="C307" t="s">
@@ -7423,10 +7417,10 @@
       </c>
     </row>
     <row r="308" spans="1:3">
-      <c r="A308" s="4">
+      <c r="A308" s="3">
         <v>4</v>
       </c>
-      <c r="B308" s="4">
+      <c r="B308" s="3">
         <v>7</v>
       </c>
       <c r="C308" t="s">
@@ -7434,10 +7428,10 @@
       </c>
     </row>
     <row r="309" spans="1:3">
-      <c r="A309" s="4">
+      <c r="A309" s="3">
         <v>4</v>
       </c>
-      <c r="B309" s="4">
+      <c r="B309" s="3">
         <v>8</v>
       </c>
       <c r="C309" t="s">
@@ -7445,10 +7439,10 @@
       </c>
     </row>
     <row r="310" spans="1:3">
-      <c r="A310" s="4">
+      <c r="A310" s="3">
         <v>4</v>
       </c>
-      <c r="B310" s="4">
+      <c r="B310" s="3">
         <v>9</v>
       </c>
       <c r="C310" t="s">
@@ -7456,10 +7450,10 @@
       </c>
     </row>
     <row r="311" spans="1:3">
-      <c r="A311" s="4">
+      <c r="A311" s="3">
         <v>4</v>
       </c>
-      <c r="B311" s="4">
+      <c r="B311" s="3">
         <v>10</v>
       </c>
       <c r="C311" t="s">
@@ -7467,10 +7461,10 @@
       </c>
     </row>
     <row r="312" spans="1:3">
-      <c r="A312" s="4">
+      <c r="A312" s="3">
         <v>4</v>
       </c>
-      <c r="B312" s="4">
+      <c r="B312" s="3">
         <v>11</v>
       </c>
       <c r="C312" t="s">
@@ -7478,10 +7472,10 @@
       </c>
     </row>
     <row r="313" spans="1:3">
-      <c r="A313" s="4">
+      <c r="A313" s="3">
         <v>4</v>
       </c>
-      <c r="B313" s="4">
+      <c r="B313" s="3">
         <v>12</v>
       </c>
       <c r="C313" t="s">
@@ -7489,10 +7483,10 @@
       </c>
     </row>
     <row r="314" spans="1:3">
-      <c r="A314" s="4">
+      <c r="A314" s="3">
         <v>4</v>
       </c>
-      <c r="B314" s="4">
+      <c r="B314" s="3">
         <v>13</v>
       </c>
       <c r="C314" t="s">
@@ -7500,10 +7494,10 @@
       </c>
     </row>
     <row r="315" spans="1:3">
-      <c r="A315" s="4">
+      <c r="A315" s="3">
         <v>4</v>
       </c>
-      <c r="B315" s="4">
+      <c r="B315" s="3">
         <v>14</v>
       </c>
       <c r="C315" t="s">
@@ -7511,10 +7505,10 @@
       </c>
     </row>
     <row r="316" spans="1:3">
-      <c r="A316" s="4">
+      <c r="A316" s="3">
         <v>4</v>
       </c>
-      <c r="B316" s="4">
+      <c r="B316" s="3">
         <v>15</v>
       </c>
       <c r="C316" t="s">
@@ -7522,10 +7516,10 @@
       </c>
     </row>
     <row r="317" spans="1:3">
-      <c r="A317" s="4">
+      <c r="A317" s="3">
         <v>4</v>
       </c>
-      <c r="B317" s="4">
+      <c r="B317" s="3">
         <v>16</v>
       </c>
       <c r="C317" t="s">
@@ -7533,10 +7527,10 @@
       </c>
     </row>
     <row r="318" spans="1:3">
-      <c r="A318" s="4">
+      <c r="A318" s="3">
         <v>4</v>
       </c>
-      <c r="B318" s="4">
+      <c r="B318" s="3">
         <v>17</v>
       </c>
       <c r="C318" t="s">
@@ -7544,10 +7538,10 @@
       </c>
     </row>
     <row r="319" spans="1:3">
-      <c r="A319" s="4">
+      <c r="A319" s="3">
         <v>4</v>
       </c>
-      <c r="B319" s="4">
+      <c r="B319" s="3">
         <v>18</v>
       </c>
       <c r="C319" t="s">
@@ -7555,10 +7549,10 @@
       </c>
     </row>
     <row r="320" spans="1:3">
-      <c r="A320" s="4">
+      <c r="A320" s="3">
         <v>4</v>
       </c>
-      <c r="B320" s="4">
+      <c r="B320" s="3">
         <v>19</v>
       </c>
       <c r="C320" t="s">
@@ -7566,10 +7560,10 @@
       </c>
     </row>
     <row r="321" spans="1:3">
-      <c r="A321" s="4">
+      <c r="A321" s="3">
         <v>4</v>
       </c>
-      <c r="B321" s="4">
+      <c r="B321" s="3">
         <v>20</v>
       </c>
       <c r="C321" t="s">
@@ -7577,10 +7571,10 @@
       </c>
     </row>
     <row r="322" spans="1:3">
-      <c r="A322" s="4">
+      <c r="A322" s="3">
         <v>4</v>
       </c>
-      <c r="B322" s="4">
+      <c r="B322" s="3">
         <v>21</v>
       </c>
       <c r="C322" t="s">
@@ -7588,10 +7582,10 @@
       </c>
     </row>
     <row r="323" spans="1:3">
-      <c r="A323" s="4">
+      <c r="A323" s="3">
         <v>4</v>
       </c>
-      <c r="B323" s="4">
+      <c r="B323" s="3">
         <v>22</v>
       </c>
       <c r="C323" t="s">
@@ -7599,10 +7593,10 @@
       </c>
     </row>
     <row r="324" spans="1:3">
-      <c r="A324" s="4">
+      <c r="A324" s="3">
         <v>4</v>
       </c>
-      <c r="B324" s="4">
+      <c r="B324" s="3">
         <v>23</v>
       </c>
       <c r="C324" t="s">
@@ -7610,10 +7604,10 @@
       </c>
     </row>
     <row r="325" spans="1:3">
-      <c r="A325" s="4">
+      <c r="A325" s="3">
         <v>4</v>
       </c>
-      <c r="B325" s="4">
+      <c r="B325" s="3">
         <v>24</v>
       </c>
       <c r="C325" t="s">
@@ -7621,10 +7615,10 @@
       </c>
     </row>
     <row r="326" spans="1:3">
-      <c r="A326" s="4">
+      <c r="A326" s="3">
         <v>4</v>
       </c>
-      <c r="B326" s="4">
+      <c r="B326" s="3">
         <v>25</v>
       </c>
       <c r="C326" t="s">
@@ -7632,10 +7626,10 @@
       </c>
     </row>
     <row r="327" spans="1:3">
-      <c r="A327" s="4">
+      <c r="A327" s="3">
         <v>4</v>
       </c>
-      <c r="B327" s="4">
+      <c r="B327" s="3">
         <v>26</v>
       </c>
       <c r="C327" t="s">
@@ -7643,10 +7637,10 @@
       </c>
     </row>
     <row r="328" spans="1:3">
-      <c r="A328" s="4">
+      <c r="A328" s="3">
         <v>4</v>
       </c>
-      <c r="B328" s="4">
+      <c r="B328" s="3">
         <v>27</v>
       </c>
       <c r="C328" t="s">
@@ -7654,10 +7648,10 @@
       </c>
     </row>
     <row r="329" spans="1:3">
-      <c r="A329" s="4">
+      <c r="A329" s="3">
         <v>4</v>
       </c>
-      <c r="B329" s="4">
+      <c r="B329" s="3">
         <v>28</v>
       </c>
       <c r="C329" t="s">
@@ -7665,10 +7659,10 @@
       </c>
     </row>
     <row r="330" spans="1:3">
-      <c r="A330" s="4">
+      <c r="A330" s="3">
         <v>4</v>
       </c>
-      <c r="B330" s="4">
+      <c r="B330" s="3">
         <v>29</v>
       </c>
       <c r="C330" t="s">
@@ -7676,10 +7670,10 @@
       </c>
     </row>
     <row r="331" spans="1:3">
-      <c r="A331" s="4">
+      <c r="A331" s="3">
         <v>4</v>
       </c>
-      <c r="B331" s="4">
+      <c r="B331" s="3">
         <v>30</v>
       </c>
       <c r="C331" t="s">
@@ -7687,10 +7681,10 @@
       </c>
     </row>
     <row r="332" spans="1:3">
-      <c r="A332" s="4">
+      <c r="A332" s="3">
         <v>4</v>
       </c>
-      <c r="B332" s="4">
+      <c r="B332" s="3">
         <v>31</v>
       </c>
       <c r="C332" t="s">
@@ -7698,10 +7692,10 @@
       </c>
     </row>
     <row r="333" spans="1:3">
-      <c r="A333" s="4">
+      <c r="A333" s="3">
         <v>4</v>
       </c>
-      <c r="B333" s="4">
+      <c r="B333" s="3">
         <v>32</v>
       </c>
       <c r="C333" t="s">
@@ -7709,10 +7703,10 @@
       </c>
     </row>
     <row r="334" spans="1:3">
-      <c r="A334" s="4">
+      <c r="A334" s="3">
         <v>4</v>
       </c>
-      <c r="B334" s="4">
+      <c r="B334" s="3">
         <v>33</v>
       </c>
       <c r="C334" t="s">
@@ -7720,10 +7714,10 @@
       </c>
     </row>
     <row r="335" spans="1:3">
-      <c r="A335" s="4">
+      <c r="A335" s="3">
         <v>4</v>
       </c>
-      <c r="B335" s="4">
+      <c r="B335" s="3">
         <v>34</v>
       </c>
       <c r="C335" t="s">
@@ -7731,10 +7725,10 @@
       </c>
     </row>
     <row r="336" spans="1:3">
-      <c r="A336" s="4">
+      <c r="A336" s="3">
         <v>4</v>
       </c>
-      <c r="B336" s="4">
+      <c r="B336" s="3">
         <v>35</v>
       </c>
       <c r="C336" t="s">
@@ -7742,10 +7736,10 @@
       </c>
     </row>
     <row r="337" spans="1:3">
-      <c r="A337" s="4">
+      <c r="A337" s="3">
         <v>4</v>
       </c>
-      <c r="B337" s="4">
+      <c r="B337" s="3">
         <v>36</v>
       </c>
       <c r="C337" t="s">
@@ -7753,10 +7747,10 @@
       </c>
     </row>
     <row r="338" spans="1:3">
-      <c r="A338" s="4">
+      <c r="A338" s="3">
         <v>4</v>
       </c>
-      <c r="B338" s="4">
+      <c r="B338" s="3">
         <v>37</v>
       </c>
       <c r="C338" t="s">
@@ -7764,10 +7758,10 @@
       </c>
     </row>
     <row r="339" spans="1:3">
-      <c r="A339" s="4">
+      <c r="A339" s="3">
         <v>4</v>
       </c>
-      <c r="B339" s="4">
+      <c r="B339" s="3">
         <v>38</v>
       </c>
       <c r="C339" t="s">
@@ -7775,10 +7769,10 @@
       </c>
     </row>
     <row r="340" spans="1:3">
-      <c r="A340" s="4">
+      <c r="A340" s="3">
         <v>4</v>
       </c>
-      <c r="B340" s="4">
+      <c r="B340" s="3">
         <v>39</v>
       </c>
       <c r="C340" t="s">
@@ -7786,10 +7780,10 @@
       </c>
     </row>
     <row r="341" spans="1:3">
-      <c r="A341" s="4">
+      <c r="A341" s="3">
         <v>4</v>
       </c>
-      <c r="B341" s="4">
+      <c r="B341" s="3">
         <v>40</v>
       </c>
       <c r="C341" t="s">
@@ -7797,10 +7791,10 @@
       </c>
     </row>
     <row r="342" spans="1:3">
-      <c r="A342" s="4">
+      <c r="A342" s="3">
         <v>4</v>
       </c>
-      <c r="B342" s="4">
+      <c r="B342" s="3">
         <v>41</v>
       </c>
       <c r="C342" t="s">
@@ -7808,10 +7802,10 @@
       </c>
     </row>
     <row r="343" spans="1:3">
-      <c r="A343" s="4">
+      <c r="A343" s="3">
         <v>4</v>
       </c>
-      <c r="B343" s="4">
+      <c r="B343" s="3">
         <v>42</v>
       </c>
       <c r="C343" t="s">
@@ -7819,10 +7813,10 @@
       </c>
     </row>
     <row r="344" spans="1:3">
-      <c r="A344" s="4">
+      <c r="A344" s="3">
         <v>4</v>
       </c>
-      <c r="B344" s="4">
+      <c r="B344" s="3">
         <v>43</v>
       </c>
       <c r="C344" t="s">
@@ -7830,10 +7824,10 @@
       </c>
     </row>
     <row r="345" spans="1:3">
-      <c r="A345" s="4">
+      <c r="A345" s="3">
         <v>4</v>
       </c>
-      <c r="B345" s="4">
+      <c r="B345" s="3">
         <v>44</v>
       </c>
       <c r="C345" t="s">
@@ -7841,10 +7835,10 @@
       </c>
     </row>
     <row r="346" spans="1:3">
-      <c r="A346" s="4">
+      <c r="A346" s="3">
         <v>4</v>
       </c>
-      <c r="B346" s="4">
+      <c r="B346" s="3">
         <v>45</v>
       </c>
       <c r="C346" t="s">
@@ -7852,10 +7846,10 @@
       </c>
     </row>
     <row r="347" spans="1:3">
-      <c r="A347" s="4">
+      <c r="A347" s="3">
         <v>4</v>
       </c>
-      <c r="B347" s="4">
+      <c r="B347" s="3">
         <v>46</v>
       </c>
       <c r="C347" t="s">
@@ -7863,10 +7857,10 @@
       </c>
     </row>
     <row r="348" spans="1:3">
-      <c r="A348" s="4">
+      <c r="A348" s="3">
         <v>4</v>
       </c>
-      <c r="B348" s="4">
+      <c r="B348" s="3">
         <v>47</v>
       </c>
       <c r="C348" t="s">
@@ -7874,10 +7868,10 @@
       </c>
     </row>
     <row r="349" spans="1:3">
-      <c r="A349" s="4">
+      <c r="A349" s="3">
         <v>4</v>
       </c>
-      <c r="B349" s="4">
+      <c r="B349" s="3">
         <v>48</v>
       </c>
       <c r="C349" t="s">
@@ -7885,10 +7879,10 @@
       </c>
     </row>
     <row r="350" spans="1:3">
-      <c r="A350" s="4">
+      <c r="A350" s="3">
         <v>4</v>
       </c>
-      <c r="B350" s="4">
+      <c r="B350" s="3">
         <v>49</v>
       </c>
       <c r="C350" t="s">
@@ -7896,10 +7890,10 @@
       </c>
     </row>
     <row r="351" spans="1:3">
-      <c r="A351" s="4">
+      <c r="A351" s="3">
         <v>4</v>
       </c>
-      <c r="B351" s="4">
+      <c r="B351" s="3">
         <v>50</v>
       </c>
       <c r="C351" t="s">
@@ -7907,10 +7901,10 @@
       </c>
     </row>
     <row r="352" spans="1:3">
-      <c r="A352" s="4">
+      <c r="A352" s="3">
         <v>4</v>
       </c>
-      <c r="B352" s="4">
+      <c r="B352" s="3">
         <v>51</v>
       </c>
       <c r="C352" t="s">
@@ -7918,10 +7912,10 @@
       </c>
     </row>
     <row r="353" spans="1:3">
-      <c r="A353" s="4">
+      <c r="A353" s="3">
         <v>4</v>
       </c>
-      <c r="B353" s="4">
+      <c r="B353" s="3">
         <v>52</v>
       </c>
       <c r="C353" t="s">
@@ -7929,10 +7923,10 @@
       </c>
     </row>
     <row r="354" spans="1:3">
-      <c r="A354" s="4">
+      <c r="A354" s="3">
         <v>4</v>
       </c>
-      <c r="B354" s="4">
+      <c r="B354" s="3">
         <v>53</v>
       </c>
       <c r="C354" t="s">
@@ -7940,10 +7934,10 @@
       </c>
     </row>
     <row r="355" spans="1:3">
-      <c r="A355" s="4">
+      <c r="A355" s="3">
         <v>4</v>
       </c>
-      <c r="B355" s="4">
+      <c r="B355" s="3">
         <v>54</v>
       </c>
       <c r="C355" t="s">
@@ -7951,10 +7945,10 @@
       </c>
     </row>
     <row r="356" spans="1:3">
-      <c r="A356" s="4">
+      <c r="A356" s="3">
         <v>4</v>
       </c>
-      <c r="B356" s="4">
+      <c r="B356" s="3">
         <v>55</v>
       </c>
       <c r="C356" t="s">
@@ -7962,10 +7956,10 @@
       </c>
     </row>
     <row r="357" spans="1:3">
-      <c r="A357" s="4">
+      <c r="A357" s="3">
         <v>4</v>
       </c>
-      <c r="B357" s="4">
+      <c r="B357" s="3">
         <v>56</v>
       </c>
       <c r="C357" t="s">
@@ -7973,10 +7967,10 @@
       </c>
     </row>
     <row r="358" spans="1:3">
-      <c r="A358" s="4">
+      <c r="A358" s="3">
         <v>4</v>
       </c>
-      <c r="B358" s="4">
+      <c r="B358" s="3">
         <v>57</v>
       </c>
       <c r="C358" t="s">
@@ -7984,10 +7978,10 @@
       </c>
     </row>
     <row r="359" spans="1:3">
-      <c r="A359" s="4">
+      <c r="A359" s="3">
         <v>4</v>
       </c>
-      <c r="B359" s="4">
+      <c r="B359" s="3">
         <v>58</v>
       </c>
       <c r="C359" t="s">
@@ -7995,10 +7989,10 @@
       </c>
     </row>
     <row r="360" spans="1:3">
-      <c r="A360" s="4">
+      <c r="A360" s="3">
         <v>4</v>
       </c>
-      <c r="B360" s="4">
+      <c r="B360" s="3">
         <v>59</v>
       </c>
       <c r="C360" t="s">
@@ -8006,10 +8000,10 @@
       </c>
     </row>
     <row r="361" spans="1:3">
-      <c r="A361" s="4">
+      <c r="A361" s="3">
         <v>4</v>
       </c>
-      <c r="B361" s="4">
+      <c r="B361" s="3">
         <v>60</v>
       </c>
       <c r="C361" t="s">
@@ -8017,10 +8011,10 @@
       </c>
     </row>
     <row r="362" spans="1:3">
-      <c r="A362" s="4">
+      <c r="A362" s="3">
         <v>4</v>
       </c>
-      <c r="B362" s="4">
+      <c r="B362" s="3">
         <v>61</v>
       </c>
       <c r="C362" t="s">
@@ -8028,10 +8022,10 @@
       </c>
     </row>
     <row r="363" spans="1:3">
-      <c r="A363" s="4">
+      <c r="A363" s="3">
         <v>4</v>
       </c>
-      <c r="B363" s="4">
+      <c r="B363" s="3">
         <v>62</v>
       </c>
       <c r="C363" t="s">
@@ -8039,10 +8033,10 @@
       </c>
     </row>
     <row r="364" spans="1:3">
-      <c r="A364" s="4">
+      <c r="A364" s="3">
         <v>4</v>
       </c>
-      <c r="B364" s="4">
+      <c r="B364" s="3">
         <v>63</v>
       </c>
       <c r="C364" t="s">
@@ -8050,10 +8044,10 @@
       </c>
     </row>
     <row r="365" spans="1:3">
-      <c r="A365" s="4">
+      <c r="A365" s="3">
         <v>4</v>
       </c>
-      <c r="B365" s="4">
+      <c r="B365" s="3">
         <v>64</v>
       </c>
       <c r="C365" t="s">
@@ -8061,10 +8055,10 @@
       </c>
     </row>
     <row r="366" spans="1:3">
-      <c r="A366" s="4">
+      <c r="A366" s="3">
         <v>4</v>
       </c>
-      <c r="B366" s="4">
+      <c r="B366" s="3">
         <v>65</v>
       </c>
       <c r="C366" t="s">
@@ -8072,10 +8066,10 @@
       </c>
     </row>
     <row r="367" spans="1:3">
-      <c r="A367" s="4">
+      <c r="A367" s="3">
         <v>4</v>
       </c>
-      <c r="B367" s="4">
+      <c r="B367" s="3">
         <v>66</v>
       </c>
       <c r="C367" t="s">
@@ -8083,10 +8077,10 @@
       </c>
     </row>
     <row r="368" spans="1:3">
-      <c r="A368" s="4">
+      <c r="A368" s="3">
         <v>4</v>
       </c>
-      <c r="B368" s="4">
+      <c r="B368" s="3">
         <v>67</v>
       </c>
       <c r="C368" t="s">
@@ -8094,10 +8088,10 @@
       </c>
     </row>
     <row r="369" spans="1:3">
-      <c r="A369" s="4">
+      <c r="A369" s="3">
         <v>4</v>
       </c>
-      <c r="B369" s="4">
+      <c r="B369" s="3">
         <v>68</v>
       </c>
       <c r="C369" t="s">
@@ -8105,10 +8099,10 @@
       </c>
     </row>
     <row r="370" spans="1:3">
-      <c r="A370" s="4">
+      <c r="A370" s="3">
         <v>4</v>
       </c>
-      <c r="B370" s="4">
+      <c r="B370" s="3">
         <v>69</v>
       </c>
       <c r="C370" t="s">
@@ -8116,10 +8110,10 @@
       </c>
     </row>
     <row r="371" spans="1:3">
-      <c r="A371" s="4">
+      <c r="A371" s="3">
         <v>4</v>
       </c>
-      <c r="B371" s="4">
+      <c r="B371" s="3">
         <v>70</v>
       </c>
       <c r="C371" t="s">
@@ -8127,10 +8121,10 @@
       </c>
     </row>
     <row r="372" spans="1:3">
-      <c r="A372" s="4">
+      <c r="A372" s="3">
         <v>4</v>
       </c>
-      <c r="B372" s="4">
+      <c r="B372" s="3">
         <v>71</v>
       </c>
       <c r="C372" t="s">
@@ -8138,10 +8132,10 @@
       </c>
     </row>
     <row r="373" spans="1:3">
-      <c r="A373" s="4">
+      <c r="A373" s="3">
         <v>4</v>
       </c>
-      <c r="B373" s="4">
+      <c r="B373" s="3">
         <v>72</v>
       </c>
       <c r="C373" t="s">
@@ -8149,10 +8143,10 @@
       </c>
     </row>
     <row r="374" spans="1:3">
-      <c r="A374" s="4">
+      <c r="A374" s="3">
         <v>4</v>
       </c>
-      <c r="B374" s="4">
+      <c r="B374" s="3">
         <v>73</v>
       </c>
       <c r="C374" t="s">
@@ -8160,10 +8154,10 @@
       </c>
     </row>
     <row r="375" spans="1:3">
-      <c r="A375" s="4">
+      <c r="A375" s="3">
         <v>4</v>
       </c>
-      <c r="B375" s="4">
+      <c r="B375" s="3">
         <v>74</v>
       </c>
       <c r="C375" t="s">
@@ -8171,10 +8165,10 @@
       </c>
     </row>
     <row r="376" spans="1:3">
-      <c r="A376" s="4">
+      <c r="A376" s="3">
         <v>4</v>
       </c>
-      <c r="B376" s="4">
+      <c r="B376" s="3">
         <v>75</v>
       </c>
       <c r="C376" t="s">
@@ -8182,10 +8176,10 @@
       </c>
     </row>
     <row r="377" spans="1:3">
-      <c r="A377" s="4">
+      <c r="A377" s="3">
         <v>4</v>
       </c>
-      <c r="B377" s="4">
+      <c r="B377" s="3">
         <v>76</v>
       </c>
       <c r="C377" t="s">
@@ -8193,10 +8187,10 @@
       </c>
     </row>
     <row r="378" spans="1:3">
-      <c r="A378" s="4">
+      <c r="A378" s="3">
         <v>4</v>
       </c>
-      <c r="B378" s="4">
+      <c r="B378" s="3">
         <v>77</v>
       </c>
       <c r="C378" t="s">
@@ -8204,10 +8198,10 @@
       </c>
     </row>
     <row r="379" spans="1:3">
-      <c r="A379" s="4">
+      <c r="A379" s="3">
         <v>4</v>
       </c>
-      <c r="B379" s="4">
+      <c r="B379" s="3">
         <v>78</v>
       </c>
       <c r="C379" t="s">
@@ -8215,10 +8209,10 @@
       </c>
     </row>
     <row r="380" spans="1:3">
-      <c r="A380" s="4">
+      <c r="A380" s="3">
         <v>4</v>
       </c>
-      <c r="B380" s="4">
+      <c r="B380" s="3">
         <v>79</v>
       </c>
       <c r="C380" t="s">
@@ -8226,10 +8220,10 @@
       </c>
     </row>
     <row r="381" spans="1:3">
-      <c r="A381" s="4">
+      <c r="A381" s="3">
         <v>4</v>
       </c>
-      <c r="B381" s="4">
+      <c r="B381" s="3">
         <v>80</v>
       </c>
       <c r="C381" t="s">
@@ -8237,10 +8231,10 @@
       </c>
     </row>
     <row r="382" spans="1:3">
-      <c r="A382" s="4">
+      <c r="A382" s="3">
         <v>4</v>
       </c>
-      <c r="B382" s="4">
+      <c r="B382" s="3">
         <v>81</v>
       </c>
       <c r="C382" t="s">
@@ -8248,10 +8242,10 @@
       </c>
     </row>
     <row r="383" spans="1:3">
-      <c r="A383" s="4">
+      <c r="A383" s="3">
         <v>4</v>
       </c>
-      <c r="B383" s="4">
+      <c r="B383" s="3">
         <v>82</v>
       </c>
       <c r="C383" t="s">
@@ -8259,10 +8253,10 @@
       </c>
     </row>
     <row r="384" spans="1:3">
-      <c r="A384" s="4">
+      <c r="A384" s="3">
         <v>4</v>
       </c>
-      <c r="B384" s="4">
+      <c r="B384" s="3">
         <v>83</v>
       </c>
       <c r="C384" t="s">
@@ -8270,10 +8264,10 @@
       </c>
     </row>
     <row r="385" spans="1:3">
-      <c r="A385" s="4">
+      <c r="A385" s="3">
         <v>4</v>
       </c>
-      <c r="B385" s="4">
+      <c r="B385" s="3">
         <v>84</v>
       </c>
       <c r="C385" t="s">
@@ -8281,10 +8275,10 @@
       </c>
     </row>
     <row r="386" spans="1:3">
-      <c r="A386" s="4">
+      <c r="A386" s="3">
         <v>4</v>
       </c>
-      <c r="B386" s="4">
+      <c r="B386" s="3">
         <v>85</v>
       </c>
       <c r="C386" t="s">
@@ -8292,10 +8286,10 @@
       </c>
     </row>
     <row r="387" spans="1:3">
-      <c r="A387" s="4">
+      <c r="A387" s="3">
         <v>4</v>
       </c>
-      <c r="B387" s="4">
+      <c r="B387" s="3">
         <v>86</v>
       </c>
       <c r="C387" t="s">
@@ -8303,10 +8297,10 @@
       </c>
     </row>
     <row r="388" spans="1:3">
-      <c r="A388" s="4">
+      <c r="A388" s="3">
         <v>4</v>
       </c>
-      <c r="B388" s="4">
+      <c r="B388" s="3">
         <v>87</v>
       </c>
       <c r="C388" t="s">
@@ -8314,10 +8308,10 @@
       </c>
     </row>
     <row r="389" spans="1:3">
-      <c r="A389" s="4">
+      <c r="A389" s="3">
         <v>4</v>
       </c>
-      <c r="B389" s="4">
+      <c r="B389" s="3">
         <v>88</v>
       </c>
       <c r="C389" t="s">
@@ -8325,10 +8319,10 @@
       </c>
     </row>
     <row r="390" spans="1:3">
-      <c r="A390" s="4">
+      <c r="A390" s="3">
         <v>4</v>
       </c>
-      <c r="B390" s="4">
+      <c r="B390" s="3">
         <v>89</v>
       </c>
       <c r="C390" t="s">
@@ -8336,10 +8330,10 @@
       </c>
     </row>
     <row r="391" spans="1:3">
-      <c r="A391" s="4">
+      <c r="A391" s="3">
         <v>4</v>
       </c>
-      <c r="B391" s="4">
+      <c r="B391" s="3">
         <v>90</v>
       </c>
       <c r="C391" t="s">
@@ -8347,10 +8341,10 @@
       </c>
     </row>
     <row r="392" spans="1:3">
-      <c r="A392" s="4">
+      <c r="A392" s="3">
         <v>4</v>
       </c>
-      <c r="B392" s="4">
+      <c r="B392" s="3">
         <v>91</v>
       </c>
       <c r="C392" t="s">
@@ -8358,10 +8352,10 @@
       </c>
     </row>
     <row r="393" spans="1:3">
-      <c r="A393" s="4">
+      <c r="A393" s="3">
         <v>4</v>
       </c>
-      <c r="B393" s="4">
+      <c r="B393" s="3">
         <v>92</v>
       </c>
       <c r="C393" t="s">
@@ -8369,10 +8363,10 @@
       </c>
     </row>
     <row r="394" spans="1:3">
-      <c r="A394" s="4">
+      <c r="A394" s="3">
         <v>4</v>
       </c>
-      <c r="B394" s="4">
+      <c r="B394" s="3">
         <v>93</v>
       </c>
       <c r="C394" t="s">
@@ -8380,10 +8374,10 @@
       </c>
     </row>
     <row r="395" spans="1:3">
-      <c r="A395" s="4">
+      <c r="A395" s="3">
         <v>4</v>
       </c>
-      <c r="B395" s="4">
+      <c r="B395" s="3">
         <v>94</v>
       </c>
       <c r="C395" t="s">
@@ -8391,10 +8385,10 @@
       </c>
     </row>
     <row r="396" spans="1:3">
-      <c r="A396" s="4">
+      <c r="A396" s="3">
         <v>4</v>
       </c>
-      <c r="B396" s="4">
+      <c r="B396" s="3">
         <v>95</v>
       </c>
       <c r="C396" t="s">
@@ -8402,10 +8396,10 @@
       </c>
     </row>
     <row r="397" spans="1:3">
-      <c r="A397" s="4">
+      <c r="A397" s="3">
         <v>4</v>
       </c>
-      <c r="B397" s="4">
+      <c r="B397" s="3">
         <v>96</v>
       </c>
       <c r="C397" t="s">
@@ -8413,10 +8407,10 @@
       </c>
     </row>
     <row r="398" spans="1:3">
-      <c r="A398" s="4">
+      <c r="A398" s="3">
         <v>4</v>
       </c>
-      <c r="B398" s="4">
+      <c r="B398" s="3">
         <v>97</v>
       </c>
       <c r="C398" t="s">
@@ -8424,10 +8418,10 @@
       </c>
     </row>
     <row r="399" spans="1:3">
-      <c r="A399" s="4">
+      <c r="A399" s="3">
         <v>4</v>
       </c>
-      <c r="B399" s="4">
+      <c r="B399" s="3">
         <v>98</v>
       </c>
       <c r="C399" t="s">
@@ -8435,10 +8429,10 @@
       </c>
     </row>
     <row r="400" spans="1:3">
-      <c r="A400" s="4">
+      <c r="A400" s="3">
         <v>4</v>
       </c>
-      <c r="B400" s="4">
+      <c r="B400" s="3">
         <v>99</v>
       </c>
       <c r="C400" t="s">
@@ -8446,10 +8440,10 @@
       </c>
     </row>
     <row r="401" spans="1:3">
-      <c r="A401" s="4">
+      <c r="A401" s="3">
         <v>4</v>
       </c>
-      <c r="B401" s="4">
+      <c r="B401" s="3">
         <v>100</v>
       </c>
       <c r="C401" t="s">
@@ -8457,10 +8451,10 @@
       </c>
     </row>
     <row r="402" spans="1:3">
-      <c r="A402" s="4">
+      <c r="A402" s="3">
         <v>5</v>
       </c>
-      <c r="B402" s="4">
+      <c r="B402" s="3">
         <v>1</v>
       </c>
       <c r="C402" t="s">
@@ -8468,10 +8462,10 @@
       </c>
     </row>
     <row r="403" spans="1:3">
-      <c r="A403" s="4">
+      <c r="A403" s="3">
         <v>5</v>
       </c>
-      <c r="B403" s="4">
+      <c r="B403" s="3">
         <v>2</v>
       </c>
       <c r="C403" t="s">
@@ -8479,10 +8473,10 @@
       </c>
     </row>
     <row r="404" spans="1:3">
-      <c r="A404" s="4">
+      <c r="A404" s="3">
         <v>5</v>
       </c>
-      <c r="B404" s="4">
+      <c r="B404" s="3">
         <v>3</v>
       </c>
       <c r="C404" t="s">
@@ -8490,10 +8484,10 @@
       </c>
     </row>
     <row r="405" spans="1:3">
-      <c r="A405" s="4">
+      <c r="A405" s="3">
         <v>5</v>
       </c>
-      <c r="B405" s="4">
+      <c r="B405" s="3">
         <v>4</v>
       </c>
       <c r="C405" t="s">
@@ -8501,10 +8495,10 @@
       </c>
     </row>
     <row r="406" spans="1:3">
-      <c r="A406" s="4">
+      <c r="A406" s="3">
         <v>5</v>
       </c>
-      <c r="B406" s="4">
+      <c r="B406" s="3">
         <v>5</v>
       </c>
       <c r="C406" t="s">
@@ -8512,10 +8506,10 @@
       </c>
     </row>
     <row r="407" spans="1:3">
-      <c r="A407" s="4">
+      <c r="A407" s="3">
         <v>5</v>
       </c>
-      <c r="B407" s="4">
+      <c r="B407" s="3">
         <v>6</v>
       </c>
       <c r="C407" t="s">
@@ -8523,10 +8517,10 @@
       </c>
     </row>
     <row r="408" spans="1:3">
-      <c r="A408" s="4">
+      <c r="A408" s="3">
         <v>5</v>
       </c>
-      <c r="B408" s="4">
+      <c r="B408" s="3">
         <v>7</v>
       </c>
       <c r="C408" t="s">
@@ -8534,10 +8528,10 @@
       </c>
     </row>
     <row r="409" spans="1:3">
-      <c r="A409" s="4">
+      <c r="A409" s="3">
         <v>5</v>
       </c>
-      <c r="B409" s="4">
+      <c r="B409" s="3">
         <v>8</v>
       </c>
       <c r="C409" t="s">
@@ -8545,10 +8539,10 @@
       </c>
     </row>
     <row r="410" spans="1:3">
-      <c r="A410" s="4">
+      <c r="A410" s="3">
         <v>5</v>
       </c>
-      <c r="B410" s="4">
+      <c r="B410" s="3">
         <v>9</v>
       </c>
       <c r="C410" t="s">
@@ -8556,10 +8550,10 @@
       </c>
     </row>
     <row r="411" spans="1:3">
-      <c r="A411" s="4">
+      <c r="A411" s="3">
         <v>5</v>
       </c>
-      <c r="B411" s="4">
+      <c r="B411" s="3">
         <v>10</v>
       </c>
       <c r="C411" t="s">
@@ -8567,10 +8561,10 @@
       </c>
     </row>
     <row r="412" spans="1:3">
-      <c r="A412" s="4">
+      <c r="A412" s="3">
         <v>5</v>
       </c>
-      <c r="B412" s="4">
+      <c r="B412" s="3">
         <v>11</v>
       </c>
       <c r="C412" t="s">
@@ -8578,10 +8572,10 @@
       </c>
     </row>
     <row r="413" spans="1:3">
-      <c r="A413" s="4">
+      <c r="A413" s="3">
         <v>5</v>
       </c>
-      <c r="B413" s="4">
+      <c r="B413" s="3">
         <v>12</v>
       </c>
       <c r="C413" t="s">
@@ -8589,10 +8583,10 @@
       </c>
     </row>
     <row r="414" spans="1:3">
-      <c r="A414" s="4">
+      <c r="A414" s="3">
         <v>5</v>
       </c>
-      <c r="B414" s="4">
+      <c r="B414" s="3">
         <v>13</v>
       </c>
       <c r="C414" t="s">
@@ -8600,10 +8594,10 @@
       </c>
     </row>
     <row r="415" spans="1:3">
-      <c r="A415" s="4">
+      <c r="A415" s="3">
         <v>5</v>
       </c>
-      <c r="B415" s="4">
+      <c r="B415" s="3">
         <v>14</v>
       </c>
       <c r="C415" t="s">
@@ -8611,10 +8605,10 @@
       </c>
     </row>
     <row r="416" spans="1:3">
-      <c r="A416" s="4">
+      <c r="A416" s="3">
         <v>5</v>
       </c>
-      <c r="B416" s="4">
+      <c r="B416" s="3">
         <v>15</v>
       </c>
       <c r="C416" t="s">
@@ -8622,10 +8616,10 @@
       </c>
     </row>
     <row r="417" spans="1:3">
-      <c r="A417" s="4">
+      <c r="A417" s="3">
         <v>5</v>
       </c>
-      <c r="B417" s="4">
+      <c r="B417" s="3">
         <v>16</v>
       </c>
       <c r="C417" t="s">
@@ -8633,10 +8627,10 @@
       </c>
     </row>
     <row r="418" spans="1:3">
-      <c r="A418" s="4">
+      <c r="A418" s="3">
         <v>5</v>
       </c>
-      <c r="B418" s="4">
+      <c r="B418" s="3">
         <v>17</v>
       </c>
       <c r="C418" t="s">
@@ -8644,10 +8638,10 @@
       </c>
     </row>
     <row r="419" spans="1:3">
-      <c r="A419" s="4">
+      <c r="A419" s="3">
         <v>5</v>
       </c>
-      <c r="B419" s="4">
+      <c r="B419" s="3">
         <v>18</v>
       </c>
       <c r="C419" t="s">
@@ -8655,10 +8649,10 @@
       </c>
     </row>
     <row r="420" spans="1:3">
-      <c r="A420" s="4">
+      <c r="A420" s="3">
         <v>5</v>
       </c>
-      <c r="B420" s="4">
+      <c r="B420" s="3">
         <v>19</v>
       </c>
       <c r="C420" t="s">
@@ -8666,10 +8660,10 @@
       </c>
     </row>
     <row r="421" spans="1:3">
-      <c r="A421" s="4">
+      <c r="A421" s="3">
         <v>5</v>
       </c>
-      <c r="B421" s="4">
+      <c r="B421" s="3">
         <v>20</v>
       </c>
       <c r="C421" t="s">
@@ -8677,10 +8671,10 @@
       </c>
     </row>
     <row r="422" spans="1:3">
-      <c r="A422" s="4">
+      <c r="A422" s="3">
         <v>5</v>
       </c>
-      <c r="B422" s="4">
+      <c r="B422" s="3">
         <v>21</v>
       </c>
       <c r="C422" t="s">
@@ -8688,10 +8682,10 @@
       </c>
     </row>
     <row r="423" spans="1:3">
-      <c r="A423" s="4">
+      <c r="A423" s="3">
         <v>5</v>
       </c>
-      <c r="B423" s="4">
+      <c r="B423" s="3">
         <v>22</v>
       </c>
       <c r="C423" t="s">
@@ -8699,10 +8693,10 @@
       </c>
     </row>
     <row r="424" spans="1:3">
-      <c r="A424" s="4">
+      <c r="A424" s="3">
         <v>5</v>
       </c>
-      <c r="B424" s="4">
+      <c r="B424" s="3">
         <v>23</v>
       </c>
       <c r="C424" t="s">
@@ -8710,10 +8704,10 @@
       </c>
     </row>
     <row r="425" spans="1:3">
-      <c r="A425" s="4">
+      <c r="A425" s="3">
         <v>5</v>
       </c>
-      <c r="B425" s="4">
+      <c r="B425" s="3">
         <v>24</v>
       </c>
       <c r="C425" t="s">
@@ -8721,10 +8715,10 @@
       </c>
     </row>
     <row r="426" spans="1:3">
-      <c r="A426" s="4">
+      <c r="A426" s="3">
         <v>5</v>
       </c>
-      <c r="B426" s="4">
+      <c r="B426" s="3">
         <v>25</v>
       </c>
       <c r="C426" t="s">
@@ -8732,10 +8726,10 @@
       </c>
     </row>
     <row r="427" spans="1:3">
-      <c r="A427" s="4">
+      <c r="A427" s="3">
         <v>5</v>
       </c>
-      <c r="B427" s="4">
+      <c r="B427" s="3">
         <v>26</v>
       </c>
       <c r="C427" t="s">
@@ -8743,10 +8737,10 @@
       </c>
     </row>
     <row r="428" spans="1:3">
-      <c r="A428" s="4">
+      <c r="A428" s="3">
         <v>5</v>
       </c>
-      <c r="B428" s="4">
+      <c r="B428" s="3">
         <v>27</v>
       </c>
       <c r="C428" t="s">
@@ -8754,10 +8748,10 @@
       </c>
     </row>
     <row r="429" spans="1:3">
-      <c r="A429" s="4">
+      <c r="A429" s="3">
         <v>5</v>
       </c>
-      <c r="B429" s="4">
+      <c r="B429" s="3">
         <v>28</v>
       </c>
       <c r="C429" t="s">
@@ -8765,10 +8759,10 @@
       </c>
     </row>
     <row r="430" spans="1:3">
-      <c r="A430" s="4">
+      <c r="A430" s="3">
         <v>5</v>
       </c>
-      <c r="B430" s="4">
+      <c r="B430" s="3">
         <v>29</v>
       </c>
       <c r="C430" t="s">
@@ -8776,10 +8770,10 @@
       </c>
     </row>
     <row r="431" spans="1:3">
-      <c r="A431" s="4">
+      <c r="A431" s="3">
         <v>5</v>
       </c>
-      <c r="B431" s="4">
+      <c r="B431" s="3">
         <v>30</v>
       </c>
       <c r="C431" t="s">
@@ -8787,10 +8781,10 @@
       </c>
     </row>
     <row r="432" spans="1:3">
-      <c r="A432" s="4">
+      <c r="A432" s="3">
         <v>5</v>
       </c>
-      <c r="B432" s="4">
+      <c r="B432" s="3">
         <v>31</v>
       </c>
       <c r="C432" t="s">
@@ -8798,10 +8792,10 @@
       </c>
     </row>
     <row r="433" spans="1:3">
-      <c r="A433" s="4">
+      <c r="A433" s="3">
         <v>5</v>
       </c>
-      <c r="B433" s="4">
+      <c r="B433" s="3">
         <v>32</v>
       </c>
       <c r="C433" t="s">
@@ -8809,10 +8803,10 @@
       </c>
     </row>
     <row r="434" spans="1:3">
-      <c r="A434" s="4">
+      <c r="A434" s="3">
         <v>5</v>
       </c>
-      <c r="B434" s="4">
+      <c r="B434" s="3">
         <v>33</v>
       </c>
       <c r="C434" t="s">
@@ -8820,10 +8814,10 @@
       </c>
     </row>
     <row r="435" spans="1:3">
-      <c r="A435" s="4">
+      <c r="A435" s="3">
         <v>5</v>
       </c>
-      <c r="B435" s="4">
+      <c r="B435" s="3">
         <v>34</v>
       </c>
       <c r="C435" t="s">
@@ -8831,10 +8825,10 @@
       </c>
     </row>
     <row r="436" spans="1:3">
-      <c r="A436" s="4">
+      <c r="A436" s="3">
         <v>5</v>
       </c>
-      <c r="B436" s="4">
+      <c r="B436" s="3">
         <v>35</v>
       </c>
       <c r="C436" t="s">
@@ -8842,10 +8836,10 @@
       </c>
     </row>
     <row r="437" spans="1:3">
-      <c r="A437" s="4">
+      <c r="A437" s="3">
         <v>5</v>
       </c>
-      <c r="B437" s="4">
+      <c r="B437" s="3">
         <v>36</v>
       </c>
       <c r="C437" t="s">
@@ -8853,10 +8847,10 @@
       </c>
     </row>
     <row r="438" spans="1:3">
-      <c r="A438" s="4">
+      <c r="A438" s="3">
         <v>5</v>
       </c>
-      <c r="B438" s="4">
+      <c r="B438" s="3">
         <v>37</v>
       </c>
       <c r="C438" t="s">
@@ -8864,10 +8858,10 @@
       </c>
     </row>
     <row r="439" spans="1:3">
-      <c r="A439" s="4">
+      <c r="A439" s="3">
         <v>5</v>
       </c>
-      <c r="B439" s="4">
+      <c r="B439" s="3">
         <v>38</v>
       </c>
       <c r="C439" t="s">
@@ -8875,10 +8869,10 @@
       </c>
     </row>
     <row r="440" spans="1:3">
-      <c r="A440" s="4">
+      <c r="A440" s="3">
         <v>5</v>
       </c>
-      <c r="B440" s="4">
+      <c r="B440" s="3">
         <v>39</v>
       </c>
       <c r="C440" t="s">
@@ -8886,10 +8880,10 @@
       </c>
     </row>
     <row r="441" spans="1:3">
-      <c r="A441" s="4">
+      <c r="A441" s="3">
         <v>5</v>
       </c>
-      <c r="B441" s="4">
+      <c r="B441" s="3">
         <v>40</v>
       </c>
       <c r="C441" t="s">
@@ -8897,10 +8891,10 @@
       </c>
     </row>
     <row r="442" spans="1:3">
-      <c r="A442" s="4">
+      <c r="A442" s="3">
         <v>5</v>
       </c>
-      <c r="B442" s="4">
+      <c r="B442" s="3">
         <v>41</v>
       </c>
       <c r="C442" t="s">
@@ -8908,10 +8902,10 @@
       </c>
     </row>
     <row r="443" spans="1:3">
-      <c r="A443" s="4">
+      <c r="A443" s="3">
         <v>5</v>
       </c>
-      <c r="B443" s="4">
+      <c r="B443" s="3">
         <v>42</v>
       </c>
       <c r="C443" t="s">
@@ -8919,10 +8913,10 @@
       </c>
     </row>
     <row r="444" spans="1:3">
-      <c r="A444" s="4">
+      <c r="A444" s="3">
         <v>5</v>
       </c>
-      <c r="B444" s="4">
+      <c r="B444" s="3">
         <v>43</v>
       </c>
       <c r="C444" t="s">
@@ -8930,10 +8924,10 @@
       </c>
     </row>
     <row r="445" spans="1:3">
-      <c r="A445" s="4">
+      <c r="A445" s="3">
         <v>5</v>
       </c>
-      <c r="B445" s="4">
+      <c r="B445" s="3">
         <v>44</v>
       </c>
       <c r="C445" t="s">
@@ -8941,10 +8935,10 @@
       </c>
     </row>
     <row r="446" spans="1:3">
-      <c r="A446" s="4">
+      <c r="A446" s="3">
         <v>5</v>
       </c>
-      <c r="B446" s="4">
+      <c r="B446" s="3">
         <v>45</v>
       </c>
       <c r="C446" t="s">
@@ -8952,10 +8946,10 @@
       </c>
     </row>
     <row r="447" spans="1:3">
-      <c r="A447" s="4">
+      <c r="A447" s="3">
         <v>5</v>
       </c>
-      <c r="B447" s="4">
+      <c r="B447" s="3">
         <v>46</v>
       </c>
       <c r="C447" t="s">
@@ -8963,10 +8957,10 @@
       </c>
     </row>
     <row r="448" spans="1:3">
-      <c r="A448" s="4">
+      <c r="A448" s="3">
         <v>5</v>
       </c>
-      <c r="B448" s="4">
+      <c r="B448" s="3">
         <v>47</v>
       </c>
       <c r="C448" t="s">
@@ -8974,10 +8968,10 @@
       </c>
     </row>
     <row r="449" spans="1:3">
-      <c r="A449" s="4">
+      <c r="A449" s="3">
         <v>5</v>
       </c>
-      <c r="B449" s="4">
+      <c r="B449" s="3">
         <v>48</v>
       </c>
       <c r="C449" t="s">
@@ -8985,10 +8979,10 @@
       </c>
     </row>
     <row r="450" spans="1:3">
-      <c r="A450" s="4">
+      <c r="A450" s="3">
         <v>5</v>
       </c>
-      <c r="B450" s="4">
+      <c r="B450" s="3">
         <v>49</v>
       </c>
       <c r="C450" t="s">
@@ -8996,10 +8990,10 @@
       </c>
     </row>
     <row r="451" spans="1:3">
-      <c r="A451" s="4">
+      <c r="A451" s="3">
         <v>5</v>
       </c>
-      <c r="B451" s="4">
+      <c r="B451" s="3">
         <v>50</v>
       </c>
       <c r="C451" t="s">
@@ -9007,10 +9001,10 @@
       </c>
     </row>
     <row r="452" spans="1:3">
-      <c r="A452" s="4">
+      <c r="A452" s="3">
         <v>5</v>
       </c>
-      <c r="B452" s="4">
+      <c r="B452" s="3">
         <v>51</v>
       </c>
       <c r="C452" t="s">
@@ -9018,10 +9012,10 @@
       </c>
     </row>
     <row r="453" spans="1:3">
-      <c r="A453" s="4">
+      <c r="A453" s="3">
         <v>5</v>
       </c>
-      <c r="B453" s="4">
+      <c r="B453" s="3">
         <v>52</v>
       </c>
       <c r="C453" t="s">
@@ -9029,10 +9023,10 @@
       </c>
     </row>
     <row r="454" spans="1:3">
-      <c r="A454" s="4">
+      <c r="A454" s="3">
         <v>5</v>
       </c>
-      <c r="B454" s="4">
+      <c r="B454" s="3">
         <v>53</v>
       </c>
       <c r="C454" t="s">
@@ -9040,10 +9034,10 @@
       </c>
     </row>
     <row r="455" spans="1:3">
-      <c r="A455" s="4">
+      <c r="A455" s="3">
         <v>5</v>
       </c>
-      <c r="B455" s="4">
+      <c r="B455" s="3">
         <v>54</v>
       </c>
       <c r="C455" t="s">
@@ -9051,10 +9045,10 @@
       </c>
     </row>
     <row r="456" spans="1:3">
-      <c r="A456" s="4">
+      <c r="A456" s="3">
         <v>5</v>
       </c>
-      <c r="B456" s="4">
+      <c r="B456" s="3">
         <v>55</v>
       </c>
       <c r="C456" t="s">
@@ -9062,10 +9056,10 @@
       </c>
     </row>
     <row r="457" spans="1:3">
-      <c r="A457" s="4">
+      <c r="A457" s="3">
         <v>5</v>
       </c>
-      <c r="B457" s="4">
+      <c r="B457" s="3">
         <v>56</v>
       </c>
       <c r="C457" t="s">
@@ -9073,10 +9067,10 @@
       </c>
     </row>
     <row r="458" spans="1:3">
-      <c r="A458" s="4">
+      <c r="A458" s="3">
         <v>5</v>
       </c>
-      <c r="B458" s="4">
+      <c r="B458" s="3">
         <v>57</v>
       </c>
       <c r="C458" t="s">
@@ -9084,10 +9078,10 @@
       </c>
     </row>
     <row r="459" spans="1:3">
-      <c r="A459" s="4">
+      <c r="A459" s="3">
         <v>5</v>
       </c>
-      <c r="B459" s="4">
+      <c r="B459" s="3">
         <v>58</v>
       </c>
       <c r="C459" t="s">
@@ -9095,10 +9089,10 @@
       </c>
     </row>
     <row r="460" spans="1:3">
-      <c r="A460" s="4">
+      <c r="A460" s="3">
         <v>5</v>
       </c>
-      <c r="B460" s="4">
+      <c r="B460" s="3">
         <v>59</v>
       </c>
       <c r="C460" t="s">
@@ -9106,10 +9100,10 @@
       </c>
     </row>
     <row r="461" spans="1:3">
-      <c r="A461" s="4">
+      <c r="A461" s="3">
         <v>5</v>
       </c>
-      <c r="B461" s="4">
+      <c r="B461" s="3">
         <v>60</v>
       </c>
       <c r="C461" t="s">
@@ -9117,10 +9111,10 @@
       </c>
     </row>
     <row r="462" spans="1:3">
-      <c r="A462" s="4">
+      <c r="A462" s="3">
         <v>5</v>
       </c>
-      <c r="B462" s="4">
+      <c r="B462" s="3">
         <v>61</v>
       </c>
       <c r="C462" t="s">
@@ -9128,10 +9122,10 @@
       </c>
     </row>
     <row r="463" spans="1:3">
-      <c r="A463" s="4">
+      <c r="A463" s="3">
         <v>5</v>
       </c>
-      <c r="B463" s="4">
+      <c r="B463" s="3">
         <v>62</v>
       </c>
       <c r="C463" t="s">
@@ -9139,10 +9133,10 @@
       </c>
     </row>
     <row r="464" spans="1:3">
-      <c r="A464" s="4">
+      <c r="A464" s="3">
         <v>5</v>
       </c>
-      <c r="B464" s="4">
+      <c r="B464" s="3">
         <v>63</v>
       </c>
       <c r="C464" t="s">
@@ -9150,10 +9144,10 @@
       </c>
     </row>
     <row r="465" spans="1:3">
-      <c r="A465" s="4">
+      <c r="A465" s="3">
         <v>5</v>
       </c>
-      <c r="B465" s="4">
+      <c r="B465" s="3">
         <v>64</v>
       </c>
       <c r="C465" t="s">
@@ -9161,10 +9155,10 @@
       </c>
     </row>
     <row r="466" spans="1:3">
-      <c r="A466" s="4">
+      <c r="A466" s="3">
         <v>5</v>
       </c>
-      <c r="B466" s="4">
+      <c r="B466" s="3">
         <v>65</v>
       </c>
       <c r="C466" t="s">
@@ -9172,10 +9166,10 @@
       </c>
     </row>
     <row r="467" spans="1:3">
-      <c r="A467" s="4">
+      <c r="A467" s="3">
         <v>5</v>
       </c>
-      <c r="B467" s="4">
+      <c r="B467" s="3">
         <v>66</v>
       </c>
       <c r="C467" t="s">
@@ -9183,10 +9177,10 @@
       </c>
     </row>
     <row r="468" spans="1:3">
-      <c r="A468" s="4">
+      <c r="A468" s="3">
         <v>5</v>
       </c>
-      <c r="B468" s="4">
+      <c r="B468" s="3">
         <v>67</v>
       </c>
       <c r="C468" t="s">
@@ -9194,10 +9188,10 @@
       </c>
     </row>
     <row r="469" spans="1:3">
-      <c r="A469" s="4">
+      <c r="A469" s="3">
         <v>5</v>
       </c>
-      <c r="B469" s="4">
+      <c r="B469" s="3">
         <v>68</v>
       </c>
       <c r="C469" t="s">
@@ -9205,10 +9199,10 @@
       </c>
     </row>
     <row r="470" spans="1:3">
-      <c r="A470" s="4">
+      <c r="A470" s="3">
         <v>5</v>
       </c>
-      <c r="B470" s="4">
+      <c r="B470" s="3">
         <v>69</v>
       </c>
       <c r="C470" t="s">
@@ -9216,10 +9210,10 @@
       </c>
     </row>
     <row r="471" spans="1:3">
-      <c r="A471" s="4">
+      <c r="A471" s="3">
         <v>5</v>
       </c>
-      <c r="B471" s="4">
+      <c r="B471" s="3">
         <v>70</v>
       </c>
       <c r="C471" t="s">
@@ -9227,10 +9221,10 @@
       </c>
     </row>
     <row r="472" spans="1:3">
-      <c r="A472" s="4">
+      <c r="A472" s="3">
         <v>5</v>
       </c>
-      <c r="B472" s="4">
+      <c r="B472" s="3">
         <v>71</v>
       </c>
       <c r="C472" t="s">
@@ -9238,10 +9232,10 @@
       </c>
     </row>
     <row r="473" spans="1:3">
-      <c r="A473" s="4">
+      <c r="A473" s="3">
         <v>5</v>
       </c>
-      <c r="B473" s="4">
+      <c r="B473" s="3">
         <v>72</v>
       </c>
       <c r="C473" t="s">
@@ -9249,10 +9243,10 @@
       </c>
     </row>
     <row r="474" spans="1:3">
-      <c r="A474" s="4">
+      <c r="A474" s="3">
         <v>5</v>
       </c>
-      <c r="B474" s="4">
+      <c r="B474" s="3">
         <v>73</v>
       </c>
       <c r="C474" t="s">
@@ -9260,10 +9254,10 @@
       </c>
     </row>
     <row r="475" spans="1:3">
-      <c r="A475" s="4">
+      <c r="A475" s="3">
         <v>5</v>
       </c>
-      <c r="B475" s="4">
+      <c r="B475" s="3">
         <v>74</v>
       </c>
       <c r="C475" t="s">
@@ -9271,10 +9265,10 @@
       </c>
     </row>
     <row r="476" spans="1:3">
-      <c r="A476" s="4">
+      <c r="A476" s="3">
         <v>5</v>
       </c>
-      <c r="B476" s="4">
+      <c r="B476" s="3">
         <v>75</v>
       </c>
       <c r="C476" t="s">
@@ -9282,10 +9276,10 @@
       </c>
     </row>
     <row r="477" spans="1:3">
-      <c r="A477" s="4">
+      <c r="A477" s="3">
         <v>5</v>
       </c>
-      <c r="B477" s="4">
+      <c r="B477" s="3">
         <v>76</v>
       </c>
       <c r="C477" t="s">
@@ -9293,10 +9287,10 @@
       </c>
     </row>
     <row r="478" spans="1:3">
-      <c r="A478" s="4">
+      <c r="A478" s="3">
         <v>5</v>
       </c>
-      <c r="B478" s="4">
+      <c r="B478" s="3">
         <v>77</v>
       </c>
       <c r="C478" t="s">
@@ -9304,10 +9298,10 @@
       </c>
     </row>
     <row r="479" spans="1:3">
-      <c r="A479" s="4">
+      <c r="A479" s="3">
         <v>5</v>
       </c>
-      <c r="B479" s="4">
+      <c r="B479" s="3">
         <v>78</v>
       </c>
       <c r="C479" t="s">
@@ -9315,10 +9309,10 @@
       </c>
     </row>
     <row r="480" spans="1:3">
-      <c r="A480" s="4">
+      <c r="A480" s="3">
         <v>5</v>
       </c>
-      <c r="B480" s="4">
+      <c r="B480" s="3">
         <v>79</v>
       </c>
       <c r="C480" t="s">
@@ -9326,10 +9320,10 @@
       </c>
     </row>
     <row r="481" spans="1:3">
-      <c r="A481" s="4">
+      <c r="A481" s="3">
         <v>5</v>
       </c>
-      <c r="B481" s="4">
+      <c r="B481" s="3">
         <v>80</v>
       </c>
       <c r="C481" t="s">
@@ -9337,10 +9331,10 @@
       </c>
     </row>
     <row r="482" spans="1:3">
-      <c r="A482" s="4">
+      <c r="A482" s="3">
         <v>5</v>
       </c>
-      <c r="B482" s="4">
+      <c r="B482" s="3">
         <v>81</v>
       </c>
       <c r="C482" t="s">
@@ -9348,10 +9342,10 @@
       </c>
     </row>
     <row r="483" spans="1:3">
-      <c r="A483" s="4">
+      <c r="A483" s="3">
         <v>5</v>
       </c>
-      <c r="B483" s="4">
+      <c r="B483" s="3">
         <v>82</v>
       </c>
       <c r="C483" t="s">
@@ -9359,10 +9353,10 @@
       </c>
     </row>
     <row r="484" spans="1:3">
-      <c r="A484" s="4">
+      <c r="A484" s="3">
         <v>5</v>
       </c>
-      <c r="B484" s="4">
+      <c r="B484" s="3">
         <v>83</v>
       </c>
       <c r="C484" t="s">
@@ -9370,10 +9364,10 @@
       </c>
     </row>
     <row r="485" spans="1:3">
-      <c r="A485" s="4">
+      <c r="A485" s="3">
         <v>5</v>
       </c>
-      <c r="B485" s="4">
+      <c r="B485" s="3">
         <v>84</v>
       </c>
       <c r="C485" t="s">
@@ -9381,10 +9375,10 @@
       </c>
     </row>
     <row r="486" spans="1:3">
-      <c r="A486" s="4">
+      <c r="A486" s="3">
         <v>5</v>
       </c>
-      <c r="B486" s="4">
+      <c r="B486" s="3">
         <v>85</v>
       </c>
       <c r="C486" t="s">
@@ -9392,10 +9386,10 @@
       </c>
     </row>
     <row r="487" spans="1:3">
-      <c r="A487" s="4">
+      <c r="A487" s="3">
         <v>5</v>
       </c>
-      <c r="B487" s="4">
+      <c r="B487" s="3">
         <v>86</v>
       </c>
       <c r="C487" t="s">
@@ -9403,10 +9397,10 @@
       </c>
     </row>
     <row r="488" spans="1:3">
-      <c r="A488" s="4">
+      <c r="A488" s="3">
         <v>5</v>
       </c>
-      <c r="B488" s="4">
+      <c r="B488" s="3">
         <v>87</v>
       </c>
       <c r="C488" t="s">
@@ -9414,10 +9408,10 @@
       </c>
     </row>
     <row r="489" spans="1:3">
-      <c r="A489" s="4">
+      <c r="A489" s="3">
         <v>5</v>
       </c>
-      <c r="B489" s="4">
+      <c r="B489" s="3">
         <v>88</v>
       </c>
       <c r="C489" t="s">
@@ -9425,10 +9419,10 @@
       </c>
     </row>
     <row r="490" spans="1:3">
-      <c r="A490" s="4">
+      <c r="A490" s="3">
         <v>5</v>
       </c>
-      <c r="B490" s="4">
+      <c r="B490" s="3">
         <v>89</v>
       </c>
       <c r="C490" t="s">
@@ -9436,10 +9430,10 @@
       </c>
     </row>
     <row r="491" spans="1:3">
-      <c r="A491" s="4">
+      <c r="A491" s="3">
         <v>5</v>
       </c>
-      <c r="B491" s="4">
+      <c r="B491" s="3">
         <v>90</v>
       </c>
       <c r="C491" t="s">
@@ -9447,10 +9441,10 @@
       </c>
     </row>
     <row r="492" spans="1:3">
-      <c r="A492" s="4">
+      <c r="A492" s="3">
         <v>5</v>
       </c>
-      <c r="B492" s="4">
+      <c r="B492" s="3">
         <v>91</v>
       </c>
       <c r="C492" t="s">
@@ -9458,10 +9452,10 @@
       </c>
     </row>
     <row r="493" spans="1:3">
-      <c r="A493" s="4">
+      <c r="A493" s="3">
         <v>5</v>
       </c>
-      <c r="B493" s="4">
+      <c r="B493" s="3">
         <v>92</v>
       </c>
       <c r="C493" t="s">
@@ -9469,10 +9463,10 @@
       </c>
     </row>
     <row r="494" spans="1:3">
-      <c r="A494" s="4">
+      <c r="A494" s="3">
         <v>5</v>
       </c>
-      <c r="B494" s="4">
+      <c r="B494" s="3">
         <v>93</v>
       </c>
       <c r="C494" t="s">
@@ -9480,10 +9474,10 @@
       </c>
     </row>
     <row r="495" spans="1:3">
-      <c r="A495" s="4">
+      <c r="A495" s="3">
         <v>5</v>
       </c>
-      <c r="B495" s="4">
+      <c r="B495" s="3">
         <v>94</v>
       </c>
       <c r="C495" t="s">
@@ -9491,10 +9485,10 @@
       </c>
     </row>
     <row r="496" spans="1:3">
-      <c r="A496" s="4">
+      <c r="A496" s="3">
         <v>5</v>
       </c>
-      <c r="B496" s="4">
+      <c r="B496" s="3">
         <v>95</v>
       </c>
       <c r="C496" t="s">
@@ -9502,10 +9496,10 @@
       </c>
     </row>
     <row r="497" spans="1:3">
-      <c r="A497" s="4">
+      <c r="A497" s="3">
         <v>5</v>
       </c>
-      <c r="B497" s="4">
+      <c r="B497" s="3">
         <v>96</v>
       </c>
       <c r="C497" t="s">
@@ -9513,10 +9507,10 @@
       </c>
     </row>
     <row r="498" spans="1:3">
-      <c r="A498" s="4">
+      <c r="A498" s="3">
         <v>5</v>
       </c>
-      <c r="B498" s="4">
+      <c r="B498" s="3">
         <v>97</v>
       </c>
       <c r="C498" t="s">
@@ -9524,10 +9518,10 @@
       </c>
     </row>
     <row r="499" spans="1:3">
-      <c r="A499" s="4">
+      <c r="A499" s="3">
         <v>5</v>
       </c>
-      <c r="B499" s="4">
+      <c r="B499" s="3">
         <v>98</v>
       </c>
       <c r="C499" t="s">
@@ -9535,10 +9529,10 @@
       </c>
     </row>
     <row r="500" spans="1:3">
-      <c r="A500" s="4">
+      <c r="A500" s="3">
         <v>5</v>
       </c>
-      <c r="B500" s="4">
+      <c r="B500" s="3">
         <v>99</v>
       </c>
       <c r="C500" t="s">
@@ -9546,10 +9540,10 @@
       </c>
     </row>
     <row r="501" spans="1:3">
-      <c r="A501" s="4">
+      <c r="A501" s="3">
         <v>5</v>
       </c>
-      <c r="B501" s="4">
+      <c r="B501" s="3">
         <v>100</v>
       </c>
       <c r="C501" t="s">
@@ -9557,230 +9551,230 @@
       </c>
     </row>
     <row r="502" spans="1:3">
-      <c r="A502" s="4">
+      <c r="A502" s="3">
         <v>6</v>
       </c>
-      <c r="B502" s="4">
+      <c r="B502" s="3">
         <v>1</v>
       </c>
-      <c r="C502" s="5" t="s">
+      <c r="C502" s="4" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="503" spans="1:3">
-      <c r="A503" s="4">
+      <c r="A503" s="3">
         <v>6</v>
       </c>
-      <c r="B503" s="4">
+      <c r="B503" s="3">
         <v>2</v>
       </c>
-      <c r="C503" s="5" t="s">
+      <c r="C503" s="4" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="504" spans="1:3">
-      <c r="A504" s="4">
+      <c r="A504" s="3">
         <v>6</v>
       </c>
-      <c r="B504" s="4">
+      <c r="B504" s="3">
         <v>3</v>
       </c>
-      <c r="C504" s="5" t="s">
+      <c r="C504" s="4" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="505" spans="1:3">
-      <c r="A505" s="4">
+      <c r="A505" s="3">
         <v>6</v>
       </c>
-      <c r="B505" s="4">
+      <c r="B505" s="3">
         <v>4</v>
       </c>
-      <c r="C505" s="5" t="s">
+      <c r="C505" s="4" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="506" spans="1:3">
-      <c r="A506" s="4">
+      <c r="A506" s="3">
         <v>6</v>
       </c>
-      <c r="B506" s="4">
+      <c r="B506" s="3">
         <v>5</v>
       </c>
-      <c r="C506" s="5" t="s">
+      <c r="C506" s="4" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="507" spans="1:3">
-      <c r="A507" s="4">
+      <c r="A507" s="3">
         <v>6</v>
       </c>
-      <c r="B507" s="4">
+      <c r="B507" s="3">
         <v>6</v>
       </c>
-      <c r="C507" s="5" t="s">
+      <c r="C507" s="4" t="s">
         <v>507</v>
       </c>
     </row>
     <row r="508" spans="1:3">
-      <c r="A508" s="4">
+      <c r="A508" s="3">
         <v>6</v>
       </c>
-      <c r="B508" s="4">
+      <c r="B508" s="3">
         <v>7</v>
       </c>
-      <c r="C508" s="5" t="s">
+      <c r="C508" s="4" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="509" spans="1:3">
-      <c r="A509" s="4">
+      <c r="A509" s="3">
         <v>6</v>
       </c>
-      <c r="B509" s="4">
+      <c r="B509" s="3">
         <v>8</v>
       </c>
-      <c r="C509" s="5" t="s">
+      <c r="C509" s="4" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="510" spans="1:3">
-      <c r="A510" s="4">
+      <c r="A510" s="3">
         <v>6</v>
       </c>
-      <c r="B510" s="4">
+      <c r="B510" s="3">
         <v>9</v>
       </c>
-      <c r="C510" s="5" t="s">
+      <c r="C510" s="4" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="511" spans="1:3">
-      <c r="A511" s="4">
+      <c r="A511" s="3">
         <v>6</v>
       </c>
-      <c r="B511" s="4">
+      <c r="B511" s="3">
         <v>10</v>
       </c>
-      <c r="C511" s="5" t="s">
+      <c r="C511" s="4" t="s">
         <v>511</v>
       </c>
     </row>
     <row r="512" spans="1:3">
-      <c r="A512" s="4">
+      <c r="A512" s="3">
         <v>6</v>
       </c>
-      <c r="B512" s="4">
+      <c r="B512" s="3">
         <v>11</v>
       </c>
-      <c r="C512" s="5" t="s">
+      <c r="C512" s="4" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="513" spans="1:3">
-      <c r="A513" s="4">
+      <c r="A513" s="3">
         <v>6</v>
       </c>
-      <c r="B513" s="4">
+      <c r="B513" s="3">
         <v>12</v>
       </c>
-      <c r="C513" s="5" t="s">
+      <c r="C513" s="4" t="s">
         <v>513</v>
       </c>
     </row>
     <row r="514" spans="1:3">
-      <c r="A514" s="4">
+      <c r="A514" s="3">
         <v>6</v>
       </c>
-      <c r="B514" s="4">
+      <c r="B514" s="3">
         <v>13</v>
       </c>
-      <c r="C514" s="5" t="s">
+      <c r="C514" s="4" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="515" spans="1:3">
-      <c r="A515" s="4">
+      <c r="A515" s="3">
         <v>6</v>
       </c>
-      <c r="B515" s="4">
+      <c r="B515" s="3">
         <v>14</v>
       </c>
-      <c r="C515" s="5" t="s">
+      <c r="C515" s="4" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="516" spans="1:3">
-      <c r="A516" s="4">
+      <c r="A516" s="3">
         <v>6</v>
       </c>
-      <c r="B516" s="4">
+      <c r="B516" s="3">
         <v>15</v>
       </c>
-      <c r="C516" s="5" t="s">
+      <c r="C516" s="4" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="517" spans="1:3">
-      <c r="A517" s="4">
+      <c r="A517" s="3">
         <v>6</v>
       </c>
-      <c r="B517" s="4">
+      <c r="B517" s="3">
         <v>16</v>
       </c>
-      <c r="C517" s="5" t="s">
+      <c r="C517" s="4" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="518" spans="1:3">
-      <c r="A518" s="4">
+      <c r="A518" s="3">
         <v>6</v>
       </c>
-      <c r="B518" s="4">
+      <c r="B518" s="3">
         <v>17</v>
       </c>
-      <c r="C518" s="5" t="s">
+      <c r="C518" s="4" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="519" spans="1:3">
-      <c r="A519" s="4">
+      <c r="A519" s="3">
         <v>6</v>
       </c>
-      <c r="B519" s="4">
+      <c r="B519" s="3">
         <v>18</v>
       </c>
-      <c r="C519" s="5" t="s">
+      <c r="C519" s="4" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="520" spans="1:3">
-      <c r="A520" s="4">
+      <c r="A520" s="3">
         <v>6</v>
       </c>
-      <c r="B520" s="4">
+      <c r="B520" s="3">
         <v>19</v>
       </c>
-      <c r="C520" s="5" t="s">
+      <c r="C520" s="4" t="s">
         <v>520</v>
       </c>
     </row>
     <row r="521" spans="1:3">
-      <c r="A521" s="4">
+      <c r="A521" s="3">
         <v>6</v>
       </c>
-      <c r="B521" s="4">
+      <c r="B521" s="3">
         <v>20</v>
       </c>
-      <c r="C521" s="5" t="s">
+      <c r="C521" s="4" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="522" spans="1:3">
-      <c r="A522" s="4">
+      <c r="A522" s="3">
         <v>6</v>
       </c>
-      <c r="B522" s="4">
+      <c r="B522" s="3">
         <v>21</v>
       </c>
       <c r="C522" t="s">
@@ -9788,10 +9782,10 @@
       </c>
     </row>
     <row r="523" spans="1:3">
-      <c r="A523" s="4">
+      <c r="A523" s="3">
         <v>6</v>
       </c>
-      <c r="B523" s="4">
+      <c r="B523" s="3">
         <v>22</v>
       </c>
       <c r="C523" t="s">
@@ -9799,21 +9793,21 @@
       </c>
     </row>
     <row r="524" spans="1:3">
-      <c r="A524" s="4">
+      <c r="A524" s="3">
         <v>6</v>
       </c>
-      <c r="B524" s="4">
+      <c r="B524" s="3">
         <v>23</v>
       </c>
-      <c r="C524" s="6" t="s">
+      <c r="C524" s="5" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="525" spans="1:3">
-      <c r="A525" s="4">
+      <c r="A525" s="3">
         <v>6</v>
       </c>
-      <c r="B525" s="4">
+      <c r="B525" s="3">
         <v>24</v>
       </c>
       <c r="C525" t="s">
@@ -9821,10 +9815,10 @@
       </c>
     </row>
     <row r="526" spans="1:3">
-      <c r="A526" s="4">
+      <c r="A526" s="3">
         <v>6</v>
       </c>
-      <c r="B526" s="4">
+      <c r="B526" s="3">
         <v>25</v>
       </c>
       <c r="C526" t="s">
@@ -9832,10 +9826,10 @@
       </c>
     </row>
     <row r="527" spans="1:3">
-      <c r="A527" s="4">
+      <c r="A527" s="3">
         <v>6</v>
       </c>
-      <c r="B527" s="4">
+      <c r="B527" s="3">
         <v>26</v>
       </c>
       <c r="C527" t="s">
@@ -9843,10 +9837,10 @@
       </c>
     </row>
     <row r="528" spans="1:3">
-      <c r="A528" s="4">
+      <c r="A528" s="3">
         <v>6</v>
       </c>
-      <c r="B528" s="4">
+      <c r="B528" s="3">
         <v>27</v>
       </c>
       <c r="C528" t="s">
@@ -9854,10 +9848,10 @@
       </c>
     </row>
     <row r="529" spans="1:3">
-      <c r="A529" s="4">
+      <c r="A529" s="3">
         <v>6</v>
       </c>
-      <c r="B529" s="4">
+      <c r="B529" s="3">
         <v>28</v>
       </c>
       <c r="C529" t="s">
@@ -9865,10 +9859,10 @@
       </c>
     </row>
     <row r="530" spans="1:3">
-      <c r="A530" s="4">
+      <c r="A530" s="3">
         <v>6</v>
       </c>
-      <c r="B530" s="4">
+      <c r="B530" s="3">
         <v>29</v>
       </c>
       <c r="C530" t="s">
@@ -9876,10 +9870,10 @@
       </c>
     </row>
     <row r="531" spans="1:3">
-      <c r="A531" s="4">
+      <c r="A531" s="3">
         <v>6</v>
       </c>
-      <c r="B531" s="4">
+      <c r="B531" s="3">
         <v>30</v>
       </c>
       <c r="C531" t="s">
@@ -9887,10 +9881,10 @@
       </c>
     </row>
     <row r="532" spans="1:3">
-      <c r="A532" s="4">
+      <c r="A532" s="3">
         <v>6</v>
       </c>
-      <c r="B532" s="4">
+      <c r="B532" s="3">
         <v>31</v>
       </c>
       <c r="C532" t="s">
@@ -9898,10 +9892,10 @@
       </c>
     </row>
     <row r="533" spans="1:3">
-      <c r="A533" s="4">
+      <c r="A533" s="3">
         <v>6</v>
       </c>
-      <c r="B533" s="4">
+      <c r="B533" s="3">
         <v>32</v>
       </c>
       <c r="C533" t="s">
@@ -9909,10 +9903,10 @@
       </c>
     </row>
     <row r="534" spans="1:3">
-      <c r="A534" s="4">
+      <c r="A534" s="3">
         <v>6</v>
       </c>
-      <c r="B534" s="4">
+      <c r="B534" s="3">
         <v>33</v>
       </c>
       <c r="C534" t="s">
@@ -9920,10 +9914,10 @@
       </c>
     </row>
     <row r="535" spans="1:3">
-      <c r="A535" s="4">
+      <c r="A535" s="3">
         <v>6</v>
       </c>
-      <c r="B535" s="4">
+      <c r="B535" s="3">
         <v>34</v>
       </c>
       <c r="C535" t="s">
@@ -9931,10 +9925,10 @@
       </c>
     </row>
     <row r="536" spans="1:3">
-      <c r="A536" s="4">
+      <c r="A536" s="3">
         <v>6</v>
       </c>
-      <c r="B536" s="4">
+      <c r="B536" s="3">
         <v>35</v>
       </c>
       <c r="C536" t="s">
@@ -9942,10 +9936,10 @@
       </c>
     </row>
     <row r="537" spans="1:3">
-      <c r="A537" s="4">
+      <c r="A537" s="3">
         <v>6</v>
       </c>
-      <c r="B537" s="4">
+      <c r="B537" s="3">
         <v>36</v>
       </c>
       <c r="C537" t="s">
@@ -9953,21 +9947,21 @@
       </c>
     </row>
     <row r="538" spans="1:3">
-      <c r="A538" s="4">
+      <c r="A538" s="3">
         <v>6</v>
       </c>
-      <c r="B538" s="4">
+      <c r="B538" s="3">
         <v>37</v>
       </c>
-      <c r="C538" s="6" t="s">
+      <c r="C538" s="5" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="539" spans="1:3">
-      <c r="A539" s="4">
+      <c r="A539" s="3">
         <v>6</v>
       </c>
-      <c r="B539" s="4">
+      <c r="B539" s="3">
         <v>38</v>
       </c>
       <c r="C539" t="s">
@@ -9975,10 +9969,10 @@
       </c>
     </row>
     <row r="540" spans="1:3">
-      <c r="A540" s="4">
+      <c r="A540" s="3">
         <v>6</v>
       </c>
-      <c r="B540" s="4">
+      <c r="B540" s="3">
         <v>39</v>
       </c>
       <c r="C540" t="s">
@@ -9986,10 +9980,10 @@
       </c>
     </row>
     <row r="541" spans="1:3">
-      <c r="A541" s="4">
+      <c r="A541" s="3">
         <v>6</v>
       </c>
-      <c r="B541" s="4">
+      <c r="B541" s="3">
         <v>40</v>
       </c>
       <c r="C541" t="s">
@@ -9997,10 +9991,10 @@
       </c>
     </row>
     <row r="542" spans="1:3">
-      <c r="A542" s="4">
+      <c r="A542" s="3">
         <v>6</v>
       </c>
-      <c r="B542" s="4">
+      <c r="B542" s="3">
         <v>41</v>
       </c>
       <c r="C542" t="s">
@@ -10008,10 +10002,10 @@
       </c>
     </row>
     <row r="543" spans="1:3">
-      <c r="A543" s="4">
+      <c r="A543" s="3">
         <v>6</v>
       </c>
-      <c r="B543" s="4">
+      <c r="B543" s="3">
         <v>42</v>
       </c>
       <c r="C543" t="s">
@@ -10019,10 +10013,10 @@
       </c>
     </row>
     <row r="544" spans="1:3">
-      <c r="A544" s="4">
+      <c r="A544" s="3">
         <v>6</v>
       </c>
-      <c r="B544" s="4">
+      <c r="B544" s="3">
         <v>43</v>
       </c>
       <c r="C544" t="s">
@@ -10030,10 +10024,10 @@
       </c>
     </row>
     <row r="545" spans="1:3">
-      <c r="A545" s="4">
+      <c r="A545" s="3">
         <v>6</v>
       </c>
-      <c r="B545" s="4">
+      <c r="B545" s="3">
         <v>44</v>
       </c>
       <c r="C545" t="s">
@@ -10041,10 +10035,10 @@
       </c>
     </row>
     <row r="546" spans="1:3">
-      <c r="A546" s="4">
+      <c r="A546" s="3">
         <v>6</v>
       </c>
-      <c r="B546" s="4">
+      <c r="B546" s="3">
         <v>45</v>
       </c>
       <c r="C546" t="s">
@@ -10052,10 +10046,10 @@
       </c>
     </row>
     <row r="547" spans="1:3">
-      <c r="A547" s="4">
+      <c r="A547" s="3">
         <v>6</v>
       </c>
-      <c r="B547" s="4">
+      <c r="B547" s="3">
         <v>46</v>
       </c>
       <c r="C547" t="s">
@@ -10063,10 +10057,10 @@
       </c>
     </row>
     <row r="548" spans="1:3">
-      <c r="A548" s="4">
+      <c r="A548" s="3">
         <v>6</v>
       </c>
-      <c r="B548" s="4">
+      <c r="B548" s="3">
         <v>47</v>
       </c>
       <c r="C548" t="s">
@@ -10074,10 +10068,10 @@
       </c>
     </row>
     <row r="549" spans="1:3">
-      <c r="A549" s="4">
+      <c r="A549" s="3">
         <v>6</v>
       </c>
-      <c r="B549" s="4">
+      <c r="B549" s="3">
         <v>48</v>
       </c>
       <c r="C549" t="s">
@@ -10085,10 +10079,10 @@
       </c>
     </row>
     <row r="550" spans="1:3">
-      <c r="A550" s="4">
+      <c r="A550" s="3">
         <v>6</v>
       </c>
-      <c r="B550" s="4">
+      <c r="B550" s="3">
         <v>49</v>
       </c>
       <c r="C550" t="s">
@@ -10096,10 +10090,10 @@
       </c>
     </row>
     <row r="551" spans="1:3">
-      <c r="A551" s="4">
+      <c r="A551" s="3">
         <v>6</v>
       </c>
-      <c r="B551" s="4">
+      <c r="B551" s="3">
         <v>50</v>
       </c>
       <c r="C551" t="s">
@@ -10107,10 +10101,10 @@
       </c>
     </row>
     <row r="552" spans="1:3">
-      <c r="A552" s="4">
+      <c r="A552" s="3">
         <v>6</v>
       </c>
-      <c r="B552" s="4">
+      <c r="B552" s="3">
         <v>51</v>
       </c>
       <c r="C552" t="s">
@@ -10118,10 +10112,10 @@
       </c>
     </row>
     <row r="553" spans="1:3">
-      <c r="A553" s="4">
+      <c r="A553" s="3">
         <v>6</v>
       </c>
-      <c r="B553" s="4">
+      <c r="B553" s="3">
         <v>52</v>
       </c>
       <c r="C553" t="s">
@@ -10129,10 +10123,10 @@
       </c>
     </row>
     <row r="554" spans="1:3">
-      <c r="A554" s="4">
+      <c r="A554" s="3">
         <v>6</v>
       </c>
-      <c r="B554" s="4">
+      <c r="B554" s="3">
         <v>53</v>
       </c>
       <c r="C554" t="s">
@@ -10140,10 +10134,10 @@
       </c>
     </row>
     <row r="555" spans="1:3">
-      <c r="A555" s="4">
+      <c r="A555" s="3">
         <v>6</v>
       </c>
-      <c r="B555" s="4">
+      <c r="B555" s="3">
         <v>54</v>
       </c>
       <c r="C555" t="s">
@@ -10151,10 +10145,10 @@
       </c>
     </row>
     <row r="556" spans="1:3">
-      <c r="A556" s="4">
+      <c r="A556" s="3">
         <v>6</v>
       </c>
-      <c r="B556" s="4">
+      <c r="B556" s="3">
         <v>55</v>
       </c>
       <c r="C556" t="s">
@@ -10162,10 +10156,10 @@
       </c>
     </row>
     <row r="557" spans="1:3">
-      <c r="A557" s="4">
+      <c r="A557" s="3">
         <v>6</v>
       </c>
-      <c r="B557" s="4">
+      <c r="B557" s="3">
         <v>56</v>
       </c>
       <c r="C557" t="s">
@@ -10173,10 +10167,10 @@
       </c>
     </row>
     <row r="558" spans="1:3">
-      <c r="A558" s="4">
+      <c r="A558" s="3">
         <v>6</v>
       </c>
-      <c r="B558" s="4">
+      <c r="B558" s="3">
         <v>57</v>
       </c>
       <c r="C558" t="s">
@@ -10184,10 +10178,10 @@
       </c>
     </row>
     <row r="559" spans="1:3">
-      <c r="A559" s="4">
+      <c r="A559" s="3">
         <v>6</v>
       </c>
-      <c r="B559" s="4">
+      <c r="B559" s="3">
         <v>58</v>
       </c>
       <c r="C559" t="s">
@@ -10195,10 +10189,10 @@
       </c>
     </row>
     <row r="560" spans="1:3">
-      <c r="A560" s="4">
+      <c r="A560" s="3">
         <v>6</v>
       </c>
-      <c r="B560" s="4">
+      <c r="B560" s="3">
         <v>59</v>
       </c>
       <c r="C560" t="s">
@@ -10206,10 +10200,10 @@
       </c>
     </row>
     <row r="561" spans="1:3">
-      <c r="A561" s="4">
+      <c r="A561" s="3">
         <v>6</v>
       </c>
-      <c r="B561" s="4">
+      <c r="B561" s="3">
         <v>60</v>
       </c>
       <c r="C561" t="s">
@@ -10217,10 +10211,10 @@
       </c>
     </row>
     <row r="562" spans="1:3">
-      <c r="A562" s="4">
+      <c r="A562" s="3">
         <v>6</v>
       </c>
-      <c r="B562" s="4">
+      <c r="B562" s="3">
         <v>61</v>
       </c>
       <c r="C562" t="s">
@@ -10228,10 +10222,10 @@
       </c>
     </row>
     <row r="563" spans="1:3">
-      <c r="A563" s="4">
+      <c r="A563" s="3">
         <v>6</v>
       </c>
-      <c r="B563" s="4">
+      <c r="B563" s="3">
         <v>62</v>
       </c>
       <c r="C563" t="s">
@@ -10239,10 +10233,10 @@
       </c>
     </row>
     <row r="564" spans="1:3">
-      <c r="A564" s="4">
+      <c r="A564" s="3">
         <v>6</v>
       </c>
-      <c r="B564" s="4">
+      <c r="B564" s="3">
         <v>63</v>
       </c>
       <c r="C564" t="s">
@@ -10250,10 +10244,10 @@
       </c>
     </row>
     <row r="565" spans="1:3">
-      <c r="A565" s="4">
+      <c r="A565" s="3">
         <v>6</v>
       </c>
-      <c r="B565" s="4">
+      <c r="B565" s="3">
         <v>64</v>
       </c>
       <c r="C565" t="s">
@@ -10261,10 +10255,10 @@
       </c>
     </row>
     <row r="566" spans="1:3">
-      <c r="A566" s="4">
+      <c r="A566" s="3">
         <v>6</v>
       </c>
-      <c r="B566" s="4">
+      <c r="B566" s="3">
         <v>65</v>
       </c>
       <c r="C566" t="s">
@@ -10272,10 +10266,10 @@
       </c>
     </row>
     <row r="567" spans="1:3">
-      <c r="A567" s="4">
+      <c r="A567" s="3">
         <v>6</v>
       </c>
-      <c r="B567" s="4">
+      <c r="B567" s="3">
         <v>66</v>
       </c>
       <c r="C567" t="s">
@@ -10283,10 +10277,10 @@
       </c>
     </row>
     <row r="568" spans="1:3">
-      <c r="A568" s="4">
+      <c r="A568" s="3">
         <v>6</v>
       </c>
-      <c r="B568" s="4">
+      <c r="B568" s="3">
         <v>67</v>
       </c>
       <c r="C568" t="s">
@@ -10294,10 +10288,10 @@
       </c>
     </row>
     <row r="569" spans="1:3">
-      <c r="A569" s="4">
+      <c r="A569" s="3">
         <v>6</v>
       </c>
-      <c r="B569" s="4">
+      <c r="B569" s="3">
         <v>68</v>
       </c>
       <c r="C569" t="s">
@@ -10305,10 +10299,10 @@
       </c>
     </row>
     <row r="570" spans="1:3">
-      <c r="A570" s="4">
+      <c r="A570" s="3">
         <v>6</v>
       </c>
-      <c r="B570" s="4">
+      <c r="B570" s="3">
         <v>69</v>
       </c>
       <c r="C570" t="s">
@@ -10316,10 +10310,10 @@
       </c>
     </row>
     <row r="571" spans="1:3">
-      <c r="A571" s="4">
+      <c r="A571" s="3">
         <v>6</v>
       </c>
-      <c r="B571" s="4">
+      <c r="B571" s="3">
         <v>70</v>
       </c>
       <c r="C571" t="s">
@@ -10327,10 +10321,10 @@
       </c>
     </row>
     <row r="572" spans="1:3">
-      <c r="A572" s="4">
+      <c r="A572" s="3">
         <v>6</v>
       </c>
-      <c r="B572" s="4">
+      <c r="B572" s="3">
         <v>71</v>
       </c>
       <c r="C572" t="s">
@@ -10338,10 +10332,10 @@
       </c>
     </row>
     <row r="573" spans="1:3">
-      <c r="A573" s="4">
+      <c r="A573" s="3">
         <v>6</v>
       </c>
-      <c r="B573" s="4">
+      <c r="B573" s="3">
         <v>72</v>
       </c>
       <c r="C573" t="s">
@@ -10349,10 +10343,10 @@
       </c>
     </row>
     <row r="574" spans="1:3">
-      <c r="A574" s="4">
+      <c r="A574" s="3">
         <v>6</v>
       </c>
-      <c r="B574" s="4">
+      <c r="B574" s="3">
         <v>73</v>
       </c>
       <c r="C574" t="s">
@@ -10360,10 +10354,10 @@
       </c>
     </row>
     <row r="575" spans="1:3">
-      <c r="A575" s="4">
+      <c r="A575" s="3">
         <v>6</v>
       </c>
-      <c r="B575" s="4">
+      <c r="B575" s="3">
         <v>74</v>
       </c>
       <c r="C575" t="s">
@@ -10371,10 +10365,10 @@
       </c>
     </row>
     <row r="576" spans="1:3">
-      <c r="A576" s="4">
+      <c r="A576" s="3">
         <v>6</v>
       </c>
-      <c r="B576" s="4">
+      <c r="B576" s="3">
         <v>75</v>
       </c>
       <c r="C576" t="s">
@@ -10382,10 +10376,10 @@
       </c>
     </row>
     <row r="577" spans="1:3">
-      <c r="A577" s="4">
+      <c r="A577" s="3">
         <v>6</v>
       </c>
-      <c r="B577" s="4">
+      <c r="B577" s="3">
         <v>76</v>
       </c>
       <c r="C577" t="s">
@@ -10393,10 +10387,10 @@
       </c>
     </row>
     <row r="578" spans="1:3">
-      <c r="A578" s="4">
+      <c r="A578" s="3">
         <v>6</v>
       </c>
-      <c r="B578" s="4">
+      <c r="B578" s="3">
         <v>77</v>
       </c>
       <c r="C578" t="s">
@@ -10404,10 +10398,10 @@
       </c>
     </row>
     <row r="579" spans="1:3">
-      <c r="A579" s="4">
+      <c r="A579" s="3">
         <v>6</v>
       </c>
-      <c r="B579" s="4">
+      <c r="B579" s="3">
         <v>78</v>
       </c>
       <c r="C579" t="s">
@@ -10415,10 +10409,10 @@
       </c>
     </row>
     <row r="580" spans="1:3">
-      <c r="A580" s="4">
+      <c r="A580" s="3">
         <v>6</v>
       </c>
-      <c r="B580" s="4">
+      <c r="B580" s="3">
         <v>79</v>
       </c>
       <c r="C580" t="s">
@@ -10426,10 +10420,10 @@
       </c>
     </row>
     <row r="581" spans="1:3">
-      <c r="A581" s="4">
+      <c r="A581" s="3">
         <v>6</v>
       </c>
-      <c r="B581" s="4">
+      <c r="B581" s="3">
         <v>80</v>
       </c>
       <c r="C581" t="s">
@@ -10437,10 +10431,10 @@
       </c>
     </row>
     <row r="582" spans="1:3">
-      <c r="A582" s="4">
+      <c r="A582" s="3">
         <v>6</v>
       </c>
-      <c r="B582" s="4">
+      <c r="B582" s="3">
         <v>81</v>
       </c>
       <c r="C582" t="s">
@@ -10448,10 +10442,10 @@
       </c>
     </row>
     <row r="583" spans="1:3">
-      <c r="A583" s="4">
+      <c r="A583" s="3">
         <v>6</v>
       </c>
-      <c r="B583" s="4">
+      <c r="B583" s="3">
         <v>82</v>
       </c>
       <c r="C583" t="s">
@@ -10459,10 +10453,10 @@
       </c>
     </row>
     <row r="584" spans="1:3">
-      <c r="A584" s="4">
+      <c r="A584" s="3">
         <v>6</v>
       </c>
-      <c r="B584" s="4">
+      <c r="B584" s="3">
         <v>83</v>
       </c>
       <c r="C584" t="s">
@@ -10470,10 +10464,10 @@
       </c>
     </row>
     <row r="585" spans="1:3">
-      <c r="A585" s="4">
+      <c r="A585" s="3">
         <v>6</v>
       </c>
-      <c r="B585" s="4">
+      <c r="B585" s="3">
         <v>84</v>
       </c>
       <c r="C585" t="s">
@@ -10481,10 +10475,10 @@
       </c>
     </row>
     <row r="586" spans="1:3">
-      <c r="A586" s="4">
+      <c r="A586" s="3">
         <v>6</v>
       </c>
-      <c r="B586" s="4">
+      <c r="B586" s="3">
         <v>85</v>
       </c>
       <c r="C586" t="s">
@@ -10492,10 +10486,10 @@
       </c>
     </row>
     <row r="587" spans="1:3">
-      <c r="A587" s="4">
+      <c r="A587" s="3">
         <v>6</v>
       </c>
-      <c r="B587" s="4">
+      <c r="B587" s="3">
         <v>86</v>
       </c>
       <c r="C587" t="s">
@@ -10503,10 +10497,10 @@
       </c>
     </row>
     <row r="588" spans="1:3">
-      <c r="A588" s="4">
+      <c r="A588" s="3">
         <v>6</v>
       </c>
-      <c r="B588" s="4">
+      <c r="B588" s="3">
         <v>87</v>
       </c>
       <c r="C588" t="s">
@@ -10514,10 +10508,10 @@
       </c>
     </row>
     <row r="589" spans="1:3">
-      <c r="A589" s="4">
+      <c r="A589" s="3">
         <v>6</v>
       </c>
-      <c r="B589" s="4">
+      <c r="B589" s="3">
         <v>88</v>
       </c>
       <c r="C589" t="s">
@@ -10525,10 +10519,10 @@
       </c>
     </row>
     <row r="590" spans="1:3">
-      <c r="A590" s="4">
+      <c r="A590" s="3">
         <v>6</v>
       </c>
-      <c r="B590" s="4">
+      <c r="B590" s="3">
         <v>89</v>
       </c>
       <c r="C590" t="s">
@@ -10536,10 +10530,10 @@
       </c>
     </row>
     <row r="591" spans="1:3">
-      <c r="A591" s="4">
+      <c r="A591" s="3">
         <v>6</v>
       </c>
-      <c r="B591" s="4">
+      <c r="B591" s="3">
         <v>90</v>
       </c>
       <c r="C591" t="s">
@@ -10547,10 +10541,10 @@
       </c>
     </row>
     <row r="592" spans="1:3">
-      <c r="A592" s="4">
+      <c r="A592" s="3">
         <v>6</v>
       </c>
-      <c r="B592" s="4">
+      <c r="B592" s="3">
         <v>91</v>
       </c>
       <c r="C592" t="s">
@@ -10558,10 +10552,10 @@
       </c>
     </row>
     <row r="593" spans="1:3">
-      <c r="A593" s="4">
+      <c r="A593" s="3">
         <v>6</v>
       </c>
-      <c r="B593" s="4">
+      <c r="B593" s="3">
         <v>92</v>
       </c>
       <c r="C593" t="s">
@@ -10569,10 +10563,10 @@
       </c>
     </row>
     <row r="594" spans="1:3">
-      <c r="A594" s="4">
+      <c r="A594" s="3">
         <v>6</v>
       </c>
-      <c r="B594" s="4">
+      <c r="B594" s="3">
         <v>93</v>
       </c>
       <c r="C594" t="s">
@@ -10580,10 +10574,10 @@
       </c>
     </row>
     <row r="595" spans="1:3">
-      <c r="A595" s="4">
+      <c r="A595" s="3">
         <v>6</v>
       </c>
-      <c r="B595" s="4">
+      <c r="B595" s="3">
         <v>94</v>
       </c>
       <c r="C595" t="s">
@@ -10591,10 +10585,10 @@
       </c>
     </row>
     <row r="596" spans="1:3">
-      <c r="A596" s="4">
+      <c r="A596" s="3">
         <v>6</v>
       </c>
-      <c r="B596" s="4">
+      <c r="B596" s="3">
         <v>95</v>
       </c>
       <c r="C596" t="s">
@@ -10602,10 +10596,10 @@
       </c>
     </row>
     <row r="597" spans="1:3">
-      <c r="A597" s="4">
+      <c r="A597" s="3">
         <v>6</v>
       </c>
-      <c r="B597" s="4">
+      <c r="B597" s="3">
         <v>96</v>
       </c>
       <c r="C597" t="s">
@@ -10613,10 +10607,10 @@
       </c>
     </row>
     <row r="598" spans="1:3">
-      <c r="A598" s="4">
+      <c r="A598" s="3">
         <v>6</v>
       </c>
-      <c r="B598" s="4">
+      <c r="B598" s="3">
         <v>97</v>
       </c>
       <c r="C598" t="s">
@@ -10624,10 +10618,10 @@
       </c>
     </row>
     <row r="599" spans="1:3">
-      <c r="A599" s="4">
+      <c r="A599" s="3">
         <v>6</v>
       </c>
-      <c r="B599" s="4">
+      <c r="B599" s="3">
         <v>98</v>
       </c>
       <c r="C599" t="s">
@@ -10635,10 +10629,10 @@
       </c>
     </row>
     <row r="600" spans="1:3">
-      <c r="A600" s="4">
+      <c r="A600" s="3">
         <v>6</v>
       </c>
-      <c r="B600" s="4">
+      <c r="B600" s="3">
         <v>99</v>
       </c>
       <c r="C600" t="s">
@@ -10646,10 +10640,10 @@
       </c>
     </row>
     <row r="601" spans="1:3">
-      <c r="A601" s="4">
+      <c r="A601" s="3">
         <v>6</v>
       </c>
-      <c r="B601" s="4">
+      <c r="B601" s="3">
         <v>100</v>
       </c>
       <c r="C601" t="s">
@@ -10657,10 +10651,10 @@
       </c>
     </row>
     <row r="602" spans="1:3">
-      <c r="A602" s="4">
+      <c r="A602" s="3">
         <v>7</v>
       </c>
-      <c r="B602" s="4">
+      <c r="B602" s="3">
         <v>1</v>
       </c>
       <c r="C602" t="s">
@@ -10668,10 +10662,10 @@
       </c>
     </row>
     <row r="603" spans="1:3">
-      <c r="A603" s="4">
+      <c r="A603" s="3">
         <v>7</v>
       </c>
-      <c r="B603" s="4">
+      <c r="B603" s="3">
         <v>2</v>
       </c>
       <c r="C603" t="s">
@@ -10679,32 +10673,32 @@
       </c>
     </row>
     <row r="604" spans="1:3">
-      <c r="A604" s="4">
+      <c r="A604" s="3">
         <v>7</v>
       </c>
-      <c r="B604" s="4">
+      <c r="B604" s="3">
         <v>3</v>
       </c>
-      <c r="C604" s="6" t="s">
+      <c r="C604" s="5" t="s">
         <v>604</v>
       </c>
     </row>
     <row r="605" spans="1:3">
-      <c r="A605" s="4">
+      <c r="A605" s="3">
         <v>7</v>
       </c>
-      <c r="B605" s="4">
+      <c r="B605" s="3">
         <v>4</v>
       </c>
-      <c r="C605" s="6" t="s">
+      <c r="C605" s="5" t="s">
         <v>605</v>
       </c>
     </row>
     <row r="606" spans="1:3">
-      <c r="A606" s="4">
+      <c r="A606" s="3">
         <v>7</v>
       </c>
-      <c r="B606" s="4">
+      <c r="B606" s="3">
         <v>5</v>
       </c>
       <c r="C606" t="s">
@@ -10712,21 +10706,21 @@
       </c>
     </row>
     <row r="607" spans="1:3">
-      <c r="A607" s="4">
+      <c r="A607" s="3">
         <v>7</v>
       </c>
-      <c r="B607" s="4">
+      <c r="B607" s="3">
         <v>6</v>
       </c>
-      <c r="C607" s="6" t="s">
+      <c r="C607" s="5" t="s">
         <v>607</v>
       </c>
     </row>
     <row r="608" spans="1:3">
-      <c r="A608" s="4">
+      <c r="A608" s="3">
         <v>7</v>
       </c>
-      <c r="B608" s="4">
+      <c r="B608" s="3">
         <v>7</v>
       </c>
       <c r="C608" t="s">
@@ -10734,10 +10728,10 @@
       </c>
     </row>
     <row r="609" spans="1:3">
-      <c r="A609" s="4">
+      <c r="A609" s="3">
         <v>7</v>
       </c>
-      <c r="B609" s="4">
+      <c r="B609" s="3">
         <v>8</v>
       </c>
       <c r="C609" t="s">
@@ -10745,10 +10739,10 @@
       </c>
     </row>
     <row r="610" spans="1:3">
-      <c r="A610" s="4">
+      <c r="A610" s="3">
         <v>7</v>
       </c>
-      <c r="B610" s="4">
+      <c r="B610" s="3">
         <v>9</v>
       </c>
       <c r="C610" t="s">
@@ -10756,10 +10750,10 @@
       </c>
     </row>
     <row r="611" spans="1:3">
-      <c r="A611" s="4">
+      <c r="A611" s="3">
         <v>7</v>
       </c>
-      <c r="B611" s="4">
+      <c r="B611" s="3">
         <v>10</v>
       </c>
       <c r="C611" t="s">
@@ -10767,10 +10761,10 @@
       </c>
     </row>
     <row r="612" spans="1:3">
-      <c r="A612" s="4">
+      <c r="A612" s="3">
         <v>7</v>
       </c>
-      <c r="B612" s="4">
+      <c r="B612" s="3">
         <v>11</v>
       </c>
       <c r="C612" t="s">
@@ -10778,10 +10772,10 @@
       </c>
     </row>
     <row r="613" spans="1:3">
-      <c r="A613" s="4">
+      <c r="A613" s="3">
         <v>7</v>
       </c>
-      <c r="B613" s="4">
+      <c r="B613" s="3">
         <v>12</v>
       </c>
       <c r="C613" t="s">
@@ -10789,10 +10783,10 @@
       </c>
     </row>
     <row r="614" spans="1:3">
-      <c r="A614" s="4">
+      <c r="A614" s="3">
         <v>7</v>
       </c>
-      <c r="B614" s="4">
+      <c r="B614" s="3">
         <v>13</v>
       </c>
       <c r="C614" t="s">
@@ -10800,10 +10794,10 @@
       </c>
     </row>
     <row r="615" spans="1:3">
-      <c r="A615" s="4">
+      <c r="A615" s="3">
         <v>7</v>
       </c>
-      <c r="B615" s="4">
+      <c r="B615" s="3">
         <v>14</v>
       </c>
       <c r="C615" t="s">
@@ -10811,10 +10805,10 @@
       </c>
     </row>
     <row r="616" spans="1:3">
-      <c r="A616" s="4">
+      <c r="A616" s="3">
         <v>7</v>
       </c>
-      <c r="B616" s="4">
+      <c r="B616" s="3">
         <v>15</v>
       </c>
       <c r="C616" t="s">
@@ -10822,10 +10816,10 @@
       </c>
     </row>
     <row r="617" spans="1:3">
-      <c r="A617" s="4">
+      <c r="A617" s="3">
         <v>7</v>
       </c>
-      <c r="B617" s="4">
+      <c r="B617" s="3">
         <v>16</v>
       </c>
       <c r="C617" t="s">
@@ -10833,10 +10827,10 @@
       </c>
     </row>
     <row r="618" spans="1:3">
-      <c r="A618" s="4">
+      <c r="A618" s="3">
         <v>7</v>
       </c>
-      <c r="B618" s="4">
+      <c r="B618" s="3">
         <v>17</v>
       </c>
       <c r="C618" t="s">
@@ -10844,10 +10838,10 @@
       </c>
     </row>
     <row r="619" spans="1:3">
-      <c r="A619" s="4">
+      <c r="A619" s="3">
         <v>7</v>
       </c>
-      <c r="B619" s="4">
+      <c r="B619" s="3">
         <v>18</v>
       </c>
       <c r="C619" t="s">
@@ -10855,10 +10849,10 @@
       </c>
     </row>
     <row r="620" spans="1:3">
-      <c r="A620" s="4">
+      <c r="A620" s="3">
         <v>7</v>
       </c>
-      <c r="B620" s="4">
+      <c r="B620" s="3">
         <v>19</v>
       </c>
       <c r="C620" t="s">
@@ -10866,10 +10860,10 @@
       </c>
     </row>
     <row r="621" spans="1:3">
-      <c r="A621" s="4">
+      <c r="A621" s="3">
         <v>7</v>
       </c>
-      <c r="B621" s="4">
+      <c r="B621" s="3">
         <v>20</v>
       </c>
       <c r="C621" t="s">
@@ -10877,10 +10871,10 @@
       </c>
     </row>
     <row r="622" spans="1:3">
-      <c r="A622" s="4">
+      <c r="A622" s="3">
         <v>7</v>
       </c>
-      <c r="B622" s="4">
+      <c r="B622" s="3">
         <v>21</v>
       </c>
       <c r="C622" t="s">
@@ -10888,10 +10882,10 @@
       </c>
     </row>
     <row r="623" spans="1:3">
-      <c r="A623" s="4">
+      <c r="A623" s="3">
         <v>7</v>
       </c>
-      <c r="B623" s="4">
+      <c r="B623" s="3">
         <v>22</v>
       </c>
       <c r="C623" t="s">
@@ -10899,10 +10893,10 @@
       </c>
     </row>
     <row r="624" spans="1:3">
-      <c r="A624" s="4">
+      <c r="A624" s="3">
         <v>7</v>
       </c>
-      <c r="B624" s="4">
+      <c r="B624" s="3">
         <v>23</v>
       </c>
       <c r="C624" t="s">
@@ -10910,10 +10904,10 @@
       </c>
     </row>
     <row r="625" spans="1:3">
-      <c r="A625" s="4">
+      <c r="A625" s="3">
         <v>7</v>
       </c>
-      <c r="B625" s="4">
+      <c r="B625" s="3">
         <v>24</v>
       </c>
       <c r="C625" t="s">
@@ -10921,10 +10915,10 @@
       </c>
     </row>
     <row r="626" spans="1:3">
-      <c r="A626" s="4">
+      <c r="A626" s="3">
         <v>7</v>
       </c>
-      <c r="B626" s="4">
+      <c r="B626" s="3">
         <v>25</v>
       </c>
       <c r="C626" t="s">
@@ -10932,10 +10926,10 @@
       </c>
     </row>
     <row r="627" spans="1:3">
-      <c r="A627" s="4">
+      <c r="A627" s="3">
         <v>7</v>
       </c>
-      <c r="B627" s="4">
+      <c r="B627" s="3">
         <v>26</v>
       </c>
       <c r="C627" t="s">
@@ -10943,10 +10937,10 @@
       </c>
     </row>
     <row r="628" spans="1:3">
-      <c r="A628" s="4">
+      <c r="A628" s="3">
         <v>7</v>
       </c>
-      <c r="B628" s="4">
+      <c r="B628" s="3">
         <v>27</v>
       </c>
       <c r="C628" t="s">
@@ -10954,10 +10948,10 @@
       </c>
     </row>
     <row r="629" spans="1:3">
-      <c r="A629" s="4">
+      <c r="A629" s="3">
         <v>7</v>
       </c>
-      <c r="B629" s="4">
+      <c r="B629" s="3">
         <v>28</v>
       </c>
       <c r="C629" t="s">
@@ -10965,10 +10959,10 @@
       </c>
     </row>
     <row r="630" spans="1:3">
-      <c r="A630" s="4">
+      <c r="A630" s="3">
         <v>7</v>
       </c>
-      <c r="B630" s="4">
+      <c r="B630" s="3">
         <v>29</v>
       </c>
       <c r="C630" t="s">
@@ -10976,10 +10970,10 @@
       </c>
     </row>
     <row r="631" spans="1:3">
-      <c r="A631" s="4">
+      <c r="A631" s="3">
         <v>7</v>
       </c>
-      <c r="B631" s="4">
+      <c r="B631" s="3">
         <v>30</v>
       </c>
       <c r="C631" t="s">
@@ -10987,10 +10981,10 @@
       </c>
     </row>
     <row r="632" spans="1:3">
-      <c r="A632" s="4">
+      <c r="A632" s="3">
         <v>7</v>
       </c>
-      <c r="B632" s="4">
+      <c r="B632" s="3">
         <v>31</v>
       </c>
       <c r="C632" t="s">
@@ -10998,10 +10992,10 @@
       </c>
     </row>
     <row r="633" spans="1:3">
-      <c r="A633" s="4">
+      <c r="A633" s="3">
         <v>7</v>
       </c>
-      <c r="B633" s="4">
+      <c r="B633" s="3">
         <v>32</v>
       </c>
       <c r="C633" t="s">
@@ -11009,10 +11003,10 @@
       </c>
     </row>
     <row r="634" spans="1:3">
-      <c r="A634" s="4">
+      <c r="A634" s="3">
         <v>7</v>
       </c>
-      <c r="B634" s="4">
+      <c r="B634" s="3">
         <v>33</v>
       </c>
       <c r="C634" t="s">
@@ -11020,10 +11014,10 @@
       </c>
     </row>
     <row r="635" spans="1:3">
-      <c r="A635" s="4">
+      <c r="A635" s="3">
         <v>7</v>
       </c>
-      <c r="B635" s="4">
+      <c r="B635" s="3">
         <v>34</v>
       </c>
       <c r="C635" t="s">
@@ -11031,10 +11025,10 @@
       </c>
     </row>
     <row r="636" spans="1:3">
-      <c r="A636" s="4">
+      <c r="A636" s="3">
         <v>7</v>
       </c>
-      <c r="B636" s="4">
+      <c r="B636" s="3">
         <v>35</v>
       </c>
       <c r="C636" t="s">
@@ -11042,10 +11036,10 @@
       </c>
     </row>
     <row r="637" spans="1:3">
-      <c r="A637" s="4">
+      <c r="A637" s="3">
         <v>7</v>
       </c>
-      <c r="B637" s="4">
+      <c r="B637" s="3">
         <v>36</v>
       </c>
       <c r="C637" t="s">
@@ -11053,10 +11047,10 @@
       </c>
     </row>
     <row r="638" spans="1:3">
-      <c r="A638" s="4">
+      <c r="A638" s="3">
         <v>7</v>
       </c>
-      <c r="B638" s="4">
+      <c r="B638" s="3">
         <v>37</v>
       </c>
       <c r="C638" t="s">
@@ -11064,10 +11058,10 @@
       </c>
     </row>
     <row r="639" spans="1:3">
-      <c r="A639" s="4">
+      <c r="A639" s="3">
         <v>7</v>
       </c>
-      <c r="B639" s="4">
+      <c r="B639" s="3">
         <v>38</v>
       </c>
       <c r="C639" t="s">
@@ -11075,10 +11069,10 @@
       </c>
     </row>
     <row r="640" spans="1:3">
-      <c r="A640" s="4">
+      <c r="A640" s="3">
         <v>7</v>
       </c>
-      <c r="B640" s="4">
+      <c r="B640" s="3">
         <v>39</v>
       </c>
       <c r="C640" t="s">
@@ -11086,10 +11080,10 @@
       </c>
     </row>
     <row r="641" spans="1:3">
-      <c r="A641" s="4">
+      <c r="A641" s="3">
         <v>7</v>
       </c>
-      <c r="B641" s="4">
+      <c r="B641" s="3">
         <v>40</v>
       </c>
       <c r="C641" t="s">
@@ -11097,10 +11091,10 @@
       </c>
     </row>
     <row r="642" spans="1:3">
-      <c r="A642" s="4">
+      <c r="A642" s="3">
         <v>7</v>
       </c>
-      <c r="B642" s="4">
+      <c r="B642" s="3">
         <v>41</v>
       </c>
       <c r="C642" t="s">
@@ -11108,10 +11102,10 @@
       </c>
     </row>
     <row r="643" spans="1:3">
-      <c r="A643" s="4">
+      <c r="A643" s="3">
         <v>7</v>
       </c>
-      <c r="B643" s="4">
+      <c r="B643" s="3">
         <v>42</v>
       </c>
       <c r="C643" t="s">
@@ -11119,10 +11113,10 @@
       </c>
     </row>
     <row r="644" spans="1:3">
-      <c r="A644" s="4">
+      <c r="A644" s="3">
         <v>7</v>
       </c>
-      <c r="B644" s="4">
+      <c r="B644" s="3">
         <v>43</v>
       </c>
       <c r="C644" t="s">
@@ -11130,10 +11124,10 @@
       </c>
     </row>
     <row r="645" spans="1:3">
-      <c r="A645" s="4">
+      <c r="A645" s="3">
         <v>7</v>
       </c>
-      <c r="B645" s="4">
+      <c r="B645" s="3">
         <v>44</v>
       </c>
       <c r="C645" t="s">
@@ -11141,10 +11135,10 @@
       </c>
     </row>
     <row r="646" spans="1:3">
-      <c r="A646" s="4">
+      <c r="A646" s="3">
         <v>7</v>
       </c>
-      <c r="B646" s="4">
+      <c r="B646" s="3">
         <v>45</v>
       </c>
       <c r="C646" t="s">
@@ -11152,10 +11146,10 @@
       </c>
     </row>
     <row r="647" spans="1:3">
-      <c r="A647" s="4">
+      <c r="A647" s="3">
         <v>7</v>
       </c>
-      <c r="B647" s="4">
+      <c r="B647" s="3">
         <v>46</v>
       </c>
       <c r="C647" t="s">
@@ -11163,10 +11157,10 @@
       </c>
     </row>
     <row r="648" spans="1:3">
-      <c r="A648" s="4">
+      <c r="A648" s="3">
         <v>7</v>
       </c>
-      <c r="B648" s="4">
+      <c r="B648" s="3">
         <v>47</v>
       </c>
       <c r="C648" t="s">
@@ -11174,10 +11168,10 @@
       </c>
     </row>
     <row r="649" spans="1:3">
-      <c r="A649" s="4">
+      <c r="A649" s="3">
         <v>7</v>
       </c>
-      <c r="B649" s="4">
+      <c r="B649" s="3">
         <v>48</v>
       </c>
       <c r="C649" t="s">
@@ -11185,10 +11179,10 @@
       </c>
     </row>
     <row r="650" spans="1:3">
-      <c r="A650" s="4">
+      <c r="A650" s="3">
         <v>7</v>
       </c>
-      <c r="B650" s="4">
+      <c r="B650" s="3">
         <v>49</v>
       </c>
       <c r="C650" t="s">
@@ -11196,10 +11190,10 @@
       </c>
     </row>
     <row r="651" spans="1:3">
-      <c r="A651" s="4">
+      <c r="A651" s="3">
         <v>7</v>
       </c>
-      <c r="B651" s="4">
+      <c r="B651" s="3">
         <v>50</v>
       </c>
       <c r="C651" t="s">
@@ -11207,10 +11201,10 @@
       </c>
     </row>
     <row r="652" spans="1:3">
-      <c r="A652" s="4">
+      <c r="A652" s="3">
         <v>7</v>
       </c>
-      <c r="B652" s="4">
+      <c r="B652" s="3">
         <v>51</v>
       </c>
       <c r="C652" t="s">
@@ -11218,10 +11212,10 @@
       </c>
     </row>
     <row r="653" spans="1:3">
-      <c r="A653" s="4">
+      <c r="A653" s="3">
         <v>7</v>
       </c>
-      <c r="B653" s="4">
+      <c r="B653" s="3">
         <v>52</v>
       </c>
       <c r="C653" t="s">
@@ -11229,10 +11223,10 @@
       </c>
     </row>
     <row r="654" spans="1:3">
-      <c r="A654" s="4">
+      <c r="A654" s="3">
         <v>7</v>
       </c>
-      <c r="B654" s="4">
+      <c r="B654" s="3">
         <v>53</v>
       </c>
       <c r="C654" t="s">
@@ -11240,10 +11234,10 @@
       </c>
     </row>
     <row r="655" spans="1:3">
-      <c r="A655" s="4">
+      <c r="A655" s="3">
         <v>7</v>
       </c>
-      <c r="B655" s="4">
+      <c r="B655" s="3">
         <v>54</v>
       </c>
       <c r="C655" t="s">
@@ -11251,10 +11245,10 @@
       </c>
     </row>
     <row r="656" spans="1:3">
-      <c r="A656" s="4">
+      <c r="A656" s="3">
         <v>7</v>
       </c>
-      <c r="B656" s="4">
+      <c r="B656" s="3">
         <v>55</v>
       </c>
       <c r="C656" t="s">
@@ -11262,10 +11256,10 @@
       </c>
     </row>
     <row r="657" spans="1:3">
-      <c r="A657" s="4">
+      <c r="A657" s="3">
         <v>7</v>
       </c>
-      <c r="B657" s="4">
+      <c r="B657" s="3">
         <v>56</v>
       </c>
       <c r="C657" t="s">
@@ -11273,10 +11267,10 @@
       </c>
     </row>
     <row r="658" spans="1:3">
-      <c r="A658" s="4">
+      <c r="A658" s="3">
         <v>7</v>
       </c>
-      <c r="B658" s="4">
+      <c r="B658" s="3">
         <v>57</v>
       </c>
       <c r="C658" t="s">
@@ -11284,10 +11278,10 @@
       </c>
     </row>
     <row r="659" spans="1:3">
-      <c r="A659" s="4">
+      <c r="A659" s="3">
         <v>7</v>
       </c>
-      <c r="B659" s="4">
+      <c r="B659" s="3">
         <v>58</v>
       </c>
       <c r="C659" t="s">
@@ -11295,10 +11289,10 @@
       </c>
     </row>
     <row r="660" spans="1:3">
-      <c r="A660" s="4">
+      <c r="A660" s="3">
         <v>7</v>
       </c>
-      <c r="B660" s="4">
+      <c r="B660" s="3">
         <v>59</v>
       </c>
       <c r="C660" t="s">
@@ -11306,10 +11300,10 @@
       </c>
     </row>
     <row r="661" spans="1:3">
-      <c r="A661" s="4">
+      <c r="A661" s="3">
         <v>7</v>
       </c>
-      <c r="B661" s="4">
+      <c r="B661" s="3">
         <v>60</v>
       </c>
       <c r="C661" t="s">
@@ -11317,10 +11311,10 @@
       </c>
     </row>
     <row r="662" spans="1:3">
-      <c r="A662" s="4">
+      <c r="A662" s="3">
         <v>7</v>
       </c>
-      <c r="B662" s="4">
+      <c r="B662" s="3">
         <v>61</v>
       </c>
       <c r="C662" t="s">
@@ -11328,10 +11322,10 @@
       </c>
     </row>
     <row r="663" spans="1:3">
-      <c r="A663" s="4">
+      <c r="A663" s="3">
         <v>7</v>
       </c>
-      <c r="B663" s="4">
+      <c r="B663" s="3">
         <v>62</v>
       </c>
       <c r="C663" t="s">
@@ -11339,10 +11333,10 @@
       </c>
     </row>
     <row r="664" spans="1:3">
-      <c r="A664" s="4">
+      <c r="A664" s="3">
         <v>7</v>
       </c>
-      <c r="B664" s="4">
+      <c r="B664" s="3">
         <v>63</v>
       </c>
       <c r="C664" t="s">
@@ -11350,10 +11344,10 @@
       </c>
     </row>
     <row r="665" spans="1:3">
-      <c r="A665" s="4">
+      <c r="A665" s="3">
         <v>7</v>
       </c>
-      <c r="B665" s="4">
+      <c r="B665" s="3">
         <v>64</v>
       </c>
       <c r="C665" t="s">
@@ -11361,10 +11355,10 @@
       </c>
     </row>
     <row r="666" spans="1:3">
-      <c r="A666" s="4">
+      <c r="A666" s="3">
         <v>7</v>
       </c>
-      <c r="B666" s="4">
+      <c r="B666" s="3">
         <v>65</v>
       </c>
       <c r="C666" t="s">
@@ -11372,10 +11366,10 @@
       </c>
     </row>
     <row r="667" spans="1:3">
-      <c r="A667" s="4">
+      <c r="A667" s="3">
         <v>7</v>
       </c>
-      <c r="B667" s="4">
+      <c r="B667" s="3">
         <v>66</v>
       </c>
       <c r="C667" t="s">
@@ -11383,10 +11377,10 @@
       </c>
     </row>
     <row r="668" spans="1:3">
-      <c r="A668" s="4">
+      <c r="A668" s="3">
         <v>7</v>
       </c>
-      <c r="B668" s="4">
+      <c r="B668" s="3">
         <v>67</v>
       </c>
       <c r="C668" t="s">
@@ -11394,10 +11388,10 @@
       </c>
     </row>
     <row r="669" spans="1:3">
-      <c r="A669" s="4">
+      <c r="A669" s="3">
         <v>7</v>
       </c>
-      <c r="B669" s="4">
+      <c r="B669" s="3">
         <v>68</v>
       </c>
       <c r="C669" t="s">
@@ -11405,10 +11399,10 @@
       </c>
     </row>
     <row r="670" spans="1:3">
-      <c r="A670" s="4">
+      <c r="A670" s="3">
         <v>7</v>
       </c>
-      <c r="B670" s="4">
+      <c r="B670" s="3">
         <v>69</v>
       </c>
       <c r="C670" t="s">
@@ -11416,10 +11410,10 @@
       </c>
     </row>
     <row r="671" spans="1:3">
-      <c r="A671" s="4">
+      <c r="A671" s="3">
         <v>7</v>
       </c>
-      <c r="B671" s="4">
+      <c r="B671" s="3">
         <v>70</v>
       </c>
       <c r="C671" t="s">
@@ -11427,10 +11421,10 @@
       </c>
     </row>
     <row r="672" spans="1:3">
-      <c r="A672" s="4">
+      <c r="A672" s="3">
         <v>7</v>
       </c>
-      <c r="B672" s="4">
+      <c r="B672" s="3">
         <v>71</v>
       </c>
       <c r="C672" t="s">
@@ -11438,10 +11432,10 @@
       </c>
     </row>
     <row r="673" spans="1:3">
-      <c r="A673" s="4">
+      <c r="A673" s="3">
         <v>7</v>
       </c>
-      <c r="B673" s="4">
+      <c r="B673" s="3">
         <v>72</v>
       </c>
       <c r="C673" t="s">
@@ -11449,10 +11443,10 @@
       </c>
     </row>
     <row r="674" spans="1:3">
-      <c r="A674" s="4">
+      <c r="A674" s="3">
         <v>7</v>
       </c>
-      <c r="B674" s="4">
+      <c r="B674" s="3">
         <v>73</v>
       </c>
       <c r="C674" t="s">
@@ -11460,10 +11454,10 @@
       </c>
     </row>
     <row r="675" spans="1:3">
-      <c r="A675" s="4">
+      <c r="A675" s="3">
         <v>7</v>
       </c>
-      <c r="B675" s="4">
+      <c r="B675" s="3">
         <v>74</v>
       </c>
       <c r="C675" t="s">
@@ -11471,10 +11465,10 @@
       </c>
     </row>
     <row r="676" spans="1:3">
-      <c r="A676" s="4">
+      <c r="A676" s="3">
         <v>7</v>
       </c>
-      <c r="B676" s="4">
+      <c r="B676" s="3">
         <v>75</v>
       </c>
       <c r="C676" t="s">
@@ -11482,10 +11476,10 @@
       </c>
     </row>
     <row r="677" spans="1:3">
-      <c r="A677" s="4">
+      <c r="A677" s="3">
         <v>7</v>
       </c>
-      <c r="B677" s="4">
+      <c r="B677" s="3">
         <v>76</v>
       </c>
       <c r="C677" t="s">
@@ -11493,10 +11487,10 @@
       </c>
     </row>
     <row r="678" spans="1:3">
-      <c r="A678" s="4">
+      <c r="A678" s="3">
         <v>7</v>
       </c>
-      <c r="B678" s="4">
+      <c r="B678" s="3">
         <v>77</v>
       </c>
       <c r="C678" t="s">
@@ -11504,10 +11498,10 @@
       </c>
     </row>
     <row r="679" spans="1:3">
-      <c r="A679" s="4">
+      <c r="A679" s="3">
         <v>7</v>
       </c>
-      <c r="B679" s="4">
+      <c r="B679" s="3">
         <v>78</v>
       </c>
       <c r="C679" t="s">
@@ -11515,10 +11509,10 @@
       </c>
     </row>
     <row r="680" spans="1:3">
-      <c r="A680" s="4">
+      <c r="A680" s="3">
         <v>7</v>
       </c>
-      <c r="B680" s="4">
+      <c r="B680" s="3">
         <v>79</v>
       </c>
       <c r="C680" t="s">
@@ -11526,10 +11520,10 @@
       </c>
     </row>
     <row r="681" spans="1:3">
-      <c r="A681" s="4">
+      <c r="A681" s="3">
         <v>7</v>
       </c>
-      <c r="B681" s="4">
+      <c r="B681" s="3">
         <v>80</v>
       </c>
       <c r="C681" t="s">
@@ -11537,10 +11531,10 @@
       </c>
     </row>
     <row r="682" spans="1:3">
-      <c r="A682" s="4">
+      <c r="A682" s="3">
         <v>7</v>
       </c>
-      <c r="B682" s="4">
+      <c r="B682" s="3">
         <v>81</v>
       </c>
       <c r="C682" t="s">
@@ -11548,10 +11542,10 @@
       </c>
     </row>
     <row r="683" spans="1:3">
-      <c r="A683" s="4">
+      <c r="A683" s="3">
         <v>7</v>
       </c>
-      <c r="B683" s="4">
+      <c r="B683" s="3">
         <v>82</v>
       </c>
       <c r="C683" t="s">
@@ -11559,10 +11553,10 @@
       </c>
     </row>
     <row r="684" spans="1:3">
-      <c r="A684" s="4">
+      <c r="A684" s="3">
         <v>7</v>
       </c>
-      <c r="B684" s="4">
+      <c r="B684" s="3">
         <v>83</v>
       </c>
       <c r="C684" t="s">
@@ -11570,10 +11564,10 @@
       </c>
     </row>
     <row r="685" spans="1:3">
-      <c r="A685" s="4">
+      <c r="A685" s="3">
         <v>7</v>
       </c>
-      <c r="B685" s="4">
+      <c r="B685" s="3">
         <v>84</v>
       </c>
       <c r="C685" t="s">
@@ -11581,10 +11575,10 @@
       </c>
     </row>
     <row r="686" spans="1:3">
-      <c r="A686" s="4">
+      <c r="A686" s="3">
         <v>7</v>
       </c>
-      <c r="B686" s="4">
+      <c r="B686" s="3">
         <v>85</v>
       </c>
       <c r="C686" t="s">
@@ -11592,10 +11586,10 @@
       </c>
     </row>
     <row r="687" spans="1:3">
-      <c r="A687" s="4">
+      <c r="A687" s="3">
         <v>7</v>
       </c>
-      <c r="B687" s="4">
+      <c r="B687" s="3">
         <v>86</v>
       </c>
       <c r="C687" t="s">
@@ -11603,10 +11597,10 @@
       </c>
     </row>
     <row r="688" spans="1:3">
-      <c r="A688" s="4">
+      <c r="A688" s="3">
         <v>7</v>
       </c>
-      <c r="B688" s="4">
+      <c r="B688" s="3">
         <v>87</v>
       </c>
       <c r="C688" t="s">
@@ -11614,10 +11608,10 @@
       </c>
     </row>
     <row r="689" spans="1:3">
-      <c r="A689" s="4">
+      <c r="A689" s="3">
         <v>7</v>
       </c>
-      <c r="B689" s="4">
+      <c r="B689" s="3">
         <v>88</v>
       </c>
       <c r="C689" t="s">
@@ -11625,10 +11619,10 @@
       </c>
     </row>
     <row r="690" spans="1:3">
-      <c r="A690" s="4">
+      <c r="A690" s="3">
         <v>7</v>
       </c>
-      <c r="B690" s="4">
+      <c r="B690" s="3">
         <v>89</v>
       </c>
       <c r="C690" t="s">
@@ -11636,10 +11630,10 @@
       </c>
     </row>
     <row r="691" spans="1:3">
-      <c r="A691" s="4">
+      <c r="A691" s="3">
         <v>7</v>
       </c>
-      <c r="B691" s="4">
+      <c r="B691" s="3">
         <v>90</v>
       </c>
       <c r="C691" t="s">
@@ -11647,10 +11641,10 @@
       </c>
     </row>
     <row r="692" spans="1:3">
-      <c r="A692" s="4">
+      <c r="A692" s="3">
         <v>7</v>
       </c>
-      <c r="B692" s="4">
+      <c r="B692" s="3">
         <v>91</v>
       </c>
       <c r="C692" t="s">
@@ -11658,10 +11652,10 @@
       </c>
     </row>
     <row r="693" spans="1:3">
-      <c r="A693" s="4">
+      <c r="A693" s="3">
         <v>7</v>
       </c>
-      <c r="B693" s="4">
+      <c r="B693" s="3">
         <v>92</v>
       </c>
       <c r="C693" t="s">
@@ -11669,10 +11663,10 @@
       </c>
     </row>
     <row r="694" spans="1:3">
-      <c r="A694" s="4">
+      <c r="A694" s="3">
         <v>7</v>
       </c>
-      <c r="B694" s="4">
+      <c r="B694" s="3">
         <v>93</v>
       </c>
       <c r="C694" t="s">
@@ -11680,10 +11674,10 @@
       </c>
     </row>
     <row r="695" spans="1:3">
-      <c r="A695" s="4">
+      <c r="A695" s="3">
         <v>7</v>
       </c>
-      <c r="B695" s="4">
+      <c r="B695" s="3">
         <v>94</v>
       </c>
       <c r="C695" t="s">
@@ -11691,10 +11685,10 @@
       </c>
     </row>
     <row r="696" spans="1:3">
-      <c r="A696" s="4">
+      <c r="A696" s="3">
         <v>7</v>
       </c>
-      <c r="B696" s="4">
+      <c r="B696" s="3">
         <v>95</v>
       </c>
       <c r="C696" t="s">
@@ -11702,10 +11696,10 @@
       </c>
     </row>
     <row r="697" spans="1:3">
-      <c r="A697" s="4">
+      <c r="A697" s="3">
         <v>7</v>
       </c>
-      <c r="B697" s="4">
+      <c r="B697" s="3">
         <v>96</v>
       </c>
       <c r="C697" t="s">
@@ -11713,10 +11707,10 @@
       </c>
     </row>
     <row r="698" spans="1:3">
-      <c r="A698" s="4">
+      <c r="A698" s="3">
         <v>7</v>
       </c>
-      <c r="B698" s="4">
+      <c r="B698" s="3">
         <v>97</v>
       </c>
       <c r="C698" t="s">
@@ -11724,10 +11718,10 @@
       </c>
     </row>
     <row r="699" spans="1:3">
-      <c r="A699" s="4">
+      <c r="A699" s="3">
         <v>7</v>
       </c>
-      <c r="B699" s="4">
+      <c r="B699" s="3">
         <v>98</v>
       </c>
       <c r="C699" t="s">
@@ -11735,10 +11729,10 @@
       </c>
     </row>
     <row r="700" spans="1:3">
-      <c r="A700" s="4">
+      <c r="A700" s="3">
         <v>7</v>
       </c>
-      <c r="B700" s="4">
+      <c r="B700" s="3">
         <v>99</v>
       </c>
       <c r="C700" t="s">
@@ -11746,10 +11740,10 @@
       </c>
     </row>
     <row r="701" spans="1:3">
-      <c r="A701" s="4">
+      <c r="A701" s="3">
         <v>7</v>
       </c>
-      <c r="B701" s="4">
+      <c r="B701" s="3">
         <v>100</v>
       </c>
       <c r="C701" t="s">
@@ -11757,10 +11751,10 @@
       </c>
     </row>
     <row r="702" spans="1:3">
-      <c r="A702" s="4">
+      <c r="A702" s="3">
         <v>8</v>
       </c>
-      <c r="B702" s="4">
+      <c r="B702" s="3">
         <v>1</v>
       </c>
       <c r="C702" t="s">
@@ -11768,10 +11762,10 @@
       </c>
     </row>
     <row r="703" spans="1:3">
-      <c r="A703" s="4">
+      <c r="A703" s="3">
         <v>8</v>
       </c>
-      <c r="B703" s="4">
+      <c r="B703" s="3">
         <v>2</v>
       </c>
       <c r="C703" t="s">
@@ -11779,10 +11773,10 @@
       </c>
     </row>
     <row r="704" spans="1:3">
-      <c r="A704" s="4">
+      <c r="A704" s="3">
         <v>8</v>
       </c>
-      <c r="B704" s="4">
+      <c r="B704" s="3">
         <v>3</v>
       </c>
       <c r="C704" t="s">
@@ -11790,10 +11784,10 @@
       </c>
     </row>
     <row r="705" spans="1:3">
-      <c r="A705" s="4">
+      <c r="A705" s="3">
         <v>8</v>
       </c>
-      <c r="B705" s="4">
+      <c r="B705" s="3">
         <v>4</v>
       </c>
       <c r="C705" t="s">
@@ -11801,10 +11795,10 @@
       </c>
     </row>
     <row r="706" spans="1:3">
-      <c r="A706" s="4">
+      <c r="A706" s="3">
         <v>8</v>
       </c>
-      <c r="B706" s="4">
+      <c r="B706" s="3">
         <v>5</v>
       </c>
       <c r="C706" t="s">
@@ -11812,10 +11806,10 @@
       </c>
     </row>
     <row r="707" spans="1:3">
-      <c r="A707" s="4">
+      <c r="A707" s="3">
         <v>8</v>
       </c>
-      <c r="B707" s="4">
+      <c r="B707" s="3">
         <v>6</v>
       </c>
       <c r="C707" t="s">
@@ -11823,10 +11817,10 @@
       </c>
     </row>
     <row r="708" spans="1:3">
-      <c r="A708" s="4">
+      <c r="A708" s="3">
         <v>8</v>
       </c>
-      <c r="B708" s="4">
+      <c r="B708" s="3">
         <v>7</v>
       </c>
       <c r="C708" t="s">
@@ -11834,10 +11828,10 @@
       </c>
     </row>
     <row r="709" spans="1:3">
-      <c r="A709" s="4">
+      <c r="A709" s="3">
         <v>8</v>
       </c>
-      <c r="B709" s="4">
+      <c r="B709" s="3">
         <v>8</v>
       </c>
       <c r="C709" t="s">
@@ -11845,10 +11839,10 @@
       </c>
     </row>
     <row r="710" spans="1:3">
-      <c r="A710" s="4">
+      <c r="A710" s="3">
         <v>8</v>
       </c>
-      <c r="B710" s="4">
+      <c r="B710" s="3">
         <v>9</v>
       </c>
       <c r="C710" t="s">
@@ -11856,10 +11850,10 @@
       </c>
     </row>
     <row r="711" spans="1:3">
-      <c r="A711" s="4">
+      <c r="A711" s="3">
         <v>8</v>
       </c>
-      <c r="B711" s="4">
+      <c r="B711" s="3">
         <v>10</v>
       </c>
       <c r="C711" t="s">
@@ -11867,10 +11861,10 @@
       </c>
     </row>
     <row r="712" spans="1:3">
-      <c r="A712" s="4">
+      <c r="A712" s="3">
         <v>8</v>
       </c>
-      <c r="B712" s="4">
+      <c r="B712" s="3">
         <v>11</v>
       </c>
       <c r="C712" t="s">
@@ -11878,10 +11872,10 @@
       </c>
     </row>
     <row r="713" spans="1:3">
-      <c r="A713" s="4">
+      <c r="A713" s="3">
         <v>8</v>
       </c>
-      <c r="B713" s="4">
+      <c r="B713" s="3">
         <v>12</v>
       </c>
       <c r="C713" t="s">
@@ -11889,10 +11883,10 @@
       </c>
     </row>
     <row r="714" spans="1:3">
-      <c r="A714" s="4">
+      <c r="A714" s="3">
         <v>8</v>
       </c>
-      <c r="B714" s="4">
+      <c r="B714" s="3">
         <v>13</v>
       </c>
       <c r="C714" t="s">
@@ -11900,10 +11894,10 @@
       </c>
     </row>
     <row r="715" spans="1:3">
-      <c r="A715" s="4">
+      <c r="A715" s="3">
         <v>8</v>
       </c>
-      <c r="B715" s="4">
+      <c r="B715" s="3">
         <v>14</v>
       </c>
       <c r="C715" t="s">
@@ -11911,10 +11905,10 @@
       </c>
     </row>
     <row r="716" spans="1:3">
-      <c r="A716" s="4">
+      <c r="A716" s="3">
         <v>8</v>
       </c>
-      <c r="B716" s="4">
+      <c r="B716" s="3">
         <v>15</v>
       </c>
       <c r="C716" t="s">
@@ -11922,10 +11916,10 @@
       </c>
     </row>
     <row r="717" spans="1:3">
-      <c r="A717" s="4">
+      <c r="A717" s="3">
         <v>8</v>
       </c>
-      <c r="B717" s="4">
+      <c r="B717" s="3">
         <v>16</v>
       </c>
       <c r="C717" t="s">
@@ -11933,10 +11927,10 @@
       </c>
     </row>
     <row r="718" spans="1:3">
-      <c r="A718" s="4">
+      <c r="A718" s="3">
         <v>8</v>
       </c>
-      <c r="B718" s="4">
+      <c r="B718" s="3">
         <v>17</v>
       </c>
       <c r="C718" t="s">
@@ -11944,10 +11938,10 @@
       </c>
     </row>
     <row r="719" spans="1:3">
-      <c r="A719" s="4">
+      <c r="A719" s="3">
         <v>8</v>
       </c>
-      <c r="B719" s="4">
+      <c r="B719" s="3">
         <v>18</v>
       </c>
       <c r="C719" t="s">
@@ -11955,10 +11949,10 @@
       </c>
     </row>
     <row r="720" spans="1:3">
-      <c r="A720" s="4">
+      <c r="A720" s="3">
         <v>8</v>
       </c>
-      <c r="B720" s="4">
+      <c r="B720" s="3">
         <v>19</v>
       </c>
       <c r="C720" t="s">
@@ -11966,10 +11960,10 @@
       </c>
     </row>
     <row r="721" spans="1:3">
-      <c r="A721" s="4">
+      <c r="A721" s="3">
         <v>8</v>
       </c>
-      <c r="B721" s="4">
+      <c r="B721" s="3">
         <v>20</v>
       </c>
       <c r="C721" t="s">
@@ -11977,10 +11971,10 @@
       </c>
     </row>
     <row r="722" spans="1:3">
-      <c r="A722" s="4">
+      <c r="A722" s="3">
         <v>8</v>
       </c>
-      <c r="B722" s="4">
+      <c r="B722" s="3">
         <v>21</v>
       </c>
       <c r="C722" t="s">
@@ -11988,10 +11982,10 @@
       </c>
     </row>
     <row r="723" spans="1:3">
-      <c r="A723" s="4">
+      <c r="A723" s="3">
         <v>8</v>
       </c>
-      <c r="B723" s="4">
+      <c r="B723" s="3">
         <v>22</v>
       </c>
       <c r="C723" t="s">
@@ -11999,10 +11993,10 @@
       </c>
     </row>
     <row r="724" spans="1:3">
-      <c r="A724" s="4">
+      <c r="A724" s="3">
         <v>8</v>
       </c>
-      <c r="B724" s="4">
+      <c r="B724" s="3">
         <v>23</v>
       </c>
       <c r="C724" t="s">
@@ -12010,10 +12004,10 @@
       </c>
     </row>
     <row r="725" spans="1:3">
-      <c r="A725" s="4">
+      <c r="A725" s="3">
         <v>8</v>
       </c>
-      <c r="B725" s="4">
+      <c r="B725" s="3">
         <v>24</v>
       </c>
       <c r="C725" t="s">
@@ -12021,10 +12015,10 @@
       </c>
     </row>
     <row r="726" spans="1:3">
-      <c r="A726" s="4">
+      <c r="A726" s="3">
         <v>8</v>
       </c>
-      <c r="B726" s="4">
+      <c r="B726" s="3">
         <v>25</v>
       </c>
       <c r="C726" t="s">
@@ -12032,10 +12026,10 @@
       </c>
     </row>
     <row r="727" spans="1:3">
-      <c r="A727" s="4">
+      <c r="A727" s="3">
         <v>8</v>
       </c>
-      <c r="B727" s="4">
+      <c r="B727" s="3">
         <v>26</v>
       </c>
       <c r="C727" t="s">
@@ -12043,10 +12037,10 @@
       </c>
     </row>
     <row r="728" spans="1:3">
-      <c r="A728" s="4">
+      <c r="A728" s="3">
         <v>8</v>
       </c>
-      <c r="B728" s="4">
+      <c r="B728" s="3">
         <v>27</v>
       </c>
       <c r="C728" t="s">
@@ -12054,10 +12048,10 @@
       </c>
     </row>
     <row r="729" spans="1:3">
-      <c r="A729" s="4">
+      <c r="A729" s="3">
         <v>8</v>
       </c>
-      <c r="B729" s="4">
+      <c r="B729" s="3">
         <v>28</v>
       </c>
       <c r="C729" t="s">
@@ -12065,10 +12059,10 @@
       </c>
     </row>
     <row r="730" spans="1:3">
-      <c r="A730" s="4">
+      <c r="A730" s="3">
         <v>8</v>
       </c>
-      <c r="B730" s="4">
+      <c r="B730" s="3">
         <v>29</v>
       </c>
       <c r="C730" t="s">
@@ -12076,10 +12070,10 @@
       </c>
     </row>
     <row r="731" spans="1:3">
-      <c r="A731" s="4">
+      <c r="A731" s="3">
         <v>8</v>
       </c>
-      <c r="B731" s="4">
+      <c r="B731" s="3">
         <v>30</v>
       </c>
       <c r="C731" t="s">
@@ -12087,10 +12081,10 @@
       </c>
     </row>
     <row r="732" spans="1:3">
-      <c r="A732" s="4">
+      <c r="A732" s="3">
         <v>8</v>
       </c>
-      <c r="B732" s="4">
+      <c r="B732" s="3">
         <v>31</v>
       </c>
       <c r="C732" t="s">
@@ -12098,10 +12092,10 @@
       </c>
     </row>
     <row r="733" spans="1:3">
-      <c r="A733" s="4">
+      <c r="A733" s="3">
         <v>8</v>
       </c>
-      <c r="B733" s="4">
+      <c r="B733" s="3">
         <v>32</v>
       </c>
       <c r="C733" t="s">
@@ -12109,10 +12103,10 @@
       </c>
     </row>
     <row r="734" spans="1:3">
-      <c r="A734" s="4">
+      <c r="A734" s="3">
         <v>8</v>
       </c>
-      <c r="B734" s="4">
+      <c r="B734" s="3">
         <v>33</v>
       </c>
       <c r="C734" t="s">
@@ -12120,10 +12114,10 @@
       </c>
     </row>
     <row r="735" spans="1:3">
-      <c r="A735" s="4">
+      <c r="A735" s="3">
         <v>8</v>
       </c>
-      <c r="B735" s="4">
+      <c r="B735" s="3">
         <v>34</v>
       </c>
       <c r="C735" t="s">
@@ -12131,10 +12125,10 @@
       </c>
     </row>
     <row r="736" spans="1:3">
-      <c r="A736" s="4">
+      <c r="A736" s="3">
         <v>8</v>
       </c>
-      <c r="B736" s="4">
+      <c r="B736" s="3">
         <v>35</v>
       </c>
       <c r="C736" t="s">
@@ -12142,10 +12136,10 @@
       </c>
     </row>
     <row r="737" spans="1:3">
-      <c r="A737" s="4">
+      <c r="A737" s="3">
         <v>8</v>
       </c>
-      <c r="B737" s="4">
+      <c r="B737" s="3">
         <v>36</v>
       </c>
       <c r="C737" t="s">
@@ -12153,10 +12147,10 @@
       </c>
     </row>
     <row r="738" spans="1:3">
-      <c r="A738" s="4">
+      <c r="A738" s="3">
         <v>8</v>
       </c>
-      <c r="B738" s="4">
+      <c r="B738" s="3">
         <v>37</v>
       </c>
       <c r="C738" t="s">
@@ -12164,10 +12158,10 @@
       </c>
     </row>
     <row r="739" spans="1:3">
-      <c r="A739" s="4">
+      <c r="A739" s="3">
         <v>8</v>
       </c>
-      <c r="B739" s="4">
+      <c r="B739" s="3">
         <v>38</v>
       </c>
       <c r="C739" t="s">
@@ -12175,10 +12169,10 @@
       </c>
     </row>
     <row r="740" spans="1:3">
-      <c r="A740" s="4">
+      <c r="A740" s="3">
         <v>8</v>
       </c>
-      <c r="B740" s="4">
+      <c r="B740" s="3">
         <v>39</v>
       </c>
       <c r="C740" t="s">
@@ -12186,10 +12180,10 @@
       </c>
     </row>
     <row r="741" spans="1:3">
-      <c r="A741" s="4">
+      <c r="A741" s="3">
         <v>8</v>
       </c>
-      <c r="B741" s="4">
+      <c r="B741" s="3">
         <v>40</v>
       </c>
       <c r="C741" t="s">
@@ -12197,10 +12191,10 @@
       </c>
     </row>
     <row r="742" spans="1:3">
-      <c r="A742" s="4">
+      <c r="A742" s="3">
         <v>8</v>
       </c>
-      <c r="B742" s="4">
+      <c r="B742" s="3">
         <v>41</v>
       </c>
       <c r="C742" t="s">
@@ -12208,10 +12202,10 @@
       </c>
     </row>
     <row r="743" spans="1:3">
-      <c r="A743" s="4">
+      <c r="A743" s="3">
         <v>8</v>
       </c>
-      <c r="B743" s="4">
+      <c r="B743" s="3">
         <v>42</v>
       </c>
       <c r="C743" t="s">
@@ -12219,10 +12213,10 @@
       </c>
     </row>
     <row r="744" spans="1:3">
-      <c r="A744" s="4">
+      <c r="A744" s="3">
         <v>8</v>
       </c>
-      <c r="B744" s="4">
+      <c r="B744" s="3">
         <v>43</v>
       </c>
       <c r="C744" t="s">
@@ -12230,10 +12224,10 @@
       </c>
     </row>
     <row r="745" spans="1:3">
-      <c r="A745" s="4">
+      <c r="A745" s="3">
         <v>8</v>
       </c>
-      <c r="B745" s="4">
+      <c r="B745" s="3">
         <v>44</v>
       </c>
       <c r="C745" t="s">
@@ -12241,10 +12235,10 @@
       </c>
     </row>
     <row r="746" spans="1:3">
-      <c r="A746" s="4">
+      <c r="A746" s="3">
         <v>8</v>
       </c>
-      <c r="B746" s="4">
+      <c r="B746" s="3">
         <v>45</v>
       </c>
       <c r="C746" t="s">
@@ -12252,10 +12246,10 @@
       </c>
     </row>
     <row r="747" spans="1:3">
-      <c r="A747" s="4">
+      <c r="A747" s="3">
         <v>8</v>
       </c>
-      <c r="B747" s="4">
+      <c r="B747" s="3">
         <v>46</v>
       </c>
       <c r="C747" t="s">
@@ -12263,10 +12257,10 @@
       </c>
     </row>
     <row r="748" spans="1:3">
-      <c r="A748" s="4">
+      <c r="A748" s="3">
         <v>8</v>
       </c>
-      <c r="B748" s="4">
+      <c r="B748" s="3">
         <v>47</v>
       </c>
       <c r="C748" t="s">
@@ -12274,10 +12268,10 @@
       </c>
     </row>
     <row r="749" spans="1:3">
-      <c r="A749" s="4">
+      <c r="A749" s="3">
         <v>8</v>
       </c>
-      <c r="B749" s="4">
+      <c r="B749" s="3">
         <v>48</v>
       </c>
       <c r="C749" t="s">
@@ -12285,10 +12279,10 @@
       </c>
     </row>
     <row r="750" spans="1:3">
-      <c r="A750" s="4">
+      <c r="A750" s="3">
         <v>8</v>
       </c>
-      <c r="B750" s="4">
+      <c r="B750" s="3">
         <v>49</v>
       </c>
       <c r="C750" t="s">
@@ -12296,10 +12290,10 @@
       </c>
     </row>
     <row r="751" spans="1:3">
-      <c r="A751" s="4">
+      <c r="A751" s="3">
         <v>8</v>
       </c>
-      <c r="B751" s="4">
+      <c r="B751" s="3">
         <v>50</v>
       </c>
       <c r="C751" t="s">
@@ -12307,10 +12301,10 @@
       </c>
     </row>
     <row r="752" spans="1:3">
-      <c r="A752" s="4">
+      <c r="A752" s="3">
         <v>8</v>
       </c>
-      <c r="B752" s="4">
+      <c r="B752" s="3">
         <v>51</v>
       </c>
       <c r="C752" t="s">
@@ -12318,10 +12312,10 @@
       </c>
     </row>
     <row r="753" spans="1:3">
-      <c r="A753" s="4">
+      <c r="A753" s="3">
         <v>8</v>
       </c>
-      <c r="B753" s="4">
+      <c r="B753" s="3">
         <v>52</v>
       </c>
       <c r="C753" t="s">
@@ -12329,10 +12323,10 @@
       </c>
     </row>
     <row r="754" spans="1:3">
-      <c r="A754" s="4">
+      <c r="A754" s="3">
         <v>8</v>
       </c>
-      <c r="B754" s="4">
+      <c r="B754" s="3">
         <v>53</v>
       </c>
       <c r="C754" t="s">
@@ -12340,10 +12334,10 @@
       </c>
     </row>
     <row r="755" spans="1:3">
-      <c r="A755" s="4">
+      <c r="A755" s="3">
         <v>8</v>
       </c>
-      <c r="B755" s="4">
+      <c r="B755" s="3">
         <v>54</v>
       </c>
       <c r="C755" t="s">
@@ -12351,10 +12345,10 @@
       </c>
     </row>
     <row r="756" spans="1:3">
-      <c r="A756" s="4">
+      <c r="A756" s="3">
         <v>8</v>
       </c>
-      <c r="B756" s="4">
+      <c r="B756" s="3">
         <v>55</v>
       </c>
       <c r="C756" t="s">
@@ -12362,10 +12356,10 @@
       </c>
     </row>
     <row r="757" spans="1:3">
-      <c r="A757" s="4">
+      <c r="A757" s="3">
         <v>8</v>
       </c>
-      <c r="B757" s="4">
+      <c r="B757" s="3">
         <v>56</v>
       </c>
       <c r="C757" t="s">
@@ -12373,10 +12367,10 @@
       </c>
     </row>
     <row r="758" spans="1:3">
-      <c r="A758" s="4">
+      <c r="A758" s="3">
         <v>8</v>
       </c>
-      <c r="B758" s="4">
+      <c r="B758" s="3">
         <v>57</v>
       </c>
       <c r="C758" t="s">
@@ -12384,10 +12378,10 @@
       </c>
     </row>
     <row r="759" spans="1:3">
-      <c r="A759" s="4">
+      <c r="A759" s="3">
         <v>8</v>
       </c>
-      <c r="B759" s="4">
+      <c r="B759" s="3">
         <v>58</v>
       </c>
       <c r="C759" t="s">
@@ -12395,10 +12389,10 @@
       </c>
     </row>
     <row r="760" spans="1:3">
-      <c r="A760" s="4">
+      <c r="A760" s="3">
         <v>8</v>
       </c>
-      <c r="B760" s="4">
+      <c r="B760" s="3">
         <v>59</v>
       </c>
       <c r="C760" t="s">
@@ -12406,10 +12400,10 @@
       </c>
     </row>
     <row r="761" spans="1:3">
-      <c r="A761" s="4">
+      <c r="A761" s="3">
         <v>8</v>
       </c>
-      <c r="B761" s="4">
+      <c r="B761" s="3">
         <v>60</v>
       </c>
       <c r="C761" t="s">
@@ -12417,10 +12411,10 @@
       </c>
     </row>
     <row r="762" spans="1:3">
-      <c r="A762" s="4">
+      <c r="A762" s="3">
         <v>8</v>
       </c>
-      <c r="B762" s="4">
+      <c r="B762" s="3">
         <v>61</v>
       </c>
       <c r="C762" t="s">
@@ -12428,10 +12422,10 @@
       </c>
     </row>
     <row r="763" spans="1:3">
-      <c r="A763" s="4">
+      <c r="A763" s="3">
         <v>8</v>
       </c>
-      <c r="B763" s="4">
+      <c r="B763" s="3">
         <v>62</v>
       </c>
       <c r="C763" t="s">
@@ -12439,10 +12433,10 @@
       </c>
     </row>
     <row r="764" spans="1:3">
-      <c r="A764" s="4">
+      <c r="A764" s="3">
         <v>8</v>
       </c>
-      <c r="B764" s="4">
+      <c r="B764" s="3">
         <v>63</v>
       </c>
       <c r="C764" t="s">
@@ -12450,10 +12444,10 @@
       </c>
     </row>
     <row r="765" spans="1:3">
-      <c r="A765" s="4">
+      <c r="A765" s="3">
         <v>8</v>
       </c>
-      <c r="B765" s="4">
+      <c r="B765" s="3">
         <v>64</v>
       </c>
       <c r="C765" t="s">
@@ -12461,10 +12455,10 @@
       </c>
     </row>
     <row r="766" spans="1:3">
-      <c r="A766" s="4">
+      <c r="A766" s="3">
         <v>8</v>
       </c>
-      <c r="B766" s="4">
+      <c r="B766" s="3">
         <v>65</v>
       </c>
       <c r="C766" t="s">
@@ -12472,10 +12466,10 @@
       </c>
     </row>
     <row r="767" spans="1:3">
-      <c r="A767" s="4">
+      <c r="A767" s="3">
         <v>8</v>
       </c>
-      <c r="B767" s="4">
+      <c r="B767" s="3">
         <v>66</v>
       </c>
       <c r="C767" t="s">
@@ -12483,10 +12477,10 @@
       </c>
     </row>
     <row r="768" spans="1:3">
-      <c r="A768" s="4">
+      <c r="A768" s="3">
         <v>8</v>
       </c>
-      <c r="B768" s="4">
+      <c r="B768" s="3">
         <v>67</v>
       </c>
       <c r="C768" t="s">
@@ -12494,10 +12488,10 @@
       </c>
     </row>
     <row r="769" spans="1:3">
-      <c r="A769" s="4">
+      <c r="A769" s="3">
         <v>8</v>
       </c>
-      <c r="B769" s="4">
+      <c r="B769" s="3">
         <v>68</v>
       </c>
       <c r="C769" t="s">
@@ -12505,10 +12499,10 @@
       </c>
     </row>
     <row r="770" spans="1:3">
-      <c r="A770" s="4">
+      <c r="A770" s="3">
         <v>8</v>
       </c>
-      <c r="B770" s="4">
+      <c r="B770" s="3">
         <v>69</v>
       </c>
       <c r="C770" t="s">
@@ -12516,10 +12510,10 @@
       </c>
     </row>
     <row r="771" spans="1:3">
-      <c r="A771" s="4">
+      <c r="A771" s="3">
         <v>8</v>
       </c>
-      <c r="B771" s="4">
+      <c r="B771" s="3">
         <v>70</v>
       </c>
       <c r="C771" t="s">
@@ -12527,10 +12521,10 @@
       </c>
     </row>
     <row r="772" spans="1:3">
-      <c r="A772" s="4">
+      <c r="A772" s="3">
         <v>8</v>
       </c>
-      <c r="B772" s="4">
+      <c r="B772" s="3">
         <v>71</v>
       </c>
       <c r="C772" t="s">
@@ -12538,10 +12532,10 @@
       </c>
     </row>
     <row r="773" spans="1:3">
-      <c r="A773" s="4">
+      <c r="A773" s="3">
         <v>8</v>
       </c>
-      <c r="B773" s="4">
+      <c r="B773" s="3">
         <v>72</v>
       </c>
       <c r="C773" t="s">
@@ -12549,10 +12543,10 @@
       </c>
     </row>
     <row r="774" spans="1:3">
-      <c r="A774" s="4">
+      <c r="A774" s="3">
         <v>8</v>
       </c>
-      <c r="B774" s="4">
+      <c r="B774" s="3">
         <v>73</v>
       </c>
       <c r="C774" t="s">
@@ -12560,10 +12554,10 @@
       </c>
     </row>
     <row r="775" spans="1:3">
-      <c r="A775" s="4">
+      <c r="A775" s="3">
         <v>8</v>
       </c>
-      <c r="B775" s="4">
+      <c r="B775" s="3">
         <v>74</v>
       </c>
       <c r="C775" t="s">
@@ -12571,10 +12565,10 @@
       </c>
     </row>
     <row r="776" spans="1:3">
-      <c r="A776" s="4">
+      <c r="A776" s="3">
         <v>8</v>
       </c>
-      <c r="B776" s="4">
+      <c r="B776" s="3">
         <v>75</v>
       </c>
       <c r="C776" t="s">
@@ -12582,10 +12576,10 @@
       </c>
     </row>
     <row r="777" spans="1:3">
-      <c r="A777" s="4">
+      <c r="A777" s="3">
         <v>8</v>
       </c>
-      <c r="B777" s="4">
+      <c r="B777" s="3">
         <v>76</v>
       </c>
       <c r="C777" t="s">
@@ -12593,10 +12587,10 @@
       </c>
     </row>
     <row r="778" spans="1:3">
-      <c r="A778" s="4">
+      <c r="A778" s="3">
         <v>8</v>
       </c>
-      <c r="B778" s="4">
+      <c r="B778" s="3">
         <v>77</v>
       </c>
       <c r="C778" t="s">
@@ -12604,10 +12598,10 @@
       </c>
     </row>
     <row r="779" spans="1:3">
-      <c r="A779" s="4">
+      <c r="A779" s="3">
         <v>8</v>
       </c>
-      <c r="B779" s="4">
+      <c r="B779" s="3">
         <v>78</v>
       </c>
       <c r="C779" t="s">
@@ -12615,10 +12609,10 @@
       </c>
     </row>
     <row r="780" spans="1:3">
-      <c r="A780" s="4">
+      <c r="A780" s="3">
         <v>8</v>
       </c>
-      <c r="B780" s="4">
+      <c r="B780" s="3">
         <v>79</v>
       </c>
       <c r="C780" t="s">
@@ -12626,10 +12620,10 @@
       </c>
     </row>
     <row r="781" spans="1:3">
-      <c r="A781" s="4">
+      <c r="A781" s="3">
         <v>8</v>
       </c>
-      <c r="B781" s="4">
+      <c r="B781" s="3">
         <v>80</v>
       </c>
       <c r="C781" t="s">
@@ -12637,10 +12631,10 @@
       </c>
     </row>
     <row r="782" spans="1:3">
-      <c r="A782" s="4">
+      <c r="A782" s="3">
         <v>8</v>
       </c>
-      <c r="B782" s="4">
+      <c r="B782" s="3">
         <v>81</v>
       </c>
       <c r="C782" t="s">
@@ -12648,10 +12642,10 @@
       </c>
     </row>
     <row r="783" spans="1:3">
-      <c r="A783" s="4">
+      <c r="A783" s="3">
         <v>8</v>
       </c>
-      <c r="B783" s="4">
+      <c r="B783" s="3">
         <v>82</v>
       </c>
       <c r="C783" t="s">
@@ -12659,10 +12653,10 @@
       </c>
     </row>
     <row r="784" spans="1:3">
-      <c r="A784" s="4">
+      <c r="A784" s="3">
         <v>8</v>
       </c>
-      <c r="B784" s="4">
+      <c r="B784" s="3">
         <v>83</v>
       </c>
       <c r="C784" t="s">
@@ -12670,10 +12664,10 @@
       </c>
     </row>
     <row r="785" spans="1:3">
-      <c r="A785" s="4">
+      <c r="A785" s="3">
         <v>8</v>
       </c>
-      <c r="B785" s="4">
+      <c r="B785" s="3">
         <v>84</v>
       </c>
       <c r="C785" t="s">
@@ -12681,10 +12675,10 @@
       </c>
     </row>
     <row r="786" spans="1:3">
-      <c r="A786" s="4">
+      <c r="A786" s="3">
         <v>8</v>
       </c>
-      <c r="B786" s="4">
+      <c r="B786" s="3">
         <v>85</v>
       </c>
       <c r="C786" t="s">
@@ -12692,10 +12686,10 @@
       </c>
     </row>
     <row r="787" spans="1:3">
-      <c r="A787" s="4">
+      <c r="A787" s="3">
         <v>8</v>
       </c>
-      <c r="B787" s="4">
+      <c r="B787" s="3">
         <v>86</v>
       </c>
       <c r="C787" t="s">
@@ -12703,10 +12697,10 @@
       </c>
     </row>
     <row r="788" spans="1:3">
-      <c r="A788" s="4">
+      <c r="A788" s="3">
         <v>8</v>
       </c>
-      <c r="B788" s="4">
+      <c r="B788" s="3">
         <v>87</v>
       </c>
       <c r="C788" t="s">
@@ -12714,10 +12708,10 @@
       </c>
     </row>
     <row r="789" spans="1:3">
-      <c r="A789" s="4">
+      <c r="A789" s="3">
         <v>8</v>
       </c>
-      <c r="B789" s="4">
+      <c r="B789" s="3">
         <v>88</v>
       </c>
       <c r="C789" t="s">
@@ -12725,10 +12719,10 @@
       </c>
     </row>
     <row r="790" spans="1:3">
-      <c r="A790" s="4">
+      <c r="A790" s="3">
         <v>8</v>
       </c>
-      <c r="B790" s="4">
+      <c r="B790" s="3">
         <v>89</v>
       </c>
       <c r="C790" t="s">
@@ -12736,10 +12730,10 @@
       </c>
     </row>
     <row r="791" spans="1:3">
-      <c r="A791" s="4">
+      <c r="A791" s="3">
         <v>8</v>
       </c>
-      <c r="B791" s="4">
+      <c r="B791" s="3">
         <v>90</v>
       </c>
       <c r="C791" t="s">
@@ -12747,10 +12741,10 @@
       </c>
     </row>
     <row r="792" spans="1:3">
-      <c r="A792" s="4">
+      <c r="A792" s="3">
         <v>8</v>
       </c>
-      <c r="B792" s="4">
+      <c r="B792" s="3">
         <v>91</v>
       </c>
       <c r="C792" t="s">
@@ -12758,10 +12752,10 @@
       </c>
     </row>
     <row r="793" spans="1:3">
-      <c r="A793" s="4">
+      <c r="A793" s="3">
         <v>8</v>
       </c>
-      <c r="B793" s="4">
+      <c r="B793" s="3">
         <v>92</v>
       </c>
       <c r="C793" t="s">
@@ -12769,10 +12763,10 @@
       </c>
     </row>
     <row r="794" spans="1:3">
-      <c r="A794" s="4">
+      <c r="A794" s="3">
         <v>8</v>
       </c>
-      <c r="B794" s="4">
+      <c r="B794" s="3">
         <v>93</v>
       </c>
       <c r="C794" t="s">
@@ -12780,10 +12774,10 @@
       </c>
     </row>
     <row r="795" spans="1:3">
-      <c r="A795" s="4">
+      <c r="A795" s="3">
         <v>8</v>
       </c>
-      <c r="B795" s="4">
+      <c r="B795" s="3">
         <v>94</v>
       </c>
       <c r="C795" t="s">
@@ -12791,10 +12785,10 @@
       </c>
     </row>
     <row r="796" spans="1:3">
-      <c r="A796" s="4">
+      <c r="A796" s="3">
         <v>8</v>
       </c>
-      <c r="B796" s="4">
+      <c r="B796" s="3">
         <v>95</v>
       </c>
       <c r="C796" t="s">
@@ -12802,10 +12796,10 @@
       </c>
     </row>
     <row r="797" spans="1:3">
-      <c r="A797" s="4">
+      <c r="A797" s="3">
         <v>8</v>
       </c>
-      <c r="B797" s="4">
+      <c r="B797" s="3">
         <v>96</v>
       </c>
       <c r="C797" t="s">
@@ -12813,10 +12807,10 @@
       </c>
     </row>
     <row r="798" spans="1:3">
-      <c r="A798" s="4">
+      <c r="A798" s="3">
         <v>8</v>
       </c>
-      <c r="B798" s="4">
+      <c r="B798" s="3">
         <v>97</v>
       </c>
       <c r="C798" t="s">
@@ -12824,10 +12818,10 @@
       </c>
     </row>
     <row r="799" spans="1:3">
-      <c r="A799" s="4">
+      <c r="A799" s="3">
         <v>8</v>
       </c>
-      <c r="B799" s="4">
+      <c r="B799" s="3">
         <v>98</v>
       </c>
       <c r="C799" t="s">
@@ -12835,10 +12829,10 @@
       </c>
     </row>
     <row r="800" spans="1:3">
-      <c r="A800" s="4">
+      <c r="A800" s="3">
         <v>8</v>
       </c>
-      <c r="B800" s="4">
+      <c r="B800" s="3">
         <v>99</v>
       </c>
       <c r="C800" t="s">
@@ -12846,10 +12840,10 @@
       </c>
     </row>
     <row r="801" spans="1:3">
-      <c r="A801" s="4">
+      <c r="A801" s="3">
         <v>8</v>
       </c>
-      <c r="B801" s="4">
+      <c r="B801" s="3">
         <v>100</v>
       </c>
       <c r="C801" t="s">
@@ -12857,10 +12851,10 @@
       </c>
     </row>
     <row r="802" spans="1:3">
-      <c r="A802" s="4">
+      <c r="A802" s="3">
         <v>9</v>
       </c>
-      <c r="B802" s="4">
+      <c r="B802" s="3">
         <v>1</v>
       </c>
       <c r="C802" t="s">
@@ -12868,10 +12862,10 @@
       </c>
     </row>
     <row r="803" spans="1:3">
-      <c r="A803" s="4">
+      <c r="A803" s="3">
         <v>9</v>
       </c>
-      <c r="B803" s="4">
+      <c r="B803" s="3">
         <v>2</v>
       </c>
       <c r="C803" t="s">
@@ -12879,10 +12873,10 @@
       </c>
     </row>
     <row r="804" spans="1:3">
-      <c r="A804" s="4">
+      <c r="A804" s="3">
         <v>9</v>
       </c>
-      <c r="B804" s="4">
+      <c r="B804" s="3">
         <v>3</v>
       </c>
       <c r="C804" t="s">
@@ -12890,10 +12884,10 @@
       </c>
     </row>
     <row r="805" spans="1:3">
-      <c r="A805" s="4">
+      <c r="A805" s="3">
         <v>9</v>
       </c>
-      <c r="B805" s="4">
+      <c r="B805" s="3">
         <v>4</v>
       </c>
       <c r="C805" t="s">
@@ -12901,10 +12895,10 @@
       </c>
     </row>
     <row r="806" spans="1:3">
-      <c r="A806" s="4">
+      <c r="A806" s="3">
         <v>9</v>
       </c>
-      <c r="B806" s="4">
+      <c r="B806" s="3">
         <v>5</v>
       </c>
       <c r="C806" t="s">
@@ -12912,10 +12906,10 @@
       </c>
     </row>
     <row r="807" spans="1:3">
-      <c r="A807" s="4">
+      <c r="A807" s="3">
         <v>9</v>
       </c>
-      <c r="B807" s="4">
+      <c r="B807" s="3">
         <v>6</v>
       </c>
       <c r="C807" t="s">
@@ -12923,10 +12917,10 @@
       </c>
     </row>
     <row r="808" spans="1:3">
-      <c r="A808" s="4">
+      <c r="A808" s="3">
         <v>9</v>
       </c>
-      <c r="B808" s="4">
+      <c r="B808" s="3">
         <v>7</v>
       </c>
       <c r="C808" t="s">
@@ -12934,10 +12928,10 @@
       </c>
     </row>
     <row r="809" spans="1:3">
-      <c r="A809" s="4">
+      <c r="A809" s="3">
         <v>9</v>
       </c>
-      <c r="B809" s="4">
+      <c r="B809" s="3">
         <v>8</v>
       </c>
       <c r="C809" t="s">
@@ -12945,10 +12939,10 @@
       </c>
     </row>
     <row r="810" spans="1:3">
-      <c r="A810" s="4">
+      <c r="A810" s="3">
         <v>9</v>
       </c>
-      <c r="B810" s="4">
+      <c r="B810" s="3">
         <v>9</v>
       </c>
       <c r="C810" t="s">
@@ -12956,10 +12950,10 @@
       </c>
     </row>
     <row r="811" spans="1:3">
-      <c r="A811" s="4">
+      <c r="A811" s="3">
         <v>9</v>
       </c>
-      <c r="B811" s="4">
+      <c r="B811" s="3">
         <v>10</v>
       </c>
       <c r="C811" t="s">
@@ -12967,10 +12961,10 @@
       </c>
     </row>
     <row r="812" spans="1:3">
-      <c r="A812" s="4">
+      <c r="A812" s="3">
         <v>9</v>
       </c>
-      <c r="B812" s="4">
+      <c r="B812" s="3">
         <v>11</v>
       </c>
       <c r="C812" t="s">
@@ -12978,10 +12972,10 @@
       </c>
     </row>
     <row r="813" spans="1:3">
-      <c r="A813" s="4">
+      <c r="A813" s="3">
         <v>9</v>
       </c>
-      <c r="B813" s="4">
+      <c r="B813" s="3">
         <v>12</v>
       </c>
       <c r="C813" t="s">
@@ -12989,10 +12983,10 @@
       </c>
     </row>
     <row r="814" spans="1:3">
-      <c r="A814" s="4">
+      <c r="A814" s="3">
         <v>9</v>
       </c>
-      <c r="B814" s="4">
+      <c r="B814" s="3">
         <v>13</v>
       </c>
       <c r="C814" t="s">
@@ -13000,10 +12994,10 @@
       </c>
     </row>
     <row r="815" spans="1:3">
-      <c r="A815" s="4">
+      <c r="A815" s="3">
         <v>9</v>
       </c>
-      <c r="B815" s="4">
+      <c r="B815" s="3">
         <v>14</v>
       </c>
       <c r="C815" t="s">
@@ -13011,10 +13005,10 @@
       </c>
     </row>
     <row r="816" spans="1:3">
-      <c r="A816" s="4">
+      <c r="A816" s="3">
         <v>9</v>
       </c>
-      <c r="B816" s="4">
+      <c r="B816" s="3">
         <v>15</v>
       </c>
       <c r="C816" t="s">
@@ -13022,10 +13016,10 @@
       </c>
     </row>
     <row r="817" spans="1:3">
-      <c r="A817" s="4">
+      <c r="A817" s="3">
         <v>9</v>
       </c>
-      <c r="B817" s="4">
+      <c r="B817" s="3">
         <v>16</v>
       </c>
       <c r="C817" t="s">
@@ -13033,10 +13027,10 @@
       </c>
     </row>
     <row r="818" spans="1:3">
-      <c r="A818" s="4">
+      <c r="A818" s="3">
         <v>9</v>
       </c>
-      <c r="B818" s="4">
+      <c r="B818" s="3">
         <v>17</v>
       </c>
       <c r="C818" t="s">
@@ -13044,10 +13038,10 @@
       </c>
     </row>
     <row r="819" spans="1:3">
-      <c r="A819" s="4">
+      <c r="A819" s="3">
         <v>9</v>
       </c>
-      <c r="B819" s="4">
+      <c r="B819" s="3">
         <v>18</v>
       </c>
       <c r="C819" t="s">
@@ -13055,10 +13049,10 @@
       </c>
     </row>
     <row r="820" spans="1:3">
-      <c r="A820" s="4">
+      <c r="A820" s="3">
         <v>9</v>
       </c>
-      <c r="B820" s="4">
+      <c r="B820" s="3">
         <v>19</v>
       </c>
       <c r="C820" t="s">
@@ -13066,10 +13060,10 @@
       </c>
     </row>
     <row r="821" spans="1:3">
-      <c r="A821" s="4">
+      <c r="A821" s="3">
         <v>9</v>
       </c>
-      <c r="B821" s="4">
+      <c r="B821" s="3">
         <v>20</v>
       </c>
       <c r="C821" t="s">
@@ -13077,10 +13071,10 @@
       </c>
     </row>
     <row r="822" spans="1:3">
-      <c r="A822" s="4">
+      <c r="A822" s="3">
         <v>9</v>
       </c>
-      <c r="B822" s="4">
+      <c r="B822" s="3">
         <v>21</v>
       </c>
       <c r="C822" t="s">
@@ -13088,10 +13082,10 @@
       </c>
     </row>
     <row r="823" spans="1:3">
-      <c r="A823" s="4">
+      <c r="A823" s="3">
         <v>9</v>
       </c>
-      <c r="B823" s="4">
+      <c r="B823" s="3">
         <v>22</v>
       </c>
       <c r="C823" t="s">
@@ -13099,10 +13093,10 @@
       </c>
     </row>
     <row r="824" spans="1:3">
-      <c r="A824" s="4">
+      <c r="A824" s="3">
         <v>9</v>
       </c>
-      <c r="B824" s="4">
+      <c r="B824" s="3">
         <v>23</v>
       </c>
       <c r="C824" t="s">
@@ -13110,10 +13104,10 @@
       </c>
     </row>
     <row r="825" spans="1:3">
-      <c r="A825" s="4">
+      <c r="A825" s="3">
         <v>9</v>
       </c>
-      <c r="B825" s="4">
+      <c r="B825" s="3">
         <v>24</v>
       </c>
       <c r="C825" t="s">
@@ -13121,10 +13115,10 @@
       </c>
     </row>
     <row r="826" spans="1:3">
-      <c r="A826" s="4">
+      <c r="A826" s="3">
         <v>9</v>
       </c>
-      <c r="B826" s="4">
+      <c r="B826" s="3">
         <v>25</v>
       </c>
       <c r="C826" t="s">
@@ -13132,10 +13126,10 @@
       </c>
     </row>
     <row r="827" spans="1:3">
-      <c r="A827" s="4">
+      <c r="A827" s="3">
         <v>9</v>
       </c>
-      <c r="B827" s="4">
+      <c r="B827" s="3">
         <v>26</v>
       </c>
       <c r="C827" t="s">
@@ -13143,10 +13137,10 @@
       </c>
     </row>
     <row r="828" spans="1:3">
-      <c r="A828" s="4">
+      <c r="A828" s="3">
         <v>9</v>
       </c>
-      <c r="B828" s="4">
+      <c r="B828" s="3">
         <v>27</v>
       </c>
       <c r="C828" t="s">
@@ -13154,10 +13148,10 @@
       </c>
     </row>
     <row r="829" spans="1:3">
-      <c r="A829" s="4">
+      <c r="A829" s="3">
         <v>9</v>
       </c>
-      <c r="B829" s="4">
+      <c r="B829" s="3">
         <v>28</v>
       </c>
       <c r="C829" t="s">
@@ -13165,10 +13159,10 @@
       </c>
     </row>
     <row r="830" spans="1:3">
-      <c r="A830" s="4">
+      <c r="A830" s="3">
         <v>9</v>
       </c>
-      <c r="B830" s="4">
+      <c r="B830" s="3">
         <v>29</v>
       </c>
       <c r="C830" t="s">
@@ -13176,10 +13170,10 @@
       </c>
     </row>
     <row r="831" spans="1:3">
-      <c r="A831" s="4">
+      <c r="A831" s="3">
         <v>9</v>
       </c>
-      <c r="B831" s="4">
+      <c r="B831" s="3">
         <v>30</v>
       </c>
       <c r="C831" t="s">
@@ -13187,10 +13181,10 @@
       </c>
     </row>
     <row r="832" spans="1:3">
-      <c r="A832" s="4">
+      <c r="A832" s="3">
         <v>9</v>
       </c>
-      <c r="B832" s="4">
+      <c r="B832" s="3">
         <v>31</v>
       </c>
       <c r="C832" t="s">
@@ -13198,10 +13192,10 @@
       </c>
     </row>
     <row r="833" spans="1:3">
-      <c r="A833" s="4">
+      <c r="A833" s="3">
         <v>9</v>
       </c>
-      <c r="B833" s="4">
+      <c r="B833" s="3">
         <v>32</v>
       </c>
       <c r="C833" t="s">
@@ -13209,10 +13203,10 @@
       </c>
     </row>
     <row r="834" spans="1:3">
-      <c r="A834" s="4">
+      <c r="A834" s="3">
         <v>9</v>
       </c>
-      <c r="B834" s="4">
+      <c r="B834" s="3">
         <v>33</v>
       </c>
       <c r="C834" t="s">
@@ -13220,10 +13214,10 @@
       </c>
     </row>
     <row r="835" spans="1:3">
-      <c r="A835" s="4">
+      <c r="A835" s="3">
         <v>9</v>
       </c>
-      <c r="B835" s="4">
+      <c r="B835" s="3">
         <v>34</v>
       </c>
       <c r="C835" t="s">
@@ -13231,10 +13225,10 @@
       </c>
     </row>
     <row r="836" spans="1:3">
-      <c r="A836" s="4">
+      <c r="A836" s="3">
         <v>9</v>
       </c>
-      <c r="B836" s="4">
+      <c r="B836" s="3">
         <v>35</v>
       </c>
       <c r="C836" t="s">
@@ -13242,10 +13236,10 @@
       </c>
     </row>
     <row r="837" spans="1:3">
-      <c r="A837" s="4">
+      <c r="A837" s="3">
         <v>9</v>
       </c>
-      <c r="B837" s="4">
+      <c r="B837" s="3">
         <v>36</v>
       </c>
       <c r="C837" t="s">
@@ -13253,10 +13247,10 @@
       </c>
     </row>
     <row r="838" spans="1:3">
-      <c r="A838" s="4">
+      <c r="A838" s="3">
         <v>9</v>
       </c>
-      <c r="B838" s="4">
+      <c r="B838" s="3">
         <v>37</v>
       </c>
       <c r="C838" t="s">
@@ -13264,10 +13258,10 @@
       </c>
     </row>
     <row r="839" spans="1:3">
-      <c r="A839" s="4">
+      <c r="A839" s="3">
         <v>9</v>
       </c>
-      <c r="B839" s="4">
+      <c r="B839" s="3">
         <v>38</v>
       </c>
       <c r="C839" t="s">
@@ -13275,10 +13269,10 @@
       </c>
     </row>
     <row r="840" spans="1:3">
-      <c r="A840" s="4">
+      <c r="A840" s="3">
         <v>9</v>
       </c>
-      <c r="B840" s="4">
+      <c r="B840" s="3">
         <v>39</v>
       </c>
       <c r="C840" t="s">
@@ -13286,10 +13280,10 @@
       </c>
     </row>
     <row r="841" spans="1:3">
-      <c r="A841" s="4">
+      <c r="A841" s="3">
         <v>9</v>
       </c>
-      <c r="B841" s="4">
+      <c r="B841" s="3">
         <v>40</v>
       </c>
       <c r="C841" t="s">
@@ -13297,10 +13291,10 @@
       </c>
     </row>
     <row r="842" spans="1:3">
-      <c r="A842" s="4">
+      <c r="A842" s="3">
         <v>9</v>
       </c>
-      <c r="B842" s="4">
+      <c r="B842" s="3">
         <v>41</v>
       </c>
       <c r="C842" t="s">
@@ -13308,10 +13302,10 @@
       </c>
     </row>
     <row r="843" spans="1:3">
-      <c r="A843" s="4">
+      <c r="A843" s="3">
         <v>9</v>
       </c>
-      <c r="B843" s="4">
+      <c r="B843" s="3">
         <v>42</v>
       </c>
       <c r="C843" t="s">
@@ -13319,10 +13313,10 @@
       </c>
     </row>
     <row r="844" spans="1:3">
-      <c r="A844" s="4">
+      <c r="A844" s="3">
         <v>9</v>
       </c>
-      <c r="B844" s="4">
+      <c r="B844" s="3">
         <v>43</v>
       </c>
       <c r="C844" t="s">
@@ -13330,10 +13324,10 @@
       </c>
     </row>
     <row r="845" spans="1:3">
-      <c r="A845" s="4">
+      <c r="A845" s="3">
         <v>9</v>
       </c>
-      <c r="B845" s="4">
+      <c r="B845" s="3">
         <v>44</v>
       </c>
       <c r="C845" t="s">
@@ -13341,10 +13335,10 @@
       </c>
     </row>
     <row r="846" spans="1:3">
-      <c r="A846" s="4">
+      <c r="A846" s="3">
         <v>9</v>
       </c>
-      <c r="B846" s="4">
+      <c r="B846" s="3">
         <v>45</v>
       </c>
       <c r="C846" t="s">
@@ -13352,10 +13346,10 @@
       </c>
     </row>
     <row r="847" spans="1:3">
-      <c r="A847" s="4">
+      <c r="A847" s="3">
         <v>9</v>
       </c>
-      <c r="B847" s="4">
+      <c r="B847" s="3">
         <v>46</v>
       </c>
       <c r="C847" t="s">
@@ -13363,10 +13357,10 @@
       </c>
     </row>
     <row r="848" spans="1:3">
-      <c r="A848" s="4">
+      <c r="A848" s="3">
         <v>9</v>
       </c>
-      <c r="B848" s="4">
+      <c r="B848" s="3">
         <v>47</v>
       </c>
       <c r="C848" t="s">
@@ -13374,10 +13368,10 @@
       </c>
     </row>
     <row r="849" spans="1:3">
-      <c r="A849" s="4">
+      <c r="A849" s="3">
         <v>9</v>
       </c>
-      <c r="B849" s="4">
+      <c r="B849" s="3">
         <v>48</v>
       </c>
       <c r="C849" t="s">
@@ -13385,10 +13379,10 @@
       </c>
     </row>
     <row r="850" spans="1:3">
-      <c r="A850" s="4">
+      <c r="A850" s="3">
         <v>9</v>
       </c>
-      <c r="B850" s="4">
+      <c r="B850" s="3">
         <v>49</v>
       </c>
       <c r="C850" t="s">
@@ -13396,10 +13390,10 @@
       </c>
     </row>
     <row r="851" spans="1:3">
-      <c r="A851" s="4">
+      <c r="A851" s="3">
         <v>9</v>
       </c>
-      <c r="B851" s="4">
+      <c r="B851" s="3">
         <v>50</v>
       </c>
       <c r="C851" t="s">
@@ -13407,10 +13401,10 @@
       </c>
     </row>
     <row r="852" spans="1:3">
-      <c r="A852" s="4">
+      <c r="A852" s="3">
         <v>9</v>
       </c>
-      <c r="B852" s="4">
+      <c r="B852" s="3">
         <v>51</v>
       </c>
       <c r="C852" t="s">
@@ -13418,10 +13412,10 @@
       </c>
     </row>
     <row r="853" spans="1:3">
-      <c r="A853" s="4">
+      <c r="A853" s="3">
         <v>9</v>
       </c>
-      <c r="B853" s="4">
+      <c r="B853" s="3">
         <v>52</v>
       </c>
       <c r="C853" t="s">
@@ -13429,10 +13423,10 @@
       </c>
     </row>
     <row r="854" spans="1:3">
-      <c r="A854" s="4">
+      <c r="A854" s="3">
         <v>9</v>
       </c>
-      <c r="B854" s="4">
+      <c r="B854" s="3">
         <v>53</v>
       </c>
       <c r="C854" t="s">
@@ -13440,10 +13434,10 @@
       </c>
     </row>
     <row r="855" spans="1:3">
-      <c r="A855" s="4">
+      <c r="A855" s="3">
         <v>9</v>
       </c>
-      <c r="B855" s="4">
+      <c r="B855" s="3">
         <v>54</v>
       </c>
       <c r="C855" t="s">
@@ -13451,10 +13445,10 @@
       </c>
     </row>
     <row r="856" spans="1:3">
-      <c r="A856" s="4">
+      <c r="A856" s="3">
         <v>9</v>
       </c>
-      <c r="B856" s="4">
+      <c r="B856" s="3">
         <v>55</v>
       </c>
       <c r="C856" t="s">
@@ -13462,10 +13456,10 @@
       </c>
     </row>
     <row r="857" spans="1:3">
-      <c r="A857" s="4">
+      <c r="A857" s="3">
         <v>9</v>
       </c>
-      <c r="B857" s="4">
+      <c r="B857" s="3">
         <v>56</v>
       </c>
       <c r="C857" t="s">
@@ -13473,10 +13467,10 @@
       </c>
     </row>
     <row r="858" spans="1:3">
-      <c r="A858" s="4">
+      <c r="A858" s="3">
         <v>9</v>
       </c>
-      <c r="B858" s="4">
+      <c r="B858" s="3">
         <v>57</v>
       </c>
       <c r="C858" t="s">
@@ -13484,10 +13478,10 @@
       </c>
     </row>
     <row r="859" spans="1:3">
-      <c r="A859" s="4">
+      <c r="A859" s="3">
         <v>9</v>
       </c>
-      <c r="B859" s="4">
+      <c r="B859" s="3">
         <v>58</v>
       </c>
       <c r="C859" t="s">
@@ -13495,10 +13489,10 @@
       </c>
     </row>
     <row r="860" spans="1:3">
-      <c r="A860" s="4">
+      <c r="A860" s="3">
         <v>9</v>
       </c>
-      <c r="B860" s="4">
+      <c r="B860" s="3">
         <v>59</v>
       </c>
       <c r="C860" t="s">
@@ -13506,10 +13500,10 @@
       </c>
     </row>
     <row r="861" spans="1:3">
-      <c r="A861" s="4">
+      <c r="A861" s="3">
         <v>9</v>
       </c>
-      <c r="B861" s="4">
+      <c r="B861" s="3">
         <v>60</v>
       </c>
       <c r="C861" t="s">
@@ -13517,10 +13511,10 @@
       </c>
     </row>
     <row r="862" spans="1:3">
-      <c r="A862" s="4">
+      <c r="A862" s="3">
         <v>9</v>
       </c>
-      <c r="B862" s="4">
+      <c r="B862" s="3">
         <v>61</v>
       </c>
       <c r="C862" t="s">
@@ -13528,10 +13522,10 @@
       </c>
     </row>
     <row r="863" spans="1:3">
-      <c r="A863" s="4">
+      <c r="A863" s="3">
         <v>9</v>
       </c>
-      <c r="B863" s="4">
+      <c r="B863" s="3">
         <v>62</v>
       </c>
       <c r="C863" t="s">
@@ -13539,10 +13533,10 @@
       </c>
     </row>
     <row r="864" spans="1:3">
-      <c r="A864" s="4">
+      <c r="A864" s="3">
         <v>9</v>
       </c>
-      <c r="B864" s="4">
+      <c r="B864" s="3">
         <v>63</v>
       </c>
       <c r="C864" t="s">
@@ -13550,10 +13544,10 @@
       </c>
     </row>
     <row r="865" spans="1:3">
-      <c r="A865" s="4">
+      <c r="A865" s="3">
         <v>9</v>
       </c>
-      <c r="B865" s="4">
+      <c r="B865" s="3">
         <v>64</v>
       </c>
       <c r="C865" t="s">
@@ -13561,10 +13555,10 @@
       </c>
     </row>
     <row r="866" spans="1:3">
-      <c r="A866" s="4">
+      <c r="A866" s="3">
         <v>9</v>
       </c>
-      <c r="B866" s="4">
+      <c r="B866" s="3">
         <v>65</v>
       </c>
       <c r="C866" t="s">
@@ -13572,10 +13566,10 @@
       </c>
     </row>
     <row r="867" spans="1:3">
-      <c r="A867" s="4">
+      <c r="A867" s="3">
         <v>9</v>
       </c>
-      <c r="B867" s="4">
+      <c r="B867" s="3">
         <v>66</v>
       </c>
       <c r="C867" t="s">
@@ -13583,10 +13577,10 @@
       </c>
     </row>
     <row r="868" spans="1:3">
-      <c r="A868" s="4">
+      <c r="A868" s="3">
         <v>9</v>
       </c>
-      <c r="B868" s="4">
+      <c r="B868" s="3">
         <v>67</v>
       </c>
       <c r="C868" t="s">
@@ -13594,10 +13588,10 @@
       </c>
     </row>
     <row r="869" spans="1:3">
-      <c r="A869" s="4">
+      <c r="A869" s="3">
         <v>9</v>
       </c>
-      <c r="B869" s="4">
+      <c r="B869" s="3">
         <v>68</v>
       </c>
       <c r="C869" t="s">
@@ -13605,10 +13599,10 @@
       </c>
     </row>
     <row r="870" spans="1:3">
-      <c r="A870" s="4">
+      <c r="A870" s="3">
         <v>9</v>
       </c>
-      <c r="B870" s="4">
+      <c r="B870" s="3">
         <v>69</v>
       </c>
       <c r="C870" t="s">
@@ -13616,10 +13610,10 @@
       </c>
     </row>
     <row r="871" spans="1:3">
-      <c r="A871" s="4">
+      <c r="A871" s="3">
         <v>9</v>
       </c>
-      <c r="B871" s="4">
+      <c r="B871" s="3">
         <v>70</v>
       </c>
       <c r="C871" t="s">
@@ -13627,10 +13621,10 @@
       </c>
     </row>
     <row r="872" spans="1:3">
-      <c r="A872" s="4">
+      <c r="A872" s="3">
         <v>9</v>
       </c>
-      <c r="B872" s="4">
+      <c r="B872" s="3">
         <v>71</v>
       </c>
       <c r="C872" t="s">
@@ -13638,10 +13632,10 @@
       </c>
     </row>
     <row r="873" spans="1:3">
-      <c r="A873" s="4">
+      <c r="A873" s="3">
         <v>9</v>
       </c>
-      <c r="B873" s="4">
+      <c r="B873" s="3">
         <v>72</v>
       </c>
       <c r="C873" t="s">
@@ -13649,10 +13643,10 @@
       </c>
     </row>
     <row r="874" spans="1:3">
-      <c r="A874" s="4">
+      <c r="A874" s="3">
         <v>9</v>
       </c>
-      <c r="B874" s="4">
+      <c r="B874" s="3">
         <v>73</v>
       </c>
       <c r="C874" t="s">
@@ -13660,10 +13654,10 @@
       </c>
     </row>
     <row r="875" spans="1:3">
-      <c r="A875" s="4">
+      <c r="A875" s="3">
         <v>9</v>
       </c>
-      <c r="B875" s="4">
+      <c r="B875" s="3">
         <v>74</v>
       </c>
       <c r="C875" t="s">
@@ -13671,10 +13665,10 @@
       </c>
     </row>
     <row r="876" spans="1:3">
-      <c r="A876" s="4">
+      <c r="A876" s="3">
         <v>9</v>
       </c>
-      <c r="B876" s="4">
+      <c r="B876" s="3">
         <v>75</v>
       </c>
       <c r="C876" t="s">
@@ -13682,10 +13676,10 @@
       </c>
     </row>
     <row r="877" spans="1:3">
-      <c r="A877" s="4">
+      <c r="A877" s="3">
         <v>9</v>
       </c>
-      <c r="B877" s="4">
+      <c r="B877" s="3">
         <v>76</v>
       </c>
       <c r="C877" t="s">
@@ -13693,10 +13687,10 @@
       </c>
     </row>
     <row r="878" spans="1:3">
-      <c r="A878" s="4">
+      <c r="A878" s="3">
         <v>9</v>
       </c>
-      <c r="B878" s="4">
+      <c r="B878" s="3">
         <v>77</v>
       </c>
       <c r="C878" t="s">
@@ -13704,10 +13698,10 @@
       </c>
     </row>
     <row r="879" spans="1:3">
-      <c r="A879" s="4">
+      <c r="A879" s="3">
         <v>9</v>
       </c>
-      <c r="B879" s="4">
+      <c r="B879" s="3">
         <v>78</v>
       </c>
       <c r="C879" t="s">
@@ -13715,10 +13709,10 @@
       </c>
     </row>
     <row r="880" spans="1:3">
-      <c r="A880" s="4">
+      <c r="A880" s="3">
         <v>9</v>
       </c>
-      <c r="B880" s="4">
+      <c r="B880" s="3">
         <v>79</v>
       </c>
       <c r="C880" t="s">
@@ -13726,10 +13720,10 @@
       </c>
     </row>
     <row r="881" spans="1:3">
-      <c r="A881" s="4">
+      <c r="A881" s="3">
         <v>9</v>
       </c>
-      <c r="B881" s="4">
+      <c r="B881" s="3">
         <v>80</v>
       </c>
       <c r="C881" t="s">
@@ -13737,10 +13731,10 @@
       </c>
     </row>
     <row r="882" spans="1:3" ht="24">
-      <c r="A882" s="4">
+      <c r="A882" s="3">
         <v>9</v>
       </c>
-      <c r="B882" s="4">
+      <c r="B882" s="3">
         <v>81</v>
       </c>
       <c r="C882" t="s">
@@ -13748,10 +13742,10 @@
       </c>
     </row>
     <row r="883" spans="1:3">
-      <c r="A883" s="4">
+      <c r="A883" s="3">
         <v>9</v>
       </c>
-      <c r="B883" s="4">
+      <c r="B883" s="3">
         <v>82</v>
       </c>
       <c r="C883" t="s">
@@ -13759,10 +13753,10 @@
       </c>
     </row>
     <row r="884" spans="1:3">
-      <c r="A884" s="4">
+      <c r="A884" s="3">
         <v>9</v>
       </c>
-      <c r="B884" s="4">
+      <c r="B884" s="3">
         <v>83</v>
       </c>
       <c r="C884" t="s">
@@ -13770,10 +13764,10 @@
       </c>
     </row>
     <row r="885" spans="1:3">
-      <c r="A885" s="4">
+      <c r="A885" s="3">
         <v>9</v>
       </c>
-      <c r="B885" s="4">
+      <c r="B885" s="3">
         <v>84</v>
       </c>
       <c r="C885" t="s">
@@ -13781,10 +13775,10 @@
       </c>
     </row>
     <row r="886" spans="1:3">
-      <c r="A886" s="4">
+      <c r="A886" s="3">
         <v>9</v>
       </c>
-      <c r="B886" s="4">
+      <c r="B886" s="3">
         <v>85</v>
       </c>
       <c r="C886" t="s">
@@ -13792,10 +13786,10 @@
       </c>
     </row>
     <row r="887" spans="1:3">
-      <c r="A887" s="4">
+      <c r="A887" s="3">
         <v>9</v>
       </c>
-      <c r="B887" s="4">
+      <c r="B887" s="3">
         <v>86</v>
       </c>
       <c r="C887" t="s">
@@ -13803,10 +13797,10 @@
       </c>
     </row>
     <row r="888" spans="1:3">
-      <c r="A888" s="4">
+      <c r="A888" s="3">
         <v>9</v>
       </c>
-      <c r="B888" s="4">
+      <c r="B888" s="3">
         <v>87</v>
       </c>
       <c r="C888" t="s">
@@ -13814,10 +13808,10 @@
       </c>
     </row>
     <row r="889" spans="1:3" ht="24">
-      <c r="A889" s="4">
+      <c r="A889" s="3">
         <v>9</v>
       </c>
-      <c r="B889" s="4">
+      <c r="B889" s="3">
         <v>88</v>
       </c>
       <c r="C889" t="s">
@@ -13825,10 +13819,10 @@
       </c>
     </row>
     <row r="890" spans="1:3">
-      <c r="A890" s="4">
+      <c r="A890" s="3">
         <v>9</v>
       </c>
-      <c r="B890" s="4">
+      <c r="B890" s="3">
         <v>89</v>
       </c>
       <c r="C890" t="s">
@@ -13836,10 +13830,10 @@
       </c>
     </row>
     <row r="891" spans="1:3">
-      <c r="A891" s="4">
+      <c r="A891" s="3">
         <v>9</v>
       </c>
-      <c r="B891" s="4">
+      <c r="B891" s="3">
         <v>90</v>
       </c>
       <c r="C891" t="s">
@@ -13847,10 +13841,10 @@
       </c>
     </row>
     <row r="892" spans="1:3">
-      <c r="A892" s="4">
+      <c r="A892" s="3">
         <v>9</v>
       </c>
-      <c r="B892" s="4">
+      <c r="B892" s="3">
         <v>91</v>
       </c>
       <c r="C892" t="s">
@@ -13858,10 +13852,10 @@
       </c>
     </row>
     <row r="893" spans="1:3">
-      <c r="A893" s="4">
+      <c r="A893" s="3">
         <v>9</v>
       </c>
-      <c r="B893" s="4">
+      <c r="B893" s="3">
         <v>92</v>
       </c>
       <c r="C893" t="s">
@@ -13869,10 +13863,10 @@
       </c>
     </row>
     <row r="894" spans="1:3">
-      <c r="A894" s="4">
+      <c r="A894" s="3">
         <v>9</v>
       </c>
-      <c r="B894" s="4">
+      <c r="B894" s="3">
         <v>93</v>
       </c>
       <c r="C894" t="s">
@@ -13880,10 +13874,10 @@
       </c>
     </row>
     <row r="895" spans="1:3">
-      <c r="A895" s="4">
+      <c r="A895" s="3">
         <v>9</v>
       </c>
-      <c r="B895" s="4">
+      <c r="B895" s="3">
         <v>94</v>
       </c>
       <c r="C895" t="s">
@@ -13891,10 +13885,10 @@
       </c>
     </row>
     <row r="896" spans="1:3">
-      <c r="A896" s="4">
+      <c r="A896" s="3">
         <v>9</v>
       </c>
-      <c r="B896" s="4">
+      <c r="B896" s="3">
         <v>95</v>
       </c>
       <c r="C896" t="s">
@@ -13902,10 +13896,10 @@
       </c>
     </row>
     <row r="897" spans="1:3">
-      <c r="A897" s="4">
+      <c r="A897" s="3">
         <v>9</v>
       </c>
-      <c r="B897" s="4">
+      <c r="B897" s="3">
         <v>96</v>
       </c>
       <c r="C897" t="s">
@@ -13913,10 +13907,10 @@
       </c>
     </row>
     <row r="898" spans="1:3">
-      <c r="A898" s="4">
+      <c r="A898" s="3">
         <v>9</v>
       </c>
-      <c r="B898" s="4">
+      <c r="B898" s="3">
         <v>97</v>
       </c>
       <c r="C898" t="s">
@@ -13924,10 +13918,10 @@
       </c>
     </row>
     <row r="899" spans="1:3" ht="24">
-      <c r="A899" s="4">
+      <c r="A899" s="3">
         <v>9</v>
       </c>
-      <c r="B899" s="4">
+      <c r="B899" s="3">
         <v>98</v>
       </c>
       <c r="C899" t="s">
@@ -13935,32 +13929,32 @@
       </c>
     </row>
     <row r="900" spans="1:3">
-      <c r="A900" s="4">
+      <c r="A900" s="3">
         <v>9</v>
       </c>
-      <c r="B900" s="4">
+      <c r="B900" s="3">
         <v>99</v>
       </c>
       <c r="C900" t="s">
         <v>899</v>
       </c>
     </row>
-    <row r="901" spans="1:3" s="3" customFormat="1">
-      <c r="A901" s="7">
+    <row r="901" spans="1:3">
+      <c r="A901" s="3">
         <v>9</v>
       </c>
-      <c r="B901" s="7">
+      <c r="B901" s="3">
         <v>100</v>
       </c>
-      <c r="C901" s="3" t="s">
+      <c r="C901" t="s">
         <v>900</v>
       </c>
     </row>
     <row r="902" spans="1:3">
-      <c r="A902" s="4">
+      <c r="A902" s="3">
         <v>10</v>
       </c>
-      <c r="B902" s="4">
+      <c r="B902" s="3">
         <v>1</v>
       </c>
       <c r="C902" t="s">
@@ -13968,10 +13962,10 @@
       </c>
     </row>
     <row r="903" spans="1:3">
-      <c r="A903" s="4">
+      <c r="A903" s="3">
         <v>10</v>
       </c>
-      <c r="B903" s="4">
+      <c r="B903" s="3">
         <v>2</v>
       </c>
       <c r="C903" t="s">
@@ -13979,10 +13973,10 @@
       </c>
     </row>
     <row r="904" spans="1:3">
-      <c r="A904" s="4">
+      <c r="A904" s="3">
         <v>10</v>
       </c>
-      <c r="B904" s="4">
+      <c r="B904" s="3">
         <v>3</v>
       </c>
       <c r="C904" t="s">
@@ -13990,10 +13984,10 @@
       </c>
     </row>
     <row r="905" spans="1:3">
-      <c r="A905" s="4">
+      <c r="A905" s="3">
         <v>10</v>
       </c>
-      <c r="B905" s="4">
+      <c r="B905" s="3">
         <v>4</v>
       </c>
       <c r="C905" t="s">
@@ -14001,10 +13995,10 @@
       </c>
     </row>
     <row r="906" spans="1:3">
-      <c r="A906" s="4">
+      <c r="A906" s="3">
         <v>10</v>
       </c>
-      <c r="B906" s="4">
+      <c r="B906" s="3">
         <v>5</v>
       </c>
       <c r="C906" t="s">
@@ -14012,10 +14006,10 @@
       </c>
     </row>
     <row r="907" spans="1:3">
-      <c r="A907" s="4">
+      <c r="A907" s="3">
         <v>10</v>
       </c>
-      <c r="B907" s="4">
+      <c r="B907" s="3">
         <v>6</v>
       </c>
       <c r="C907" t="s">
@@ -14023,10 +14017,10 @@
       </c>
     </row>
     <row r="908" spans="1:3">
-      <c r="A908" s="4">
+      <c r="A908" s="3">
         <v>10</v>
       </c>
-      <c r="B908" s="4">
+      <c r="B908" s="3">
         <v>7</v>
       </c>
       <c r="C908" t="s">
@@ -14034,10 +14028,10 @@
       </c>
     </row>
     <row r="909" spans="1:3">
-      <c r="A909" s="4">
+      <c r="A909" s="3">
         <v>10</v>
       </c>
-      <c r="B909" s="4">
+      <c r="B909" s="3">
         <v>8</v>
       </c>
       <c r="C909" t="s">
@@ -14045,10 +14039,10 @@
       </c>
     </row>
     <row r="910" spans="1:3">
-      <c r="A910" s="4">
+      <c r="A910" s="3">
         <v>10</v>
       </c>
-      <c r="B910" s="4">
+      <c r="B910" s="3">
         <v>9</v>
       </c>
       <c r="C910" t="s">
@@ -14056,10 +14050,10 @@
       </c>
     </row>
     <row r="911" spans="1:3">
-      <c r="A911" s="4">
+      <c r="A911" s="3">
         <v>10</v>
       </c>
-      <c r="B911" s="4">
+      <c r="B911" s="3">
         <v>10</v>
       </c>
       <c r="C911" t="s">
@@ -14067,10 +14061,10 @@
       </c>
     </row>
     <row r="912" spans="1:3">
-      <c r="A912" s="4">
+      <c r="A912" s="3">
         <v>10</v>
       </c>
-      <c r="B912" s="4">
+      <c r="B912" s="3">
         <v>11</v>
       </c>
       <c r="C912" t="s">
@@ -14078,10 +14072,10 @@
       </c>
     </row>
     <row r="913" spans="1:3">
-      <c r="A913" s="4">
+      <c r="A913" s="3">
         <v>10</v>
       </c>
-      <c r="B913" s="4">
+      <c r="B913" s="3">
         <v>12</v>
       </c>
       <c r="C913" t="s">
@@ -14089,10 +14083,10 @@
       </c>
     </row>
     <row r="914" spans="1:3">
-      <c r="A914" s="4">
+      <c r="A914" s="3">
         <v>10</v>
       </c>
-      <c r="B914" s="4">
+      <c r="B914" s="3">
         <v>13</v>
       </c>
       <c r="C914" t="s">
@@ -14100,10 +14094,10 @@
       </c>
     </row>
     <row r="915" spans="1:3">
-      <c r="A915" s="4">
+      <c r="A915" s="3">
         <v>10</v>
       </c>
-      <c r="B915" s="4">
+      <c r="B915" s="3">
         <v>14</v>
       </c>
       <c r="C915" t="s">
@@ -14111,10 +14105,10 @@
       </c>
     </row>
     <row r="916" spans="1:3">
-      <c r="A916" s="4">
+      <c r="A916" s="3">
         <v>10</v>
       </c>
-      <c r="B916" s="4">
+      <c r="B916" s="3">
         <v>15</v>
       </c>
       <c r="C916" t="s">
@@ -14122,10 +14116,10 @@
       </c>
     </row>
     <row r="917" spans="1:3">
-      <c r="A917" s="4">
+      <c r="A917" s="3">
         <v>10</v>
       </c>
-      <c r="B917" s="4">
+      <c r="B917" s="3">
         <v>16</v>
       </c>
       <c r="C917" t="s">
@@ -14133,10 +14127,10 @@
       </c>
     </row>
     <row r="918" spans="1:3">
-      <c r="A918" s="4">
+      <c r="A918" s="3">
         <v>10</v>
       </c>
-      <c r="B918" s="4">
+      <c r="B918" s="3">
         <v>17</v>
       </c>
       <c r="C918" t="s">
@@ -14144,10 +14138,10 @@
       </c>
     </row>
     <row r="919" spans="1:3">
-      <c r="A919" s="4">
+      <c r="A919" s="3">
         <v>10</v>
       </c>
-      <c r="B919" s="4">
+      <c r="B919" s="3">
         <v>18</v>
       </c>
       <c r="C919" t="s">
@@ -14155,10 +14149,10 @@
       </c>
     </row>
     <row r="920" spans="1:3">
-      <c r="A920" s="4">
+      <c r="A920" s="3">
         <v>10</v>
       </c>
-      <c r="B920" s="4">
+      <c r="B920" s="3">
         <v>19</v>
       </c>
       <c r="C920" t="s">
@@ -14166,10 +14160,10 @@
       </c>
     </row>
     <row r="921" spans="1:3">
-      <c r="A921" s="4">
+      <c r="A921" s="3">
         <v>10</v>
       </c>
-      <c r="B921" s="4">
+      <c r="B921" s="3">
         <v>20</v>
       </c>
       <c r="C921" t="s">
@@ -14177,10 +14171,10 @@
       </c>
     </row>
     <row r="922" spans="1:3">
-      <c r="A922" s="4">
+      <c r="A922" s="3">
         <v>10</v>
       </c>
-      <c r="B922" s="4">
+      <c r="B922" s="3">
         <v>21</v>
       </c>
       <c r="C922" t="s">
@@ -14188,10 +14182,10 @@
       </c>
     </row>
     <row r="923" spans="1:3">
-      <c r="A923" s="4">
+      <c r="A923" s="3">
         <v>10</v>
       </c>
-      <c r="B923" s="4">
+      <c r="B923" s="3">
         <v>22</v>
       </c>
       <c r="C923" t="s">
@@ -14199,10 +14193,10 @@
       </c>
     </row>
     <row r="924" spans="1:3">
-      <c r="A924" s="4">
+      <c r="A924" s="3">
         <v>10</v>
       </c>
-      <c r="B924" s="4">
+      <c r="B924" s="3">
         <v>23</v>
       </c>
       <c r="C924" t="s">
@@ -14210,10 +14204,10 @@
       </c>
     </row>
     <row r="925" spans="1:3">
-      <c r="A925" s="4">
+      <c r="A925" s="3">
         <v>10</v>
       </c>
-      <c r="B925" s="4">
+      <c r="B925" s="3">
         <v>24</v>
       </c>
       <c r="C925" t="s">
@@ -14221,10 +14215,10 @@
       </c>
     </row>
     <row r="926" spans="1:3">
-      <c r="A926" s="4">
+      <c r="A926" s="3">
         <v>10</v>
       </c>
-      <c r="B926" s="4">
+      <c r="B926" s="3">
         <v>25</v>
       </c>
       <c r="C926" t="s">
@@ -14232,10 +14226,10 @@
       </c>
     </row>
     <row r="927" spans="1:3">
-      <c r="A927" s="4">
+      <c r="A927" s="3">
         <v>10</v>
       </c>
-      <c r="B927" s="4">
+      <c r="B927" s="3">
         <v>26</v>
       </c>
       <c r="C927" t="s">
@@ -14243,10 +14237,10 @@
       </c>
     </row>
     <row r="928" spans="1:3">
-      <c r="A928" s="4">
+      <c r="A928" s="3">
         <v>10</v>
       </c>
-      <c r="B928" s="4">
+      <c r="B928" s="3">
         <v>27</v>
       </c>
       <c r="C928" t="s">
@@ -14254,10 +14248,10 @@
       </c>
     </row>
     <row r="929" spans="1:3">
-      <c r="A929" s="4">
+      <c r="A929" s="3">
         <v>10</v>
       </c>
-      <c r="B929" s="4">
+      <c r="B929" s="3">
         <v>28</v>
       </c>
       <c r="C929" t="s">
@@ -14265,10 +14259,10 @@
       </c>
     </row>
     <row r="930" spans="1:3">
-      <c r="A930" s="4">
+      <c r="A930" s="3">
         <v>10</v>
       </c>
-      <c r="B930" s="4">
+      <c r="B930" s="3">
         <v>29</v>
       </c>
       <c r="C930" t="s">
@@ -14276,10 +14270,10 @@
       </c>
     </row>
     <row r="931" spans="1:3">
-      <c r="A931" s="4">
+      <c r="A931" s="3">
         <v>10</v>
       </c>
-      <c r="B931" s="4">
+      <c r="B931" s="3">
         <v>30</v>
       </c>
       <c r="C931" t="s">
@@ -14287,10 +14281,10 @@
       </c>
     </row>
     <row r="932" spans="1:3">
-      <c r="A932" s="4">
+      <c r="A932" s="3">
         <v>10</v>
       </c>
-      <c r="B932" s="4">
+      <c r="B932" s="3">
         <v>31</v>
       </c>
       <c r="C932" t="s">
@@ -14298,10 +14292,10 @@
       </c>
     </row>
     <row r="933" spans="1:3">
-      <c r="A933" s="4">
+      <c r="A933" s="3">
         <v>10</v>
       </c>
-      <c r="B933" s="4">
+      <c r="B933" s="3">
         <v>32</v>
       </c>
       <c r="C933" t="s">
@@ -14309,10 +14303,10 @@
       </c>
     </row>
     <row r="934" spans="1:3">
-      <c r="A934" s="4">
+      <c r="A934" s="3">
         <v>10</v>
       </c>
-      <c r="B934" s="4">
+      <c r="B934" s="3">
         <v>33</v>
       </c>
       <c r="C934" t="s">
@@ -14320,10 +14314,10 @@
       </c>
     </row>
     <row r="935" spans="1:3">
-      <c r="A935" s="4">
+      <c r="A935" s="3">
         <v>10</v>
       </c>
-      <c r="B935" s="4">
+      <c r="B935" s="3">
         <v>34</v>
       </c>
       <c r="C935" t="s">
@@ -14331,10 +14325,10 @@
       </c>
     </row>
     <row r="936" spans="1:3">
-      <c r="A936" s="4">
+      <c r="A936" s="3">
         <v>10</v>
       </c>
-      <c r="B936" s="4">
+      <c r="B936" s="3">
         <v>35</v>
       </c>
       <c r="C936" t="s">
@@ -14342,10 +14336,10 @@
       </c>
     </row>
     <row r="937" spans="1:3">
-      <c r="A937" s="4">
+      <c r="A937" s="3">
         <v>10</v>
       </c>
-      <c r="B937" s="4">
+      <c r="B937" s="3">
         <v>36</v>
       </c>
       <c r="C937" t="s">
@@ -14353,10 +14347,10 @@
       </c>
     </row>
     <row r="938" spans="1:3">
-      <c r="A938" s="4">
+      <c r="A938" s="3">
         <v>10</v>
       </c>
-      <c r="B938" s="4">
+      <c r="B938" s="3">
         <v>37</v>
       </c>
       <c r="C938" t="s">
@@ -14364,10 +14358,10 @@
       </c>
     </row>
     <row r="939" spans="1:3">
-      <c r="A939" s="4">
+      <c r="A939" s="3">
         <v>10</v>
       </c>
-      <c r="B939" s="4">
+      <c r="B939" s="3">
         <v>38</v>
       </c>
       <c r="C939" t="s">
@@ -14375,10 +14369,10 @@
       </c>
     </row>
     <row r="940" spans="1:3">
-      <c r="A940" s="4">
+      <c r="A940" s="3">
         <v>10</v>
       </c>
-      <c r="B940" s="4">
+      <c r="B940" s="3">
         <v>39</v>
       </c>
       <c r="C940" t="s">
@@ -14386,10 +14380,10 @@
       </c>
     </row>
     <row r="941" spans="1:3">
-      <c r="A941" s="4">
+      <c r="A941" s="3">
         <v>10</v>
       </c>
-      <c r="B941" s="4">
+      <c r="B941" s="3">
         <v>40</v>
       </c>
       <c r="C941" t="s">
@@ -14397,10 +14391,10 @@
       </c>
     </row>
     <row r="942" spans="1:3">
-      <c r="A942" s="4">
+      <c r="A942" s="3">
         <v>10</v>
       </c>
-      <c r="B942" s="4">
+      <c r="B942" s="3">
         <v>41</v>
       </c>
       <c r="C942" t="s">
@@ -14408,10 +14402,10 @@
       </c>
     </row>
     <row r="943" spans="1:3">
-      <c r="A943" s="4">
+      <c r="A943" s="3">
         <v>10</v>
       </c>
-      <c r="B943" s="4">
+      <c r="B943" s="3">
         <v>42</v>
       </c>
       <c r="C943" t="s">
@@ -14419,10 +14413,10 @@
       </c>
     </row>
     <row r="944" spans="1:3">
-      <c r="A944" s="4">
+      <c r="A944" s="3">
         <v>10</v>
       </c>
-      <c r="B944" s="4">
+      <c r="B944" s="3">
         <v>43</v>
       </c>
       <c r="C944" t="s">
@@ -14430,10 +14424,10 @@
       </c>
     </row>
     <row r="945" spans="1:3">
-      <c r="A945" s="4">
+      <c r="A945" s="3">
         <v>10</v>
       </c>
-      <c r="B945" s="4">
+      <c r="B945" s="3">
         <v>44</v>
       </c>
       <c r="C945" t="s">
@@ -14441,10 +14435,10 @@
       </c>
     </row>
     <row r="946" spans="1:3">
-      <c r="A946" s="4">
+      <c r="A946" s="3">
         <v>10</v>
       </c>
-      <c r="B946" s="4">
+      <c r="B946" s="3">
         <v>45</v>
       </c>
       <c r="C946" t="s">
@@ -14452,10 +14446,10 @@
       </c>
     </row>
     <row r="947" spans="1:3">
-      <c r="A947" s="4">
+      <c r="A947" s="3">
         <v>10</v>
       </c>
-      <c r="B947" s="4">
+      <c r="B947" s="3">
         <v>46</v>
       </c>
       <c r="C947" t="s">
@@ -14463,10 +14457,10 @@
       </c>
     </row>
     <row r="948" spans="1:3">
-      <c r="A948" s="4">
+      <c r="A948" s="3">
         <v>10</v>
       </c>
-      <c r="B948" s="4">
+      <c r="B948" s="3">
         <v>47</v>
       </c>
       <c r="C948" t="s">
@@ -14474,10 +14468,10 @@
       </c>
     </row>
     <row r="949" spans="1:3">
-      <c r="A949" s="4">
+      <c r="A949" s="3">
         <v>10</v>
       </c>
-      <c r="B949" s="4">
+      <c r="B949" s="3">
         <v>48</v>
       </c>
       <c r="C949" t="s">
@@ -14485,10 +14479,10 @@
       </c>
     </row>
     <row r="950" spans="1:3">
-      <c r="A950" s="4">
+      <c r="A950" s="3">
         <v>10</v>
       </c>
-      <c r="B950" s="4">
+      <c r="B950" s="3">
         <v>49</v>
       </c>
       <c r="C950" t="s">
@@ -14496,10 +14490,10 @@
       </c>
     </row>
     <row r="951" spans="1:3">
-      <c r="A951" s="4">
+      <c r="A951" s="3">
         <v>10</v>
       </c>
-      <c r="B951" s="4">
+      <c r="B951" s="3">
         <v>50</v>
       </c>
       <c r="C951" t="s">
@@ -14507,10 +14501,10 @@
       </c>
     </row>
     <row r="952" spans="1:3">
-      <c r="A952" s="4">
+      <c r="A952" s="3">
         <v>10</v>
       </c>
-      <c r="B952" s="4">
+      <c r="B952" s="3">
         <v>51</v>
       </c>
       <c r="C952" t="s">
@@ -14518,10 +14512,10 @@
       </c>
     </row>
     <row r="953" spans="1:3">
-      <c r="A953" s="4">
+      <c r="A953" s="3">
         <v>10</v>
       </c>
-      <c r="B953" s="4">
+      <c r="B953" s="3">
         <v>52</v>
       </c>
       <c r="C953" t="s">
@@ -14529,10 +14523,10 @@
       </c>
     </row>
     <row r="954" spans="1:3">
-      <c r="A954" s="4">
+      <c r="A954" s="3">
         <v>10</v>
       </c>
-      <c r="B954" s="4">
+      <c r="B954" s="3">
         <v>53</v>
       </c>
       <c r="C954" t="s">
@@ -14540,10 +14534,10 @@
       </c>
     </row>
     <row r="955" spans="1:3">
-      <c r="A955" s="4">
+      <c r="A955" s="3">
         <v>10</v>
       </c>
-      <c r="B955" s="4">
+      <c r="B955" s="3">
         <v>54</v>
       </c>
       <c r="C955" t="s">
@@ -14551,10 +14545,10 @@
       </c>
     </row>
     <row r="956" spans="1:3">
-      <c r="A956" s="4">
+      <c r="A956" s="3">
         <v>10</v>
       </c>
-      <c r="B956" s="4">
+      <c r="B956" s="3">
         <v>55</v>
       </c>
       <c r="C956" t="s">
@@ -14562,10 +14556,10 @@
       </c>
     </row>
     <row r="957" spans="1:3">
-      <c r="A957" s="4">
+      <c r="A957" s="3">
         <v>10</v>
       </c>
-      <c r="B957" s="4">
+      <c r="B957" s="3">
         <v>56</v>
       </c>
       <c r="C957" t="s">
@@ -14573,10 +14567,10 @@
       </c>
     </row>
     <row r="958" spans="1:3">
-      <c r="A958" s="4">
+      <c r="A958" s="3">
         <v>10</v>
       </c>
-      <c r="B958" s="4">
+      <c r="B958" s="3">
         <v>57</v>
       </c>
       <c r="C958" t="s">
@@ -14584,10 +14578,10 @@
       </c>
     </row>
     <row r="959" spans="1:3">
-      <c r="A959" s="4">
+      <c r="A959" s="3">
         <v>10</v>
       </c>
-      <c r="B959" s="4">
+      <c r="B959" s="3">
         <v>58</v>
       </c>
       <c r="C959" t="s">
@@ -14595,10 +14589,10 @@
       </c>
     </row>
     <row r="960" spans="1:3">
-      <c r="A960" s="4">
+      <c r="A960" s="3">
         <v>10</v>
       </c>
-      <c r="B960" s="4">
+      <c r="B960" s="3">
         <v>59</v>
       </c>
       <c r="C960" t="s">
@@ -14606,10 +14600,10 @@
       </c>
     </row>
     <row r="961" spans="1:3">
-      <c r="A961" s="4">
+      <c r="A961" s="3">
         <v>10</v>
       </c>
-      <c r="B961" s="4">
+      <c r="B961" s="3">
         <v>60</v>
       </c>
       <c r="C961" t="s">
@@ -14617,10 +14611,10 @@
       </c>
     </row>
     <row r="962" spans="1:3">
-      <c r="A962" s="4">
+      <c r="A962" s="3">
         <v>10</v>
       </c>
-      <c r="B962" s="4">
+      <c r="B962" s="3">
         <v>61</v>
       </c>
       <c r="C962" t="s">
@@ -14628,10 +14622,10 @@
       </c>
     </row>
     <row r="963" spans="1:3">
-      <c r="A963" s="4">
+      <c r="A963" s="3">
         <v>10</v>
       </c>
-      <c r="B963" s="4">
+      <c r="B963" s="3">
         <v>62</v>
       </c>
       <c r="C963" t="s">
@@ -14639,10 +14633,10 @@
       </c>
     </row>
     <row r="964" spans="1:3">
-      <c r="A964" s="4">
+      <c r="A964" s="3">
         <v>10</v>
       </c>
-      <c r="B964" s="4">
+      <c r="B964" s="3">
         <v>63</v>
       </c>
       <c r="C964" t="s">
@@ -14650,10 +14644,10 @@
       </c>
     </row>
     <row r="965" spans="1:3">
-      <c r="A965" s="4">
+      <c r="A965" s="3">
         <v>10</v>
       </c>
-      <c r="B965" s="4">
+      <c r="B965" s="3">
         <v>64</v>
       </c>
       <c r="C965" t="s">
@@ -14661,10 +14655,10 @@
       </c>
     </row>
     <row r="966" spans="1:3">
-      <c r="A966" s="4">
+      <c r="A966" s="3">
         <v>10</v>
       </c>
-      <c r="B966" s="4">
+      <c r="B966" s="3">
         <v>65</v>
       </c>
       <c r="C966" t="s">
@@ -14672,10 +14666,10 @@
       </c>
     </row>
     <row r="967" spans="1:3">
-      <c r="A967" s="4">
+      <c r="A967" s="3">
         <v>10</v>
       </c>
-      <c r="B967" s="4">
+      <c r="B967" s="3">
         <v>66</v>
       </c>
       <c r="C967" t="s">
@@ -14683,10 +14677,10 @@
       </c>
     </row>
     <row r="968" spans="1:3">
-      <c r="A968" s="4">
+      <c r="A968" s="3">
         <v>10</v>
       </c>
-      <c r="B968" s="4">
+      <c r="B968" s="3">
         <v>67</v>
       </c>
       <c r="C968" t="s">
@@ -14694,10 +14688,10 @@
       </c>
     </row>
     <row r="969" spans="1:3">
-      <c r="A969" s="4">
+      <c r="A969" s="3">
         <v>10</v>
       </c>
-      <c r="B969" s="4">
+      <c r="B969" s="3">
         <v>68</v>
       </c>
       <c r="C969" t="s">
@@ -14705,10 +14699,10 @@
       </c>
     </row>
     <row r="970" spans="1:3">
-      <c r="A970" s="4">
+      <c r="A970" s="3">
         <v>10</v>
       </c>
-      <c r="B970" s="4">
+      <c r="B970" s="3">
         <v>69</v>
       </c>
       <c r="C970" t="s">
@@ -14716,10 +14710,10 @@
       </c>
     </row>
     <row r="971" spans="1:3">
-      <c r="A971" s="4">
+      <c r="A971" s="3">
         <v>10</v>
       </c>
-      <c r="B971" s="4">
+      <c r="B971" s="3">
         <v>70</v>
       </c>
       <c r="C971" t="s">
@@ -14727,10 +14721,10 @@
       </c>
     </row>
     <row r="972" spans="1:3">
-      <c r="A972" s="4">
+      <c r="A972" s="3">
         <v>10</v>
       </c>
-      <c r="B972" s="4">
+      <c r="B972" s="3">
         <v>71</v>
       </c>
       <c r="C972" t="s">
@@ -14738,10 +14732,10 @@
       </c>
     </row>
     <row r="973" spans="1:3">
-      <c r="A973" s="4">
+      <c r="A973" s="3">
         <v>10</v>
       </c>
-      <c r="B973" s="4">
+      <c r="B973" s="3">
         <v>72</v>
       </c>
       <c r="C973" t="s">
@@ -14749,10 +14743,10 @@
       </c>
     </row>
     <row r="974" spans="1:3">
-      <c r="A974" s="4">
+      <c r="A974" s="3">
         <v>10</v>
       </c>
-      <c r="B974" s="4">
+      <c r="B974" s="3">
         <v>73</v>
       </c>
       <c r="C974" t="s">
@@ -14760,10 +14754,10 @@
       </c>
     </row>
     <row r="975" spans="1:3">
-      <c r="A975" s="4">
+      <c r="A975" s="3">
         <v>10</v>
       </c>
-      <c r="B975" s="4">
+      <c r="B975" s="3">
         <v>74</v>
       </c>
       <c r="C975" t="s">
@@ -14771,10 +14765,10 @@
       </c>
     </row>
     <row r="976" spans="1:3">
-      <c r="A976" s="4">
+      <c r="A976" s="3">
         <v>10</v>
       </c>
-      <c r="B976" s="4">
+      <c r="B976" s="3">
         <v>75</v>
       </c>
       <c r="C976" t="s">
@@ -14782,10 +14776,10 @@
       </c>
     </row>
     <row r="977" spans="1:3">
-      <c r="A977" s="4">
+      <c r="A977" s="3">
         <v>10</v>
       </c>
-      <c r="B977" s="4">
+      <c r="B977" s="3">
         <v>76</v>
       </c>
       <c r="C977" t="s">
@@ -14793,10 +14787,10 @@
       </c>
     </row>
     <row r="978" spans="1:3">
-      <c r="A978" s="4">
+      <c r="A978" s="3">
         <v>10</v>
       </c>
-      <c r="B978" s="4">
+      <c r="B978" s="3">
         <v>77</v>
       </c>
       <c r="C978" t="s">
@@ -14804,10 +14798,10 @@
       </c>
     </row>
     <row r="979" spans="1:3">
-      <c r="A979" s="4">
+      <c r="A979" s="3">
         <v>10</v>
       </c>
-      <c r="B979" s="4">
+      <c r="B979" s="3">
         <v>78</v>
       </c>
       <c r="C979" t="s">
@@ -14815,10 +14809,10 @@
       </c>
     </row>
     <row r="980" spans="1:3">
-      <c r="A980" s="4">
+      <c r="A980" s="3">
         <v>10</v>
       </c>
-      <c r="B980" s="4">
+      <c r="B980" s="3">
         <v>79</v>
       </c>
       <c r="C980" t="s">
@@ -14826,10 +14820,10 @@
       </c>
     </row>
     <row r="981" spans="1:3">
-      <c r="A981" s="4">
+      <c r="A981" s="3">
         <v>10</v>
       </c>
-      <c r="B981" s="4">
+      <c r="B981" s="3">
         <v>80</v>
       </c>
       <c r="C981" t="s">
@@ -14837,10 +14831,10 @@
       </c>
     </row>
     <row r="982" spans="1:3">
-      <c r="A982" s="4">
+      <c r="A982" s="3">
         <v>10</v>
       </c>
-      <c r="B982" s="4">
+      <c r="B982" s="3">
         <v>81</v>
       </c>
       <c r="C982" t="s">
@@ -14848,10 +14842,10 @@
       </c>
     </row>
     <row r="983" spans="1:3">
-      <c r="A983" s="4">
+      <c r="A983" s="3">
         <v>10</v>
       </c>
-      <c r="B983" s="4">
+      <c r="B983" s="3">
         <v>82</v>
       </c>
       <c r="C983" t="s">
@@ -14859,10 +14853,10 @@
       </c>
     </row>
     <row r="984" spans="1:3">
-      <c r="A984" s="4">
+      <c r="A984" s="3">
         <v>10</v>
       </c>
-      <c r="B984" s="4">
+      <c r="B984" s="3">
         <v>83</v>
       </c>
       <c r="C984" t="s">
@@ -14870,10 +14864,10 @@
       </c>
     </row>
     <row r="985" spans="1:3">
-      <c r="A985" s="4">
+      <c r="A985" s="3">
         <v>10</v>
       </c>
-      <c r="B985" s="4">
+      <c r="B985" s="3">
         <v>84</v>
       </c>
       <c r="C985" t="s">
@@ -14881,10 +14875,10 @@
       </c>
     </row>
     <row r="986" spans="1:3">
-      <c r="A986" s="4">
+      <c r="A986" s="3">
         <v>10</v>
       </c>
-      <c r="B986" s="4">
+      <c r="B986" s="3">
         <v>85</v>
       </c>
       <c r="C986" t="s">
@@ -14892,10 +14886,10 @@
       </c>
     </row>
     <row r="987" spans="1:3">
-      <c r="A987" s="4">
+      <c r="A987" s="3">
         <v>10</v>
       </c>
-      <c r="B987" s="4">
+      <c r="B987" s="3">
         <v>86</v>
       </c>
       <c r="C987" t="s">
@@ -14903,10 +14897,10 @@
       </c>
     </row>
     <row r="988" spans="1:3">
-      <c r="A988" s="4">
+      <c r="A988" s="3">
         <v>10</v>
       </c>
-      <c r="B988" s="4">
+      <c r="B988" s="3">
         <v>87</v>
       </c>
       <c r="C988" t="s">
@@ -14914,10 +14908,10 @@
       </c>
     </row>
     <row r="989" spans="1:3">
-      <c r="A989" s="4">
+      <c r="A989" s="3">
         <v>10</v>
       </c>
-      <c r="B989" s="4">
+      <c r="B989" s="3">
         <v>88</v>
       </c>
       <c r="C989" t="s">
@@ -14925,10 +14919,10 @@
       </c>
     </row>
     <row r="990" spans="1:3">
-      <c r="A990" s="4">
+      <c r="A990" s="3">
         <v>10</v>
       </c>
-      <c r="B990" s="4">
+      <c r="B990" s="3">
         <v>89</v>
       </c>
       <c r="C990" t="s">
@@ -14936,10 +14930,10 @@
       </c>
     </row>
     <row r="991" spans="1:3">
-      <c r="A991" s="4">
+      <c r="A991" s="3">
         <v>10</v>
       </c>
-      <c r="B991" s="4">
+      <c r="B991" s="3">
         <v>90</v>
       </c>
       <c r="C991" t="s">
@@ -14947,10 +14941,10 @@
       </c>
     </row>
     <row r="992" spans="1:3">
-      <c r="A992" s="4">
+      <c r="A992" s="3">
         <v>10</v>
       </c>
-      <c r="B992" s="4">
+      <c r="B992" s="3">
         <v>91</v>
       </c>
       <c r="C992" t="s">
@@ -14958,10 +14952,10 @@
       </c>
     </row>
     <row r="993" spans="1:3">
-      <c r="A993" s="4">
+      <c r="A993" s="3">
         <v>10</v>
       </c>
-      <c r="B993" s="4">
+      <c r="B993" s="3">
         <v>92</v>
       </c>
       <c r="C993" t="s">
@@ -14969,10 +14963,10 @@
       </c>
     </row>
     <row r="994" spans="1:3">
-      <c r="A994" s="4">
+      <c r="A994" s="3">
         <v>10</v>
       </c>
-      <c r="B994" s="4">
+      <c r="B994" s="3">
         <v>93</v>
       </c>
       <c r="C994" t="s">
@@ -14980,10 +14974,10 @@
       </c>
     </row>
     <row r="995" spans="1:3">
-      <c r="A995" s="4">
+      <c r="A995" s="3">
         <v>10</v>
       </c>
-      <c r="B995" s="4">
+      <c r="B995" s="3">
         <v>94</v>
       </c>
       <c r="C995" t="s">
@@ -14991,10 +14985,10 @@
       </c>
     </row>
     <row r="996" spans="1:3">
-      <c r="A996" s="4">
+      <c r="A996" s="3">
         <v>10</v>
       </c>
-      <c r="B996" s="4">
+      <c r="B996" s="3">
         <v>95</v>
       </c>
       <c r="C996" t="s">
@@ -15002,10 +14996,10 @@
       </c>
     </row>
     <row r="997" spans="1:3">
-      <c r="A997" s="4">
+      <c r="A997" s="3">
         <v>10</v>
       </c>
-      <c r="B997" s="4">
+      <c r="B997" s="3">
         <v>96</v>
       </c>
       <c r="C997" t="s">
@@ -15013,10 +15007,10 @@
       </c>
     </row>
     <row r="998" spans="1:3">
-      <c r="A998" s="4">
+      <c r="A998" s="3">
         <v>10</v>
       </c>
-      <c r="B998" s="4">
+      <c r="B998" s="3">
         <v>97</v>
       </c>
       <c r="C998" t="s">
@@ -15024,10 +15018,10 @@
       </c>
     </row>
     <row r="999" spans="1:3">
-      <c r="A999" s="4">
+      <c r="A999" s="3">
         <v>10</v>
       </c>
-      <c r="B999" s="4">
+      <c r="B999" s="3">
         <v>98</v>
       </c>
       <c r="C999" t="s">
@@ -15035,10 +15029,10 @@
       </c>
     </row>
     <row r="1000" spans="1:3">
-      <c r="A1000" s="4">
+      <c r="A1000" s="3">
         <v>10</v>
       </c>
-      <c r="B1000" s="4">
+      <c r="B1000" s="3">
         <v>99</v>
       </c>
       <c r="C1000" t="s">
@@ -15046,10 +15040,10 @@
       </c>
     </row>
     <row r="1001" spans="1:3">
-      <c r="A1001" s="4">
+      <c r="A1001" s="3">
         <v>10</v>
       </c>
-      <c r="B1001" s="4">
+      <c r="B1001" s="3">
         <v>100</v>
       </c>
       <c r="C1001" t="s">
